--- a/docs/reports/Shelly_Stock_Reorder.xlsx
+++ b/docs/reports/Shelly_Stock_Reorder.xlsx
@@ -8641,7 +8641,7 @@
     <row r="6">
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.1.0.</t>
+          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.4.0.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 29 Sep 2026 22:17</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Stock_Reorder.xlsx
+++ b/docs/reports/Shelly_Stock_Reorder.xlsx
@@ -8764,7 +8764,7 @@
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 03 Oct 2026 05:37</t>
+          <t>Generated by Shelly on 03 Oct 2026 05:51</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Stock_Reorder.xlsx
+++ b/docs/reports/Shelly_Stock_Reorder.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Model" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Raw" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lookup" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Notes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Model" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Pivot" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Raw" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Lookup" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Notes" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="in_lead">Assumptions!$C$6</definedName>
@@ -25,7 +25,7 @@
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
   <pivotCaches>
-    <pivotCache xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cacheId="1" r:id="rId8"/>
+    <pivotCache cacheId="1" r:id="rId8"/>
   </pivotCaches>
 </workbook>
 </file>
@@ -306,13 +306,13 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:bodyPr/>
+          <a:p>
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -334,10 +334,10 @@
             <v>Order $</v>
           </tx>
           <spPr>
-            <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:solidFill>
               <a:srgbClr val="2A8FB8"/>
             </a:solidFill>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:ln>
               <a:solidFill>
                 <a:srgbClr val="2A8FB8"/>
               </a:solidFill>
@@ -410,7 +410,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>1</col>
@@ -425,9 +425,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+      <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <c:chart r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -586,13 +586,13 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Daily demand" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1.286" maxValue="34.179"/>
+      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="0.643" maxValue="34.286"/>
     </cacheField>
     <cacheField name="Demand sd" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1.384" maxValue="14.368"/>
+      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="0.951" maxValue="14.658"/>
     </cacheField>
     <cacheField name="On hand" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsInteger="1" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="0" maxValue="135"/>
+      <sharedItems count="0" containsInteger="1" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="9" maxValue="344"/>
     </cacheField>
     <cacheField name="Shelf life days" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
       <sharedItems count="0" containsInteger="1" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1" maxValue="3650"/>
@@ -610,15 +610,51 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
   <r>
+    <x v="0"/>
     <x v="46"/>
-    <x v="8"/>
-    <x v="10"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="20.286"/>
+    <n v="6.879"/>
+    <n v="181"/>
+    <n v="5"/>
+    <n v="2.2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="49"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="9.929"/>
+    <n v="4.337"/>
+    <n v="104"/>
+    <n v="5"/>
+    <n v="2.7"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="13"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="7.286"/>
+    <n v="3.376"/>
+    <n v="48"/>
+    <n v="3"/>
+    <n v="3.3"/>
+    <n v="0"/>
+  </r>
+  <r>
     <x v="3"/>
-    <n v="17.357"/>
-    <n v="5.977"/>
-    <n v="6"/>
-    <n v="270"/>
-    <n v="3.2"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="5.607"/>
+    <n v="3.01"/>
+    <n v="37"/>
+    <n v="90"/>
+    <n v="3.9"/>
     <n v="0"/>
   </r>
   <r>
@@ -626,263 +662,35 @@
     <x v="16"/>
     <x v="2"/>
     <x v="2"/>
-    <n v="26.964"/>
-    <n v="11.902"/>
-    <n v="24"/>
+    <n v="30.5"/>
+    <n v="14.658"/>
+    <n v="235"/>
     <n v="365"/>
     <n v="2.15"/>
     <n v="0"/>
   </r>
   <r>
+    <x v="5"/>
     <x v="10"/>
-    <x v="4"/>
-    <x v="3"/>
-    <x v="4"/>
-    <n v="7.25"/>
-    <n v="4.664"/>
-    <n v="9"/>
-    <n v="60"/>
-    <n v="5.6"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="14.214"/>
+    <n v="4.879"/>
+    <n v="119"/>
+    <n v="270"/>
+    <n v="2.3"/>
     <n v="0"/>
   </r>
   <r>
-    <x v="36"/>
-    <x v="35"/>
-    <x v="1"/>
-    <x v="10"/>
-    <n v="2.107"/>
-    <n v="1.75"/>
-    <n v="0"/>
-    <n v="730"/>
-    <n v="12.8"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="16"/>
-    <x v="18"/>
-    <x v="5"/>
-    <x v="0"/>
-    <n v="4.75"/>
-    <n v="1.506"/>
-    <n v="4"/>
+    <x v="6"/>
+    <x v="42"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="11.679"/>
+    <n v="3.982"/>
+    <n v="106"/>
     <n v="365"/>
-    <n v="7.1"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="22"/>
-    <x v="25"/>
-    <x v="6"/>
-    <x v="0"/>
-    <n v="14.036"/>
-    <n v="4.384"/>
-    <n v="25"/>
-    <n v="365"/>
-    <n v="2.6"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="29"/>
-    <x v="9"/>
-    <x v="6"/>
-    <x v="11"/>
-    <n v="3.357"/>
-    <n v="1.768"/>
-    <n v="5"/>
-    <n v="180"/>
-    <n v="7.6"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="47"/>
-    <x v="30"/>
-    <x v="10"/>
-    <x v="15"/>
-    <n v="10.357"/>
-    <n v="3.889"/>
-    <n v="16"/>
-    <n v="240"/>
-    <n v="2.6"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="41"/>
-    <x v="43"/>
-    <x v="7"/>
-    <x v="12"/>
-    <n v="2.321"/>
-    <n v="1.442"/>
-    <n v="3"/>
-    <n v="730"/>
-    <n v="8.199999999999999"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="27"/>
-    <x v="45"/>
-    <x v="6"/>
-    <x v="9"/>
-    <n v="2.786"/>
-    <n v="2.234"/>
-    <n v="1"/>
-    <n v="365"/>
-    <n v="4"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="49"/>
-    <x v="27"/>
-    <x v="10"/>
-    <x v="3"/>
-    <n v="10.75"/>
-    <n v="4.979"/>
-    <n v="20"/>
-    <n v="300"/>
-    <n v="1.7"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="2"/>
-    <x v="13"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="6.75"/>
-    <n v="3.122"/>
-    <n v="7"/>
-    <n v="3"/>
-    <n v="3.3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="25"/>
-    <x v="41"/>
-    <x v="6"/>
-    <x v="11"/>
-    <n v="5.286"/>
-    <n v="2.507"/>
-    <n v="9"/>
-    <n v="540"/>
-    <n v="2.3"/>
-    <n v="1"/>
-  </r>
-  <r>
-    <x v="23"/>
-    <x v="5"/>
-    <x v="6"/>
-    <x v="11"/>
-    <n v="6.143"/>
-    <n v="2.46"/>
-    <n v="10"/>
-    <n v="730"/>
-    <n v="1.9"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="40"/>
-    <x v="32"/>
-    <x v="7"/>
-    <x v="12"/>
-    <n v="4.607"/>
-    <n v="2.544"/>
-    <n v="8"/>
-    <n v="730"/>
-    <n v="1.6"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="19"/>
-    <x v="21"/>
-    <x v="4"/>
-    <x v="6"/>
-    <n v="18.179"/>
-    <n v="4.347"/>
-    <n v="27"/>
-    <n v="2"/>
-    <n v="2.4"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="37"/>
-    <x v="29"/>
-    <x v="3"/>
-    <x v="4"/>
-    <n v="34.179"/>
-    <n v="14.368"/>
-    <n v="135"/>
-    <n v="10"/>
-    <n v="3.55"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="35"/>
-    <x v="37"/>
-    <x v="1"/>
-    <x v="10"/>
-    <n v="4.179"/>
-    <n v="2.374"/>
-    <n v="13"/>
-    <n v="365"/>
-    <n v="11.9"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="0"/>
-    <x v="46"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="20.786"/>
-    <n v="6.511"/>
-    <n v="44"/>
-    <n v="5"/>
-    <n v="2.2"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="28"/>
-    <x v="15"/>
-    <x v="6"/>
-    <x v="5"/>
-    <n v="9.464"/>
-    <n v="4.55"/>
-    <n v="38"/>
-    <n v="35"/>
-    <n v="8.199999999999999"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="38"/>
-    <x v="28"/>
-    <x v="3"/>
-    <x v="4"/>
-    <n v="15.857"/>
-    <n v="4.942"/>
-    <n v="49"/>
-    <n v="10"/>
-    <n v="3.55"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="45"/>
-    <x v="36"/>
-    <x v="10"/>
-    <x v="15"/>
-    <n v="21.321"/>
-    <n v="6.492"/>
-    <n v="57"/>
-    <n v="180"/>
-    <n v="2.1"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="30"/>
-    <x v="47"/>
-    <x v="8"/>
-    <x v="8"/>
-    <n v="5.536"/>
-    <n v="2.603"/>
-    <n v="17"/>
-    <n v="3650"/>
-    <n v="5.9"/>
+    <n v="1.1"/>
     <n v="0"/>
   </r>
   <r>
@@ -890,155 +698,11 @@
     <x v="24"/>
     <x v="2"/>
     <x v="4"/>
-    <n v="13.143"/>
-    <n v="4.461"/>
-    <n v="39"/>
+    <n v="12.5"/>
+    <n v="4.726"/>
+    <n v="114"/>
     <n v="30"/>
     <n v="2.7"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="12"/>
-    <x v="6"/>
-    <x v="3"/>
-    <x v="4"/>
-    <n v="5.321"/>
-    <n v="2.229"/>
-    <n v="21"/>
-    <n v="90"/>
-    <n v="10.4"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="5"/>
-    <x v="10"/>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="14.321"/>
-    <n v="4.839"/>
-    <n v="47"/>
-    <n v="270"/>
-    <n v="2.3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="15"/>
-    <x v="19"/>
-    <x v="5"/>
-    <x v="7"/>
-    <n v="5.214"/>
-    <n v="2.807"/>
-    <n v="17"/>
-    <n v="365"/>
-    <n v="4.7"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="34"/>
-    <x v="40"/>
-    <x v="1"/>
-    <x v="10"/>
-    <n v="4.571"/>
-    <n v="2.268"/>
-    <n v="20"/>
-    <n v="730"/>
-    <n v="10.2"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="48"/>
-    <x v="11"/>
-    <x v="10"/>
-    <x v="9"/>
-    <n v="8.821"/>
-    <n v="2.982"/>
-    <n v="27"/>
-    <n v="180"/>
-    <n v="2.4"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="32"/>
-    <x v="34"/>
-    <x v="8"/>
-    <x v="8"/>
-    <n v="1.286"/>
-    <n v="1.384"/>
-    <n v="4"/>
-    <n v="3650"/>
-    <n v="5.5"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="24"/>
-    <x v="33"/>
-    <x v="6"/>
-    <x v="11"/>
-    <n v="6.929"/>
-    <n v="3.848"/>
-    <n v="15"/>
-    <n v="730"/>
-    <n v="1.3"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="39"/>
-    <x v="31"/>
-    <x v="3"/>
-    <x v="13"/>
-    <n v="7.357"/>
-    <n v="2.697"/>
-    <n v="28"/>
-    <n v="60"/>
-    <n v="2.7"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="31"/>
-    <x v="14"/>
-    <x v="8"/>
-    <x v="8"/>
-    <n v="3.214"/>
-    <n v="1.813"/>
-    <n v="14"/>
-    <n v="1095"/>
-    <n v="2.9"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="1"/>
-    <x v="49"/>
-    <x v="0"/>
-    <x v="1"/>
-    <n v="10.393"/>
-    <n v="3.804"/>
-    <n v="47"/>
-    <n v="5"/>
-    <n v="2.7"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="3"/>
-    <x v="3"/>
-    <x v="2"/>
-    <x v="0"/>
-    <n v="5.5"/>
-    <n v="2.546"/>
-    <n v="29"/>
-    <n v="90"/>
-    <n v="3.9"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="6"/>
-    <x v="42"/>
-    <x v="2"/>
-    <x v="2"/>
-    <n v="11.143"/>
-    <n v="3.669"/>
-    <n v="48"/>
-    <n v="365"/>
-    <n v="1.1"/>
     <n v="0"/>
   </r>
   <r>
@@ -1046,9 +710,9 @@
     <x v="26"/>
     <x v="2"/>
     <x v="13"/>
-    <n v="5.143"/>
-    <n v="3.535"/>
-    <n v="28"/>
+    <n v="4.571"/>
+    <n v="2.755"/>
+    <n v="56"/>
     <n v="120"/>
     <n v="2.6"/>
     <n v="0"/>
@@ -1058,11 +722,23 @@
     <x v="2"/>
     <x v="2"/>
     <x v="2"/>
-    <n v="15.964"/>
-    <n v="4.623"/>
-    <n v="73"/>
+    <n v="17.393"/>
+    <n v="5.101"/>
+    <n v="171"/>
     <n v="365"/>
     <n v="0.95"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="10"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="6.786"/>
+    <n v="4.677"/>
+    <n v="53"/>
+    <n v="60"/>
+    <n v="5.6"/>
     <n v="0"/>
   </r>
   <r>
@@ -1070,11 +746,23 @@
     <x v="20"/>
     <x v="3"/>
     <x v="4"/>
-    <n v="5.107"/>
-    <n v="2.544"/>
-    <n v="24"/>
+    <n v="4.893"/>
+    <n v="2.299"/>
+    <n v="51"/>
     <n v="21"/>
     <n v="5.1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="12"/>
+    <x v="6"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="5.214"/>
+    <n v="2.378"/>
+    <n v="50"/>
+    <n v="90"/>
+    <n v="10.4"/>
     <n v="0"/>
   </r>
   <r>
@@ -1082,9 +770,9 @@
     <x v="23"/>
     <x v="5"/>
     <x v="7"/>
-    <n v="5.214"/>
-    <n v="2.872"/>
-    <n v="30"/>
+    <n v="7.071"/>
+    <n v="3.126"/>
+    <n v="62"/>
     <n v="365"/>
     <n v="5.4"/>
     <n v="0"/>
@@ -1094,11 +782,35 @@
     <x v="22"/>
     <x v="5"/>
     <x v="7"/>
-    <n v="10.679"/>
-    <n v="3.549"/>
-    <n v="47"/>
+    <n v="9.893000000000001"/>
+    <n v="3.975"/>
+    <n v="102"/>
     <n v="365"/>
     <n v="1.2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="15"/>
+    <x v="19"/>
+    <x v="5"/>
+    <x v="7"/>
+    <n v="5.964"/>
+    <n v="3.361"/>
+    <n v="46"/>
+    <n v="365"/>
+    <n v="4.7"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="16"/>
+    <x v="18"/>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="4.464"/>
+    <n v="2.457"/>
+    <n v="32"/>
+    <n v="365"/>
+    <n v="7.1"/>
     <n v="0"/>
   </r>
   <r>
@@ -1106,9 +818,9 @@
     <x v="7"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="18.214"/>
-    <n v="4.459"/>
-    <n v="51"/>
+    <n v="19.357"/>
+    <n v="5.411"/>
+    <n v="147"/>
     <n v="2"/>
     <n v="3.9"/>
     <n v="0"/>
@@ -1118,11 +830,23 @@
     <x v="44"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="10.857"/>
-    <n v="6.029"/>
-    <n v="60"/>
+    <n v="9.214"/>
+    <n v="3.224"/>
+    <n v="117"/>
     <n v="1"/>
     <n v="5.6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="19"/>
+    <x v="21"/>
+    <x v="4"/>
+    <x v="6"/>
+    <n v="18.143"/>
+    <n v="6.346"/>
+    <n v="129"/>
+    <n v="2"/>
+    <n v="2.4"/>
     <n v="0"/>
   </r>
   <r>
@@ -1130,9 +854,9 @@
     <x v="38"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="5.893"/>
-    <n v="2.807"/>
-    <n v="21"/>
+    <n v="6.286"/>
+    <n v="2.637"/>
+    <n v="51"/>
     <n v="2"/>
     <n v="6.2"/>
     <n v="0"/>
@@ -1142,23 +866,143 @@
     <x v="17"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="11.893"/>
-    <n v="3.891"/>
-    <n v="33"/>
+    <n v="11"/>
+    <n v="4.823"/>
+    <n v="91"/>
     <n v="2"/>
     <n v="3.2"/>
     <n v="0"/>
+  </r>
+  <r>
+    <x v="22"/>
+    <x v="25"/>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="11.857"/>
+    <n v="4.369"/>
+    <n v="89"/>
+    <n v="365"/>
+    <n v="2.6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="23"/>
+    <x v="5"/>
+    <x v="6"/>
+    <x v="11"/>
+    <n v="5.786"/>
+    <n v="3.201"/>
+    <n v="40"/>
+    <n v="730"/>
+    <n v="1.9"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="24"/>
+    <x v="33"/>
+    <x v="6"/>
+    <x v="11"/>
+    <n v="6.714"/>
+    <n v="3.041"/>
+    <n v="48"/>
+    <n v="730"/>
+    <n v="1.3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="25"/>
+    <x v="41"/>
+    <x v="6"/>
+    <x v="11"/>
+    <n v="5"/>
+    <n v="2.553"/>
+    <n v="28"/>
+    <n v="540"/>
+    <n v="2.3"/>
+    <n v="1"/>
   </r>
   <r>
     <x v="26"/>
     <x v="39"/>
     <x v="6"/>
     <x v="9"/>
-    <n v="2.857"/>
-    <n v="2.46"/>
-    <n v="19"/>
+    <n v="2.679"/>
+    <n v="2.389"/>
+    <n v="33"/>
     <n v="365"/>
     <n v="2.9"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="27"/>
+    <x v="45"/>
+    <x v="6"/>
+    <x v="9"/>
+    <n v="2.893"/>
+    <n v="1.524"/>
+    <n v="31"/>
+    <n v="365"/>
+    <n v="4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="28"/>
+    <x v="15"/>
+    <x v="6"/>
+    <x v="5"/>
+    <n v="9.393000000000001"/>
+    <n v="3.573"/>
+    <n v="77"/>
+    <n v="35"/>
+    <n v="8.199999999999999"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="29"/>
+    <x v="9"/>
+    <x v="6"/>
+    <x v="11"/>
+    <n v="3.643"/>
+    <n v="2.147"/>
+    <n v="28"/>
+    <n v="180"/>
+    <n v="7.6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="30"/>
+    <x v="47"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="5.5"/>
+    <n v="2.411"/>
+    <n v="47"/>
+    <n v="3650"/>
+    <n v="5.9"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="31"/>
+    <x v="14"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="2.107"/>
+    <n v="1.37"/>
+    <n v="23"/>
+    <n v="1095"/>
+    <n v="2.9"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="32"/>
+    <x v="34"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="0.643"/>
+    <n v="0.951"/>
+    <n v="9"/>
+    <n v="3650"/>
+    <n v="5.5"/>
     <n v="0"/>
   </r>
   <r>
@@ -1166,11 +1010,107 @@
     <x v="12"/>
     <x v="1"/>
     <x v="10"/>
-    <n v="4.821"/>
-    <n v="3.092"/>
-    <n v="36"/>
+    <n v="4.857"/>
+    <n v="2.649"/>
+    <n v="49"/>
     <n v="180"/>
     <n v="15.3"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="34"/>
+    <x v="40"/>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="5.286"/>
+    <n v="3.017"/>
+    <n v="54"/>
+    <n v="730"/>
+    <n v="10.2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="35"/>
+    <x v="37"/>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="3.857"/>
+    <n v="2.05"/>
+    <n v="42"/>
+    <n v="365"/>
+    <n v="11.9"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="36"/>
+    <x v="35"/>
+    <x v="1"/>
+    <x v="10"/>
+    <n v="1.929"/>
+    <n v="1.904"/>
+    <n v="14"/>
+    <n v="730"/>
+    <n v="12.8"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="37"/>
+    <x v="29"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="34.286"/>
+    <n v="13.424"/>
+    <n v="344"/>
+    <n v="10"/>
+    <n v="3.55"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="38"/>
+    <x v="28"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="14.607"/>
+    <n v="4.113"/>
+    <n v="145"/>
+    <n v="10"/>
+    <n v="3.55"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="39"/>
+    <x v="31"/>
+    <x v="3"/>
+    <x v="13"/>
+    <n v="8.071"/>
+    <n v="4.225"/>
+    <n v="60"/>
+    <n v="60"/>
+    <n v="2.7"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="40"/>
+    <x v="32"/>
+    <x v="7"/>
+    <x v="12"/>
+    <n v="5.357"/>
+    <n v="3.021"/>
+    <n v="38"/>
+    <n v="730"/>
+    <n v="1.6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="41"/>
+    <x v="43"/>
+    <x v="7"/>
+    <x v="12"/>
+    <n v="1.714"/>
+    <n v="1.243"/>
+    <n v="17"/>
+    <n v="730"/>
+    <n v="8.199999999999999"/>
     <n v="0"/>
   </r>
   <r>
@@ -1178,9 +1118,9 @@
     <x v="1"/>
     <x v="9"/>
     <x v="14"/>
-    <n v="32.429"/>
-    <n v="8.02"/>
-    <n v="121"/>
+    <n v="31.607"/>
+    <n v="6.63"/>
+    <n v="270"/>
     <n v="6"/>
     <n v="0.38"/>
     <n v="0"/>
@@ -1190,9 +1130,9 @@
     <x v="0"/>
     <x v="9"/>
     <x v="14"/>
-    <n v="7.107"/>
-    <n v="2.529"/>
-    <n v="33"/>
+    <n v="8.071"/>
+    <n v="3.463"/>
+    <n v="69"/>
     <n v="5"/>
     <n v="1.4"/>
     <n v="0"/>
@@ -1202,11 +1142,71 @@
     <x v="48"/>
     <x v="9"/>
     <x v="14"/>
-    <n v="3.929"/>
-    <n v="2.035"/>
-    <n v="32"/>
+    <n v="4.5"/>
+    <n v="2.769"/>
+    <n v="48"/>
     <n v="7"/>
     <n v="2.6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="45"/>
+    <x v="36"/>
+    <x v="10"/>
+    <x v="15"/>
+    <n v="20.679"/>
+    <n v="6.717"/>
+    <n v="170"/>
+    <n v="180"/>
+    <n v="2.1"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="46"/>
+    <x v="8"/>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="15.821"/>
+    <n v="4.785"/>
+    <n v="106"/>
+    <n v="270"/>
+    <n v="3.2"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="47"/>
+    <x v="30"/>
+    <x v="10"/>
+    <x v="15"/>
+    <n v="9.356999999999999"/>
+    <n v="3.498"/>
+    <n v="74"/>
+    <n v="240"/>
+    <n v="2.6"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="48"/>
+    <x v="11"/>
+    <x v="10"/>
+    <x v="9"/>
+    <n v="9.143000000000001"/>
+    <n v="3.229"/>
+    <n v="74"/>
+    <n v="180"/>
+    <n v="2.4"/>
+    <n v="0"/>
+  </r>
+  <r>
+    <x v="49"/>
+    <x v="27"/>
+    <x v="10"/>
+    <x v="3"/>
+    <n v="10.107"/>
+    <n v="3.833"/>
+    <n v="83"/>
+    <n v="300"/>
+    <n v="1.7"/>
     <n v="0"/>
   </r>
 </pivotCacheRecords>
@@ -1738,7 +1738,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Demo Neighbourhood Store (Eden Terrace format) · stock position at 25 Sep 2026</t>
+          <t>Demo Neighbourhood Store (Eden Terrace format) · stock position at 04 Oct 2026</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1804,17 +1804,17 @@
     <row r="10">
       <c r="B10" s="10">
         <f>SUMIFS(Model!$L$8:$L$57,Model!$O$8:$O$57,1)</f>
-        <v>2958.3</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="11">
         <f>COUNTIFS(Model!$K$8:$K$57,"&gt;0",Model!$O$8:$O$57,1)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="11">
         <f>COUNTIFS(Model!$N$8:$N$57,"Order now",Model!$O$8:$O$57,1)</f>
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J10" s="9" t="n"/>
       <c r="K10" s="11">
@@ -2059,39 +2059,39 @@
       </c>
       <c r="F8" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B8,Raw!$A$2:$A$51,0))</f>
-        <v>6.75</v>
+        <v>7.286</v>
       </c>
       <c r="G8" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B8,Raw!$A$2:$A$51,0))</f>
-        <v>7</v>
+        <v>48</v>
       </c>
       <c r="H8" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B8,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.92231332502956</v>
+        <v>9.64821581848167</v>
       </c>
       <c r="I8" s="15">
         <f>MIN(F8*(Assumptions!$C$6+Assumptions!$C$7)+H8,F8*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B8,Raw!$A$2:$A$51,0))))</f>
-        <v>20.25</v>
+        <v>21.858</v>
       </c>
       <c r="J8" s="15">
         <f>MIN(I8+F8*Assumptions!$C$7,F8*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B8,Raw!$A$2:$A$51,0))))</f>
-        <v>20.25</v>
+        <v>21.858</v>
       </c>
       <c r="K8" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B8,Raw!$A$2:$A$51,0))=1,G8&gt;I8),0,ROUNDUP(MAX(0,J8-G8),0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L8" s="17">
         <f>K8*INDEX(Raw!$I$2:$I$51,MATCH($B8,Raw!$A$2:$A$51,0))</f>
-        <v>46.2</v>
+        <v>0</v>
       </c>
       <c r="M8" s="15">
         <f>IFERROR(G8/F8,0)</f>
-        <v>1.03703703703704</v>
+        <v>6.5879769420807</v>
       </c>
       <c r="N8" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B8,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M8&lt;Assumptions!$C$6,"Order now",IF(K8&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O8" s="16">
         <f>IF(OR(SelCat="All",D8=SelCat),1,0)</f>
@@ -2118,39 +2118,39 @@
       </c>
       <c r="F9" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B9,Raw!$A$2:$A$51,0))</f>
-        <v>20.786</v>
+        <v>20.286</v>
       </c>
       <c r="G9" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B9,Raw!$A$2:$A$51,0))</f>
-        <v>44</v>
+        <v>181</v>
       </c>
       <c r="H9" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B9,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>18.6076816333336</v>
+        <v>19.6593828836894</v>
       </c>
       <c r="I9" s="15">
         <f>MIN(F9*(Assumptions!$C$6+Assumptions!$C$7)+H9,F9*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B9,Raw!$A$2:$A$51,0))))</f>
-        <v>80.9656816333336</v>
+        <v>80.5173828836894</v>
       </c>
       <c r="J9" s="15">
         <f>MIN(I9+F9*Assumptions!$C$7,F9*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B9,Raw!$A$2:$A$51,0))))</f>
-        <v>101.751681633334</v>
+        <v>100.803382883689</v>
       </c>
       <c r="K9" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B9,Raw!$A$2:$A$51,0))=1,G9&gt;I9),0,ROUNDUP(MAX(0,J9-G9),0))</f>
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="L9" s="17">
         <f>K9*INDEX(Raw!$I$2:$I$51,MATCH($B9,Raw!$A$2:$A$51,0))</f>
-        <v>127.6</v>
+        <v>0</v>
       </c>
       <c r="M9" s="15">
         <f>IFERROR(G9/F9,0)</f>
-        <v>2.11680939093621</v>
+        <v>8.92240954352756</v>
       </c>
       <c r="N9" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B9,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M9&lt;Assumptions!$C$6,"Order now",IF(K9&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O9" s="16">
         <f>IF(OR(SelCat="All",D9=SelCat),1,0)</f>
@@ -2177,23 +2177,23 @@
       </c>
       <c r="F10" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B10,Raw!$A$2:$A$51,0))</f>
-        <v>10.393</v>
+        <v>9.929</v>
       </c>
       <c r="G10" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B10,Raw!$A$2:$A$51,0))</f>
-        <v>47</v>
+        <v>104</v>
       </c>
       <c r="H10" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B10,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>10.8713900987868</v>
+        <v>12.3946421815033</v>
       </c>
       <c r="I10" s="15">
         <f>MIN(F10*(Assumptions!$C$6+Assumptions!$C$7)+H10,F10*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B10,Raw!$A$2:$A$51,0))))</f>
-        <v>42.0503900987868</v>
+        <v>42.1816421815033</v>
       </c>
       <c r="J10" s="15">
         <f>MIN(I10+F10*Assumptions!$C$7,F10*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B10,Raw!$A$2:$A$51,0))))</f>
-        <v>51.965</v>
+        <v>49.645</v>
       </c>
       <c r="K10" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B10,Raw!$A$2:$A$51,0))=1,G10&gt;I10),0,ROUNDUP(MAX(0,J10-G10),0))</f>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M10" s="15">
         <f>IFERROR(G10/F10,0)</f>
-        <v>4.52227460790917</v>
+        <v>10.4743680128915</v>
       </c>
       <c r="N10" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B10,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M10&lt;Assumptions!$C$6,"Order now",IF(K10&gt;0,"Order","OK")))</f>
@@ -2236,23 +2236,23 @@
       </c>
       <c r="F11" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B11,Raw!$A$2:$A$51,0))</f>
-        <v>4.821</v>
+        <v>4.857</v>
       </c>
       <c r="G11" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B11,Raw!$A$2:$A$51,0))</f>
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="H11" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B11,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.8365768100549</v>
+        <v>7.57053427226243</v>
       </c>
       <c r="I11" s="15">
         <f>MIN(F11*(Assumptions!$C$6+Assumptions!$C$7)+H11,F11*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B11,Raw!$A$2:$A$51,0))))</f>
-        <v>23.2995768100549</v>
+        <v>22.1415342722624</v>
       </c>
       <c r="J11" s="15">
         <f>MIN(I11+F11*Assumptions!$C$7,F11*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B11,Raw!$A$2:$A$51,0))))</f>
-        <v>28.1205768100549</v>
+        <v>26.9985342722624</v>
       </c>
       <c r="K11" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B11,Raw!$A$2:$A$51,0))=1,G11&gt;I11),0,ROUNDUP(MAX(0,J11-G11),0))</f>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M11" s="15">
         <f>IFERROR(G11/F11,0)</f>
-        <v>7.4673304293715</v>
+        <v>10.0885320156475</v>
       </c>
       <c r="N11" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B11,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M11&lt;Assumptions!$C$6,"Order now",IF(K11&gt;0,"Order","OK")))</f>
@@ -2295,39 +2295,39 @@
       </c>
       <c r="F12" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B12,Raw!$A$2:$A$51,0))</f>
-        <v>2.107</v>
+        <v>1.929</v>
       </c>
       <c r="G12" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B12,Raw!$A$2:$A$51,0))</f>
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="H12" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B12,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>5.00129670685513</v>
+        <v>5.44141081705838</v>
       </c>
       <c r="I12" s="15">
         <f>MIN(F12*(Assumptions!$C$6+Assumptions!$C$7)+H12,F12*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B12,Raw!$A$2:$A$51,0))))</f>
-        <v>11.3222967068551</v>
+        <v>11.2284108170584</v>
       </c>
       <c r="J12" s="15">
         <f>MIN(I12+F12*Assumptions!$C$7,F12*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B12,Raw!$A$2:$A$51,0))))</f>
-        <v>13.4292967068551</v>
+        <v>13.1574108170584</v>
       </c>
       <c r="K12" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B12,Raw!$A$2:$A$51,0))=1,G12&gt;I12),0,ROUNDUP(MAX(0,J12-G12),0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L12" s="17">
         <f>K12*INDEX(Raw!$I$2:$I$51,MATCH($B12,Raw!$A$2:$A$51,0))</f>
-        <v>179.2</v>
+        <v>0</v>
       </c>
       <c r="M12" s="15">
         <f>IFERROR(G12/F12,0)</f>
-        <v>0</v>
+        <v>7.25764644893727</v>
       </c>
       <c r="N12" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B12,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M12&lt;Assumptions!$C$6,"Order now",IF(K12&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O12" s="16">
         <f>IF(OR(SelCat="All",D12=SelCat),1,0)</f>
@@ -2354,39 +2354,39 @@
       </c>
       <c r="F13" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B13,Raw!$A$2:$A$51,0))</f>
-        <v>4.179</v>
+        <v>3.857</v>
       </c>
       <c r="G13" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B13,Raw!$A$2:$A$51,0))</f>
-        <v>13</v>
+        <v>42</v>
       </c>
       <c r="H13" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B13,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.78461621832805</v>
+        <v>5.85866185660173</v>
       </c>
       <c r="I13" s="15">
         <f>MIN(F13*(Assumptions!$C$6+Assumptions!$C$7)+H13,F13*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B13,Raw!$A$2:$A$51,0))))</f>
-        <v>19.3216162183281</v>
+        <v>17.4296618566017</v>
       </c>
       <c r="J13" s="15">
         <f>MIN(I13+F13*Assumptions!$C$7,F13*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B13,Raw!$A$2:$A$51,0))))</f>
-        <v>23.500616218328</v>
+        <v>21.2866618566017</v>
       </c>
       <c r="K13" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B13,Raw!$A$2:$A$51,0))=1,G13&gt;I13),0,ROUNDUP(MAX(0,J13-G13),0))</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L13" s="17">
         <f>K13*INDEX(Raw!$I$2:$I$51,MATCH($B13,Raw!$A$2:$A$51,0))</f>
-        <v>130.9</v>
+        <v>0</v>
       </c>
       <c r="M13" s="15">
         <f>IFERROR(G13/F13,0)</f>
-        <v>3.11079205551567</v>
+        <v>10.8892921960073</v>
       </c>
       <c r="N13" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B13,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M13&lt;Assumptions!$C$6,"Order now",IF(K13&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O13" s="16">
         <f>IF(OR(SelCat="All",D13=SelCat),1,0)</f>
@@ -2413,39 +2413,39 @@
       </c>
       <c r="F14" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B14,Raw!$A$2:$A$51,0))</f>
-        <v>4.571</v>
+        <v>5.286</v>
       </c>
       <c r="G14" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B14,Raw!$A$2:$A$51,0))</f>
-        <v>20</v>
+        <v>54</v>
       </c>
       <c r="H14" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B14,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.48168053208425</v>
+        <v>8.62223552261825</v>
       </c>
       <c r="I14" s="15">
         <f>MIN(F14*(Assumptions!$C$6+Assumptions!$C$7)+H14,F14*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B14,Raw!$A$2:$A$51,0))))</f>
-        <v>20.1946805320843</v>
+        <v>24.4802355226182</v>
       </c>
       <c r="J14" s="15">
         <f>MIN(I14+F14*Assumptions!$C$7,F14*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B14,Raw!$A$2:$A$51,0))))</f>
-        <v>24.7656805320842</v>
+        <v>29.7662355226182</v>
       </c>
       <c r="K14" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B14,Raw!$A$2:$A$51,0))=1,G14&gt;I14),0,ROUNDUP(MAX(0,J14-G14),0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L14" s="17">
         <f>K14*INDEX(Raw!$I$2:$I$51,MATCH($B14,Raw!$A$2:$A$51,0))</f>
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="M14" s="15">
         <f>IFERROR(G14/F14,0)</f>
-        <v>4.37541019470575</v>
+        <v>10.2156640181612</v>
       </c>
       <c r="N14" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B14,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M14&lt;Assumptions!$C$6,"Order now",IF(K14&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O14" s="16">
         <f>IF(OR(SelCat="All",D14=SelCat),1,0)</f>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="F15" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B15,Raw!$A$2:$A$51,0))</f>
-        <v>15.964</v>
+        <v>17.393</v>
       </c>
       <c r="G15" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B15,Raw!$A$2:$A$51,0))</f>
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="H15" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B15,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.211996957595</v>
+        <v>14.5780654295246</v>
       </c>
       <c r="I15" s="15">
         <f>MIN(F15*(Assumptions!$C$6+Assumptions!$C$7)+H15,F15*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B15,Raw!$A$2:$A$51,0))))</f>
-        <v>61.103996957595</v>
+        <v>66.7570654295246</v>
       </c>
       <c r="J15" s="15">
         <f>MIN(I15+F15*Assumptions!$C$7,F15*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B15,Raw!$A$2:$A$51,0))))</f>
-        <v>77.067996957595</v>
+        <v>84.1500654295246</v>
       </c>
       <c r="K15" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B15,Raw!$A$2:$A$51,0))=1,G15&gt;I15),0,ROUNDUP(MAX(0,J15-G15),0))</f>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="M15" s="15">
         <f>IFERROR(G15/F15,0)</f>
-        <v>4.57278877474317</v>
+        <v>9.83154142471109</v>
       </c>
       <c r="N15" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B15,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M15&lt;Assumptions!$C$6,"Order now",IF(K15&gt;0,"Order","OK")))</f>
@@ -2531,23 +2531,23 @@
       </c>
       <c r="F16" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B16,Raw!$A$2:$A$51,0))</f>
-        <v>5.5</v>
+        <v>5.607</v>
       </c>
       <c r="G16" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B16,Raw!$A$2:$A$51,0))</f>
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H16" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B16,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.2761722375161</v>
+        <v>8.60223033579083</v>
       </c>
       <c r="I16" s="15">
         <f>MIN(F16*(Assumptions!$C$6+Assumptions!$C$7)+H16,F16*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B16,Raw!$A$2:$A$51,0))))</f>
-        <v>23.7761722375161</v>
+        <v>25.4232303357908</v>
       </c>
       <c r="J16" s="15">
         <f>MIN(I16+F16*Assumptions!$C$7,F16*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B16,Raw!$A$2:$A$51,0))))</f>
-        <v>29.2761722375161</v>
+        <v>31.0302303357908</v>
       </c>
       <c r="K16" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B16,Raw!$A$2:$A$51,0))=1,G16&gt;I16),0,ROUNDUP(MAX(0,J16-G16),0))</f>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M16" s="15">
         <f>IFERROR(G16/F16,0)</f>
-        <v>5.27272727272727</v>
+        <v>6.59889423934368</v>
       </c>
       <c r="N16" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B16,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M16&lt;Assumptions!$C$6,"Order now",IF(K16&gt;0,"Order","OK")))</f>
@@ -2590,39 +2590,39 @@
       </c>
       <c r="F17" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B17,Raw!$A$2:$A$51,0))</f>
-        <v>14.321</v>
+        <v>14.214</v>
       </c>
       <c r="G17" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B17,Raw!$A$2:$A$51,0))</f>
-        <v>47</v>
+        <v>119</v>
       </c>
       <c r="H17" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B17,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.8292998654126</v>
+        <v>13.9436152187121</v>
       </c>
       <c r="I17" s="15">
         <f>MIN(F17*(Assumptions!$C$6+Assumptions!$C$7)+H17,F17*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B17,Raw!$A$2:$A$51,0))))</f>
-        <v>56.7922998654126</v>
+        <v>56.5856152187121</v>
       </c>
       <c r="J17" s="15">
         <f>MIN(I17+F17*Assumptions!$C$7,F17*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B17,Raw!$A$2:$A$51,0))))</f>
-        <v>71.1132998654126</v>
+        <v>70.7996152187121</v>
       </c>
       <c r="K17" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B17,Raw!$A$2:$A$51,0))=1,G17&gt;I17),0,ROUNDUP(MAX(0,J17-G17),0))</f>
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="L17" s="17">
         <f>K17*INDEX(Raw!$I$2:$I$51,MATCH($B17,Raw!$A$2:$A$51,0))</f>
-        <v>57.5</v>
+        <v>0</v>
       </c>
       <c r="M17" s="15">
         <f>IFERROR(G17/F17,0)</f>
-        <v>3.28189372250541</v>
+        <v>8.37202757844379</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B17,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M17&lt;Assumptions!$C$6,"Order now",IF(K17&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O17" s="16">
         <f>IF(OR(SelCat="All",D17=SelCat),1,0)</f>
@@ -2649,39 +2649,39 @@
       </c>
       <c r="F18" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B18,Raw!$A$2:$A$51,0))</f>
-        <v>26.964</v>
+        <v>30.5</v>
       </c>
       <c r="G18" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B18,Raw!$A$2:$A$51,0))</f>
-        <v>24</v>
+        <v>235</v>
       </c>
       <c r="H18" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B18,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>34.0145333742799</v>
+        <v>41.8908612166186</v>
       </c>
       <c r="I18" s="15">
         <f>MIN(F18*(Assumptions!$C$6+Assumptions!$C$7)+H18,F18*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B18,Raw!$A$2:$A$51,0))))</f>
-        <v>114.90653337428</v>
+        <v>133.390861216619</v>
       </c>
       <c r="J18" s="15">
         <f>MIN(I18+F18*Assumptions!$C$7,F18*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B18,Raw!$A$2:$A$51,0))))</f>
-        <v>141.87053337428</v>
+        <v>163.890861216619</v>
       </c>
       <c r="K18" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B18,Raw!$A$2:$A$51,0))=1,G18&gt;I18),0,ROUNDUP(MAX(0,J18-G18),0))</f>
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="L18" s="17">
         <f>K18*INDEX(Raw!$I$2:$I$51,MATCH($B18,Raw!$A$2:$A$51,0))</f>
-        <v>253.7</v>
+        <v>0</v>
       </c>
       <c r="M18" s="15">
         <f>IFERROR(G18/F18,0)</f>
-        <v>0.890075656430797</v>
+        <v>7.70491803278689</v>
       </c>
       <c r="N18" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B18,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M18&lt;Assumptions!$C$6,"Order now",IF(K18&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O18" s="16">
         <f>IF(OR(SelCat="All",D18=SelCat),1,0)</f>
@@ -2708,39 +2708,39 @@
       </c>
       <c r="F19" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B19,Raw!$A$2:$A$51,0))</f>
-        <v>13.143</v>
+        <v>12.5</v>
       </c>
       <c r="G19" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B19,Raw!$A$2:$A$51,0))</f>
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="H19" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B19,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>12.7490197767319</v>
+        <v>13.5063589923413</v>
       </c>
       <c r="I19" s="15">
         <f>MIN(F19*(Assumptions!$C$6+Assumptions!$C$7)+H19,F19*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B19,Raw!$A$2:$A$51,0))))</f>
-        <v>52.1780197767319</v>
+        <v>51.0063589923414</v>
       </c>
       <c r="J19" s="15">
         <f>MIN(I19+F19*Assumptions!$C$7,F19*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B19,Raw!$A$2:$A$51,0))))</f>
-        <v>65.3210197767319</v>
+        <v>63.5063589923414</v>
       </c>
       <c r="K19" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B19,Raw!$A$2:$A$51,0))=1,G19&gt;I19),0,ROUNDUP(MAX(0,J19-G19),0))</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="L19" s="17">
         <f>K19*INDEX(Raw!$I$2:$I$51,MATCH($B19,Raw!$A$2:$A$51,0))</f>
-        <v>72.9</v>
+        <v>0</v>
       </c>
       <c r="M19" s="15">
         <f>IFERROR(G19/F19,0)</f>
-        <v>2.9673590504451</v>
+        <v>9.12</v>
       </c>
       <c r="N19" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B19,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M19&lt;Assumptions!$C$6,"Order now",IF(K19&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O19" s="16">
         <f>IF(OR(SelCat="All",D19=SelCat),1,0)</f>
@@ -2767,23 +2767,23 @@
       </c>
       <c r="F20" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B20,Raw!$A$2:$A$51,0))</f>
-        <v>5.143</v>
+        <v>4.571</v>
       </c>
       <c r="G20" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B20,Raw!$A$2:$A$51,0))</f>
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="H20" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B20,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>10.1026193478474</v>
+        <v>7.87346995850622</v>
       </c>
       <c r="I20" s="15">
         <f>MIN(F20*(Assumptions!$C$6+Assumptions!$C$7)+H20,F20*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B20,Raw!$A$2:$A$51,0))))</f>
-        <v>25.5316193478474</v>
+        <v>21.5864699585062</v>
       </c>
       <c r="J20" s="15">
         <f>MIN(I20+F20*Assumptions!$C$7,F20*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B20,Raw!$A$2:$A$51,0))))</f>
-        <v>30.6746193478474</v>
+        <v>26.1574699585062</v>
       </c>
       <c r="K20" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B20,Raw!$A$2:$A$51,0))=1,G20&gt;I20),0,ROUNDUP(MAX(0,J20-G20),0))</f>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="M20" s="15">
         <f>IFERROR(G20/F20,0)</f>
-        <v>5.44429321407739</v>
+        <v>12.2511485451761</v>
       </c>
       <c r="N20" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B20,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M20&lt;Assumptions!$C$6,"Order now",IF(K20&gt;0,"Order","OK")))</f>
@@ -2826,23 +2826,23 @@
       </c>
       <c r="F21" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B21,Raw!$A$2:$A$51,0))</f>
-        <v>11.143</v>
+        <v>11.679</v>
       </c>
       <c r="G21" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B21,Raw!$A$2:$A$51,0))</f>
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="H21" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B21,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>10.4855757814008</v>
+        <v>11.3800934209698</v>
       </c>
       <c r="I21" s="15">
         <f>MIN(F21*(Assumptions!$C$6+Assumptions!$C$7)+H21,F21*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B21,Raw!$A$2:$A$51,0))))</f>
-        <v>43.9145757814009</v>
+        <v>46.4170934209698</v>
       </c>
       <c r="J21" s="15">
         <f>MIN(I21+F21*Assumptions!$C$7,F21*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B21,Raw!$A$2:$A$51,0))))</f>
-        <v>55.0575757814009</v>
+        <v>58.0960934209698</v>
       </c>
       <c r="K21" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B21,Raw!$A$2:$A$51,0))=1,G21&gt;I21),0,ROUNDUP(MAX(0,J21-G21),0))</f>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="M21" s="15">
         <f>IFERROR(G21/F21,0)</f>
-        <v>4.30763708157588</v>
+        <v>9.07611953078174</v>
       </c>
       <c r="N21" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B21,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M21&lt;Assumptions!$C$6,"Order now",IF(K21&gt;0,"Order","OK")))</f>
@@ -2885,39 +2885,39 @@
       </c>
       <c r="F22" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B22,Raw!$A$2:$A$51,0))</f>
-        <v>7.25</v>
+        <v>6.786</v>
       </c>
       <c r="G22" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B22,Raw!$A$2:$A$51,0))</f>
-        <v>9</v>
+        <v>53</v>
       </c>
       <c r="H22" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B22,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.3291701947271</v>
+        <v>13.3663226845494</v>
       </c>
       <c r="I22" s="15">
         <f>MIN(F22*(Assumptions!$C$6+Assumptions!$C$7)+H22,F22*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B22,Raw!$A$2:$A$51,0))))</f>
-        <v>35.0791701947271</v>
+        <v>33.7243226845494</v>
       </c>
       <c r="J22" s="15">
         <f>MIN(I22+F22*Assumptions!$C$7,F22*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B22,Raw!$A$2:$A$51,0))))</f>
-        <v>42.3291701947271</v>
+        <v>40.5103226845494</v>
       </c>
       <c r="K22" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B22,Raw!$A$2:$A$51,0))=1,G22&gt;I22),0,ROUNDUP(MAX(0,J22-G22),0))</f>
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="L22" s="17">
         <f>K22*INDEX(Raw!$I$2:$I$51,MATCH($B22,Raw!$A$2:$A$51,0))</f>
-        <v>190.4</v>
+        <v>0</v>
       </c>
       <c r="M22" s="15">
         <f>IFERROR(G22/F22,0)</f>
-        <v>1.24137931034483</v>
+        <v>7.81019746536988</v>
       </c>
       <c r="N22" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B22,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M22&lt;Assumptions!$C$6,"Order now",IF(K22&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O22" s="16">
         <f>IF(OR(SelCat="All",D22=SelCat),1,0)</f>
@@ -2944,39 +2944,39 @@
       </c>
       <c r="F23" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B23,Raw!$A$2:$A$51,0))</f>
-        <v>5.321</v>
+        <v>5.214</v>
       </c>
       <c r="G23" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B23,Raw!$A$2:$A$51,0))</f>
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="H23" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B23,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.37022306261719</v>
+        <v>6.796047753658</v>
       </c>
       <c r="I23" s="15">
         <f>MIN(F23*(Assumptions!$C$6+Assumptions!$C$7)+H23,F23*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B23,Raw!$A$2:$A$51,0))))</f>
-        <v>22.3332230626172</v>
+        <v>22.438047753658</v>
       </c>
       <c r="J23" s="15">
         <f>MIN(I23+F23*Assumptions!$C$7,F23*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B23,Raw!$A$2:$A$51,0))))</f>
-        <v>27.6542230626172</v>
+        <v>27.652047753658</v>
       </c>
       <c r="K23" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B23,Raw!$A$2:$A$51,0))=1,G23&gt;I23),0,ROUNDUP(MAX(0,J23-G23),0))</f>
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L23" s="17">
         <f>K23*INDEX(Raw!$I$2:$I$51,MATCH($B23,Raw!$A$2:$A$51,0))</f>
-        <v>72.8</v>
+        <v>0</v>
       </c>
       <c r="M23" s="15">
         <f>IFERROR(G23/F23,0)</f>
-        <v>3.94662657395227</v>
+        <v>9.58956655159187</v>
       </c>
       <c r="N23" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B23,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M23&lt;Assumptions!$C$6,"Order now",IF(K23&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O23" s="16">
         <f>IF(OR(SelCat="All",D23=SelCat),1,0)</f>
@@ -3003,23 +3003,23 @@
       </c>
       <c r="F24" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B24,Raw!$A$2:$A$51,0))</f>
-        <v>5.107</v>
+        <v>4.893</v>
       </c>
       <c r="G24" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B24,Raw!$A$2:$A$51,0))</f>
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="H24" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B24,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.27045646985112</v>
+        <v>6.5702749308914</v>
       </c>
       <c r="I24" s="15">
         <f>MIN(F24*(Assumptions!$C$6+Assumptions!$C$7)+H24,F24*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B24,Raw!$A$2:$A$51,0))))</f>
-        <v>22.5914564698511</v>
+        <v>21.2492749308914</v>
       </c>
       <c r="J24" s="15">
         <f>MIN(I24+F24*Assumptions!$C$7,F24*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B24,Raw!$A$2:$A$51,0))))</f>
-        <v>27.6984564698511</v>
+        <v>26.1422749308914</v>
       </c>
       <c r="K24" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B24,Raw!$A$2:$A$51,0))=1,G24&gt;I24),0,ROUNDUP(MAX(0,J24-G24),0))</f>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="M24" s="15">
         <f>IFERROR(G24/F24,0)</f>
-        <v>4.69943215194831</v>
+        <v>10.4230533415083</v>
       </c>
       <c r="N24" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B24,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M24&lt;Assumptions!$C$6,"Order now",IF(K24&gt;0,"Order","OK")))</f>
@@ -3062,39 +3062,39 @@
       </c>
       <c r="F25" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B25,Raw!$A$2:$A$51,0))</f>
-        <v>15.857</v>
+        <v>14.607</v>
       </c>
       <c r="G25" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B25,Raw!$A$2:$A$51,0))</f>
-        <v>49</v>
+        <v>145</v>
       </c>
       <c r="H25" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B25,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>14.1236619001589</v>
+        <v>11.7544762030258</v>
       </c>
       <c r="I25" s="15">
         <f>MIN(F25*(Assumptions!$C$6+Assumptions!$C$7)+H25,F25*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B25,Raw!$A$2:$A$51,0))))</f>
-        <v>61.6946619001589</v>
+        <v>55.5754762030258</v>
       </c>
       <c r="J25" s="15">
         <f>MIN(I25+F25*Assumptions!$C$7,F25*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B25,Raw!$A$2:$A$51,0))))</f>
-        <v>77.5516619001589</v>
+        <v>70.1824762030258</v>
       </c>
       <c r="K25" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B25,Raw!$A$2:$A$51,0))=1,G25&gt;I25),0,ROUNDUP(MAX(0,J25-G25),0))</f>
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="L25" s="17">
         <f>K25*INDEX(Raw!$I$2:$I$51,MATCH($B25,Raw!$A$2:$A$51,0))</f>
-        <v>102.95</v>
+        <v>0</v>
       </c>
       <c r="M25" s="15">
         <f>IFERROR(G25/F25,0)</f>
-        <v>3.09011792899035</v>
+        <v>9.92674744985281</v>
       </c>
       <c r="N25" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B25,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M25&lt;Assumptions!$C$6,"Order now",IF(K25&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O25" s="16">
         <f>IF(OR(SelCat="All",D25=SelCat),1,0)</f>
@@ -3121,39 +3121,39 @@
       </c>
       <c r="F26" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B26,Raw!$A$2:$A$51,0))</f>
-        <v>34.179</v>
+        <v>34.286</v>
       </c>
       <c r="G26" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B26,Raw!$A$2:$A$51,0))</f>
-        <v>135</v>
+        <v>344</v>
       </c>
       <c r="H26" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B26,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>41.0620749051969</v>
+        <v>38.3642325673276</v>
       </c>
       <c r="I26" s="15">
         <f>MIN(F26*(Assumptions!$C$6+Assumptions!$C$7)+H26,F26*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B26,Raw!$A$2:$A$51,0))))</f>
-        <v>143.599074905197</v>
+        <v>141.222232567328</v>
       </c>
       <c r="J26" s="15">
         <f>MIN(I26+F26*Assumptions!$C$7,F26*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B26,Raw!$A$2:$A$51,0))))</f>
-        <v>177.778074905197</v>
+        <v>175.508232567328</v>
       </c>
       <c r="K26" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B26,Raw!$A$2:$A$51,0))=1,G26&gt;I26),0,ROUNDUP(MAX(0,J26-G26),0))</f>
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="L26" s="17">
         <f>K26*INDEX(Raw!$I$2:$I$51,MATCH($B26,Raw!$A$2:$A$51,0))</f>
-        <v>152.65</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
         <f>IFERROR(G26/F26,0)</f>
-        <v>3.94979373299394</v>
+        <v>10.033249722919</v>
       </c>
       <c r="N26" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B26,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M26&lt;Assumptions!$C$6,"Order now",IF(K26&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O26" s="16">
         <f>IF(OR(SelCat="All",D26=SelCat),1,0)</f>
@@ -3180,39 +3180,39 @@
       </c>
       <c r="F27" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B27,Raw!$A$2:$A$51,0))</f>
-        <v>7.357</v>
+        <v>8.071</v>
       </c>
       <c r="G27" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B27,Raw!$A$2:$A$51,0))</f>
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="H27" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B27,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.70771269622188</v>
+        <v>12.0745591922645</v>
       </c>
       <c r="I27" s="15">
         <f>MIN(F27*(Assumptions!$C$6+Assumptions!$C$7)+H27,F27*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B27,Raw!$A$2:$A$51,0))))</f>
-        <v>29.7787126962219</v>
+        <v>36.2875591922645</v>
       </c>
       <c r="J27" s="15">
         <f>MIN(I27+F27*Assumptions!$C$7,F27*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B27,Raw!$A$2:$A$51,0))))</f>
-        <v>37.1357126962219</v>
+        <v>44.3585591922645</v>
       </c>
       <c r="K27" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B27,Raw!$A$2:$A$51,0))=1,G27&gt;I27),0,ROUNDUP(MAX(0,J27-G27),0))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L27" s="17">
         <f>K27*INDEX(Raw!$I$2:$I$51,MATCH($B27,Raw!$A$2:$A$51,0))</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="M27" s="15">
         <f>IFERROR(G27/F27,0)</f>
-        <v>3.80589914367269</v>
+        <v>7.43402304547144</v>
       </c>
       <c r="N27" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B27,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M27&lt;Assumptions!$C$6,"Order now",IF(K27&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O27" s="16">
         <f>IF(OR(SelCat="All",D27=SelCat),1,0)</f>
@@ -3239,23 +3239,23 @@
       </c>
       <c r="F28" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B28,Raw!$A$2:$A$51,0))</f>
-        <v>18.214</v>
+        <v>19.357</v>
       </c>
       <c r="G28" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B28,Raw!$A$2:$A$51,0))</f>
-        <v>51</v>
+        <v>147</v>
       </c>
       <c r="H28" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B28,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>12.7433040090669</v>
+        <v>15.4640094175961</v>
       </c>
       <c r="I28" s="15">
         <f>MIN(F28*(Assumptions!$C$6+Assumptions!$C$7)+H28,F28*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B28,Raw!$A$2:$A$51,0))))</f>
-        <v>36.428</v>
+        <v>38.714</v>
       </c>
       <c r="J28" s="15">
         <f>MIN(I28+F28*Assumptions!$C$7,F28*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B28,Raw!$A$2:$A$51,0))))</f>
-        <v>36.428</v>
+        <v>38.714</v>
       </c>
       <c r="K28" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B28,Raw!$A$2:$A$51,0))=1,G28&gt;I28),0,ROUNDUP(MAX(0,J28-G28),0))</f>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="M28" s="15">
         <f>IFERROR(G28/F28,0)</f>
-        <v>2.8000439222576</v>
+        <v>7.59415198636152</v>
       </c>
       <c r="N28" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B28,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M28&lt;Assumptions!$C$6,"Order now",IF(K28&gt;0,"Order","OK")))</f>
@@ -3298,23 +3298,23 @@
       </c>
       <c r="F29" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B29,Raw!$A$2:$A$51,0))</f>
-        <v>11.893</v>
+        <v>11</v>
       </c>
       <c r="G29" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B29,Raw!$A$2:$A$51,0))</f>
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="H29" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B29,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>11.1200259922133</v>
+        <v>13.7835737240927</v>
       </c>
       <c r="I29" s="15">
         <f>MIN(F29*(Assumptions!$C$6+Assumptions!$C$7)+H29,F29*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B29,Raw!$A$2:$A$51,0))))</f>
-        <v>23.786</v>
+        <v>22</v>
       </c>
       <c r="J29" s="15">
         <f>MIN(I29+F29*Assumptions!$C$7,F29*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B29,Raw!$A$2:$A$51,0))))</f>
-        <v>23.786</v>
+        <v>22</v>
       </c>
       <c r="K29" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B29,Raw!$A$2:$A$51,0))=1,G29&gt;I29),0,ROUNDUP(MAX(0,J29-G29),0))</f>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="M29" s="15">
         <f>IFERROR(G29/F29,0)</f>
-        <v>2.77474144454721</v>
+        <v>8.27272727272727</v>
       </c>
       <c r="N29" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B29,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M29&lt;Assumptions!$C$6,"Order now",IF(K29&gt;0,"Order","OK")))</f>
@@ -3357,39 +3357,39 @@
       </c>
       <c r="F30" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B30,Raw!$A$2:$A$51,0))</f>
-        <v>18.179</v>
+        <v>18.143</v>
       </c>
       <c r="G30" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B30,Raw!$A$2:$A$51,0))</f>
-        <v>27</v>
+        <v>129</v>
       </c>
       <c r="H30" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B30,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>12.4232210198282</v>
+        <v>18.136130800973</v>
       </c>
       <c r="I30" s="15">
         <f>MIN(F30*(Assumptions!$C$6+Assumptions!$C$7)+H30,F30*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B30,Raw!$A$2:$A$51,0))))</f>
-        <v>36.358</v>
+        <v>36.286</v>
       </c>
       <c r="J30" s="15">
         <f>MIN(I30+F30*Assumptions!$C$7,F30*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B30,Raw!$A$2:$A$51,0))))</f>
-        <v>36.358</v>
+        <v>36.286</v>
       </c>
       <c r="K30" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B30,Raw!$A$2:$A$51,0))=1,G30&gt;I30),0,ROUNDUP(MAX(0,J30-G30),0))</f>
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L30" s="17">
         <f>K30*INDEX(Raw!$I$2:$I$51,MATCH($B30,Raw!$A$2:$A$51,0))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="M30" s="15">
         <f>IFERROR(G30/F30,0)</f>
-        <v>1.48523021068266</v>
+        <v>7.1101802348013</v>
       </c>
       <c r="N30" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B30,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M30&lt;Assumptions!$C$6,"Order now",IF(K30&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O30" s="16">
         <f>IF(OR(SelCat="All",D30=SelCat),1,0)</f>
@@ -3416,23 +3416,23 @@
       </c>
       <c r="F31" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B31,Raw!$A$2:$A$51,0))</f>
-        <v>5.893</v>
+        <v>6.286</v>
       </c>
       <c r="G31" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B31,Raw!$A$2:$A$51,0))</f>
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="H31" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B31,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.02207991779563</v>
+        <v>7.53623966627256</v>
       </c>
       <c r="I31" s="15">
         <f>MIN(F31*(Assumptions!$C$6+Assumptions!$C$7)+H31,F31*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B31,Raw!$A$2:$A$51,0))))</f>
-        <v>11.786</v>
+        <v>12.572</v>
       </c>
       <c r="J31" s="15">
         <f>MIN(I31+F31*Assumptions!$C$7,F31*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B31,Raw!$A$2:$A$51,0))))</f>
-        <v>11.786</v>
+        <v>12.572</v>
       </c>
       <c r="K31" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B31,Raw!$A$2:$A$51,0))=1,G31&gt;I31),0,ROUNDUP(MAX(0,J31-G31),0))</f>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M31" s="15">
         <f>IFERROR(G31/F31,0)</f>
-        <v>3.56354997454607</v>
+        <v>8.11326757874642</v>
       </c>
       <c r="N31" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B31,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M31&lt;Assumptions!$C$6,"Order now",IF(K31&gt;0,"Order","OK")))</f>
@@ -3475,23 +3475,23 @@
       </c>
       <c r="F32" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B32,Raw!$A$2:$A$51,0))</f>
-        <v>10.857</v>
+        <v>9.214</v>
       </c>
       <c r="G32" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B32,Raw!$A$2:$A$51,0))</f>
-        <v>60</v>
+        <v>117</v>
       </c>
       <c r="H32" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B32,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>17.2301816260741</v>
+        <v>9.2138174759434</v>
       </c>
       <c r="I32" s="15">
         <f>MIN(F32*(Assumptions!$C$6+Assumptions!$C$7)+H32,F32*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B32,Raw!$A$2:$A$51,0))))</f>
-        <v>10.857</v>
+        <v>9.214</v>
       </c>
       <c r="J32" s="15">
         <f>MIN(I32+F32*Assumptions!$C$7,F32*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B32,Raw!$A$2:$A$51,0))))</f>
-        <v>10.857</v>
+        <v>9.214</v>
       </c>
       <c r="K32" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B32,Raw!$A$2:$A$51,0))=1,G32&gt;I32),0,ROUNDUP(MAX(0,J32-G32),0))</f>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="M32" s="15">
         <f>IFERROR(G32/F32,0)</f>
-        <v>5.52638850511191</v>
+        <v>12.6980681571522</v>
       </c>
       <c r="N32" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B32,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M32&lt;Assumptions!$C$6,"Order now",IF(K32&gt;0,"Order","OK")))</f>
@@ -3534,39 +3534,39 @@
       </c>
       <c r="F33" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B33,Raw!$A$2:$A$51,0))</f>
-        <v>4.75</v>
+        <v>4.464</v>
       </c>
       <c r="G33" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B33,Raw!$A$2:$A$51,0))</f>
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="H33" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B33,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>4.3039730517279</v>
+        <v>7.02182057642461</v>
       </c>
       <c r="I33" s="15">
         <f>MIN(F33*(Assumptions!$C$6+Assumptions!$C$7)+H33,F33*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B33,Raw!$A$2:$A$51,0))))</f>
-        <v>18.5539730517279</v>
+        <v>20.4138205764246</v>
       </c>
       <c r="J33" s="15">
         <f>MIN(I33+F33*Assumptions!$C$7,F33*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B33,Raw!$A$2:$A$51,0))))</f>
-        <v>23.3039730517279</v>
+        <v>24.8778205764246</v>
       </c>
       <c r="K33" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B33,Raw!$A$2:$A$51,0))=1,G33&gt;I33),0,ROUNDUP(MAX(0,J33-G33),0))</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L33" s="17">
         <f>K33*INDEX(Raw!$I$2:$I$51,MATCH($B33,Raw!$A$2:$A$51,0))</f>
-        <v>142</v>
+        <v>0</v>
       </c>
       <c r="M33" s="15">
         <f>IFERROR(G33/F33,0)</f>
-        <v>0.842105263157895</v>
+        <v>7.16845878136201</v>
       </c>
       <c r="N33" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B33,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M33&lt;Assumptions!$C$6,"Order now",IF(K33&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O33" s="16">
         <f>IF(OR(SelCat="All",D33=SelCat),1,0)</f>
@@ -3593,39 +3593,39 @@
       </c>
       <c r="F34" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B34,Raw!$A$2:$A$51,0))</f>
-        <v>5.214</v>
+        <v>5.964</v>
       </c>
       <c r="G34" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B34,Raw!$A$2:$A$51,0))</f>
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H34" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B34,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.02207991779563</v>
+        <v>9.60534756099434</v>
       </c>
       <c r="I34" s="15">
         <f>MIN(F34*(Assumptions!$C$6+Assumptions!$C$7)+H34,F34*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B34,Raw!$A$2:$A$51,0))))</f>
-        <v>23.6640799177956</v>
+        <v>27.4973475609944</v>
       </c>
       <c r="J34" s="15">
         <f>MIN(I34+F34*Assumptions!$C$7,F34*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B34,Raw!$A$2:$A$51,0))))</f>
-        <v>28.8780799177956</v>
+        <v>33.4613475609944</v>
       </c>
       <c r="K34" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B34,Raw!$A$2:$A$51,0))=1,G34&gt;I34),0,ROUNDUP(MAX(0,J34-G34),0))</f>
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="L34" s="17">
         <f>K34*INDEX(Raw!$I$2:$I$51,MATCH($B34,Raw!$A$2:$A$51,0))</f>
-        <v>56.4</v>
+        <v>0</v>
       </c>
       <c r="M34" s="15">
         <f>IFERROR(G34/F34,0)</f>
-        <v>3.26045262754124</v>
+        <v>7.71294433266264</v>
       </c>
       <c r="N34" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B34,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M34&lt;Assumptions!$C$6,"Order now",IF(K34&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O34" s="16">
         <f>IF(OR(SelCat="All",D34=SelCat),1,0)</f>
@@ -3652,23 +3652,23 @@
       </c>
       <c r="F35" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B35,Raw!$A$2:$A$51,0))</f>
-        <v>10.679</v>
+        <v>9.893</v>
       </c>
       <c r="G35" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B35,Raw!$A$2:$A$51,0))</f>
-        <v>47</v>
+        <v>102</v>
       </c>
       <c r="H35" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B35,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>10.1426297215022</v>
+        <v>11.3600882341424</v>
       </c>
       <c r="I35" s="15">
         <f>MIN(F35*(Assumptions!$C$6+Assumptions!$C$7)+H35,F35*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B35,Raw!$A$2:$A$51,0))))</f>
-        <v>42.1796297215022</v>
+        <v>41.0390882341424</v>
       </c>
       <c r="J35" s="15">
         <f>MIN(I35+F35*Assumptions!$C$7,F35*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B35,Raw!$A$2:$A$51,0))))</f>
-        <v>52.8586297215022</v>
+        <v>50.9320882341424</v>
       </c>
       <c r="K35" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B35,Raw!$A$2:$A$51,0))=1,G35&gt;I35),0,ROUNDUP(MAX(0,J35-G35),0))</f>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="M35" s="15">
         <f>IFERROR(G35/F35,0)</f>
-        <v>4.40116115741174</v>
+        <v>10.3103204285859</v>
       </c>
       <c r="N35" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B35,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M35&lt;Assumptions!$C$6,"Order now",IF(K35&gt;0,"Order","OK")))</f>
@@ -3711,23 +3711,23 @@
       </c>
       <c r="F36" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B36,Raw!$A$2:$A$51,0))</f>
-        <v>5.214</v>
+        <v>7.071</v>
       </c>
       <c r="G36" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B36,Raw!$A$2:$A$51,0))</f>
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="H36" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B36,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.2078423669074</v>
+        <v>8.93374486035951</v>
       </c>
       <c r="I36" s="15">
         <f>MIN(F36*(Assumptions!$C$6+Assumptions!$C$7)+H36,F36*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B36,Raw!$A$2:$A$51,0))))</f>
-        <v>23.8498423669074</v>
+        <v>30.1467448603595</v>
       </c>
       <c r="J36" s="15">
         <f>MIN(I36+F36*Assumptions!$C$7,F36*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B36,Raw!$A$2:$A$51,0))))</f>
-        <v>29.0638423669074</v>
+        <v>37.2177448603595</v>
       </c>
       <c r="K36" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B36,Raw!$A$2:$A$51,0))=1,G36&gt;I36),0,ROUNDUP(MAX(0,J36-G36),0))</f>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="M36" s="15">
         <f>IFERROR(G36/F36,0)</f>
-        <v>5.75373993095512</v>
+        <v>8.76820817423278</v>
       </c>
       <c r="N36" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B36,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M36&lt;Assumptions!$C$6,"Order now",IF(K36&gt;0,"Order","OK")))</f>
@@ -3770,39 +3770,39 @@
       </c>
       <c r="F37" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B37,Raw!$A$2:$A$51,0))</f>
-        <v>6.143</v>
+        <v>5.786</v>
       </c>
       <c r="G37" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B37,Raw!$A$2:$A$51,0))</f>
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="H37" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B37,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.03039422792207</v>
+        <v>9.14808614779616</v>
       </c>
       <c r="I37" s="15">
         <f>MIN(F37*(Assumptions!$C$6+Assumptions!$C$7)+H37,F37*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B37,Raw!$A$2:$A$51,0))))</f>
-        <v>25.4593942279221</v>
+        <v>26.5060861477962</v>
       </c>
       <c r="J37" s="15">
         <f>MIN(I37+F37*Assumptions!$C$7,F37*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B37,Raw!$A$2:$A$51,0))))</f>
-        <v>31.6023942279221</v>
+        <v>32.2920861477962</v>
       </c>
       <c r="K37" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B37,Raw!$A$2:$A$51,0))=1,G37&gt;I37),0,ROUNDUP(MAX(0,J37-G37),0))</f>
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L37" s="17">
         <f>K37*INDEX(Raw!$I$2:$I$51,MATCH($B37,Raw!$A$2:$A$51,0))</f>
-        <v>41.8</v>
+        <v>0</v>
       </c>
       <c r="M37" s="15">
         <f>IFERROR(G37/F37,0)</f>
-        <v>1.62786911932281</v>
+        <v>6.91323885240235</v>
       </c>
       <c r="N37" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B37,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M37&lt;Assumptions!$C$6,"Order now",IF(K37&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O37" s="16">
         <f>IF(OR(SelCat="All",D37=SelCat),1,0)</f>
@@ -3829,39 +3829,39 @@
       </c>
       <c r="F38" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B38,Raw!$A$2:$A$51,0))</f>
-        <v>3.357</v>
+        <v>3.643</v>
       </c>
       <c r="G38" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B38,Raw!$A$2:$A$51,0))</f>
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H38" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B38,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>5.05273861583993</v>
+        <v>6.13587658835313</v>
       </c>
       <c r="I38" s="15">
         <f>MIN(F38*(Assumptions!$C$6+Assumptions!$C$7)+H38,F38*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B38,Raw!$A$2:$A$51,0))))</f>
-        <v>15.1237386158399</v>
+        <v>17.0648765883531</v>
       </c>
       <c r="J38" s="15">
         <f>MIN(I38+F38*Assumptions!$C$7,F38*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B38,Raw!$A$2:$A$51,0))))</f>
-        <v>18.4807386158399</v>
+        <v>20.7078765883531</v>
       </c>
       <c r="K38" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B38,Raw!$A$2:$A$51,0))=1,G38&gt;I38),0,ROUNDUP(MAX(0,J38-G38),0))</f>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="L38" s="17">
         <f>K38*INDEX(Raw!$I$2:$I$51,MATCH($B38,Raw!$A$2:$A$51,0))</f>
-        <v>106.4</v>
+        <v>0</v>
       </c>
       <c r="M38" s="15">
         <f>IFERROR(G38/F38,0)</f>
-        <v>1.48942508191838</v>
+        <v>7.68597309909415</v>
       </c>
       <c r="N38" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B38,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M38&lt;Assumptions!$C$6,"Order now",IF(K38&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O38" s="16">
         <f>IF(OR(SelCat="All",D38=SelCat),1,0)</f>
@@ -3888,39 +3888,39 @@
       </c>
       <c r="F39" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B39,Raw!$A$2:$A$51,0))</f>
-        <v>9.464</v>
+        <v>9.393</v>
       </c>
       <c r="G39" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B39,Raw!$A$2:$A$51,0))</f>
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="H39" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B39,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.0033714378233</v>
+        <v>10.2112189334819</v>
       </c>
       <c r="I39" s="15">
         <f>MIN(F39*(Assumptions!$C$6+Assumptions!$C$7)+H39,F39*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B39,Raw!$A$2:$A$51,0))))</f>
-        <v>41.3953714378234</v>
+        <v>38.3902189334819</v>
       </c>
       <c r="J39" s="15">
         <f>MIN(I39+F39*Assumptions!$C$7,F39*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B39,Raw!$A$2:$A$51,0))))</f>
-        <v>50.8593714378234</v>
+        <v>47.7832189334819</v>
       </c>
       <c r="K39" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B39,Raw!$A$2:$A$51,0))=1,G39&gt;I39),0,ROUNDUP(MAX(0,J39-G39),0))</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L39" s="17">
         <f>K39*INDEX(Raw!$I$2:$I$51,MATCH($B39,Raw!$A$2:$A$51,0))</f>
-        <v>106.6</v>
+        <v>0</v>
       </c>
       <c r="M39" s="15">
         <f>IFERROR(G39/F39,0)</f>
-        <v>4.01521555367709</v>
+        <v>8.19759395294368</v>
       </c>
       <c r="N39" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B39,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M39&lt;Assumptions!$C$6,"Order now",IF(K39&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O39" s="16">
         <f>IF(OR(SelCat="All",D39=SelCat),1,0)</f>
@@ -3947,39 +3947,39 @@
       </c>
       <c r="F40" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B40,Raw!$A$2:$A$51,0))</f>
-        <v>14.036</v>
+        <v>11.857</v>
       </c>
       <c r="G40" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B40,Raw!$A$2:$A$51,0))</f>
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="H40" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B40,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>12.5289627216302</v>
+        <v>12.4860944641429</v>
       </c>
       <c r="I40" s="15">
         <f>MIN(F40*(Assumptions!$C$6+Assumptions!$C$7)+H40,F40*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B40,Raw!$A$2:$A$51,0))))</f>
-        <v>54.6369627216302</v>
+        <v>48.0570944641429</v>
       </c>
       <c r="J40" s="15">
         <f>MIN(I40+F40*Assumptions!$C$7,F40*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B40,Raw!$A$2:$A$51,0))))</f>
-        <v>68.6729627216302</v>
+        <v>59.9140944641429</v>
       </c>
       <c r="K40" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B40,Raw!$A$2:$A$51,0))=1,G40&gt;I40),0,ROUNDUP(MAX(0,J40-G40),0))</f>
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="L40" s="17">
         <f>K40*INDEX(Raw!$I$2:$I$51,MATCH($B40,Raw!$A$2:$A$51,0))</f>
-        <v>114.4</v>
+        <v>0</v>
       </c>
       <c r="M40" s="15">
         <f>IFERROR(G40/F40,0)</f>
-        <v>1.78113422627529</v>
+        <v>7.50611453150038</v>
       </c>
       <c r="N40" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B40,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M40&lt;Assumptions!$C$6,"Order now",IF(K40&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O40" s="16">
         <f>IF(OR(SelCat="All",D40=SelCat),1,0)</f>
@@ -4006,39 +4006,39 @@
       </c>
       <c r="F41" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B41,Raw!$A$2:$A$51,0))</f>
-        <v>6.929</v>
+        <v>6.714</v>
       </c>
       <c r="G41" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B41,Raw!$A$2:$A$51,0))</f>
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H41" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B41,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>10.9971369874163</v>
+        <v>8.69082473459798</v>
       </c>
       <c r="I41" s="15">
         <f>MIN(F41*(Assumptions!$C$6+Assumptions!$C$7)+H41,F41*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B41,Raw!$A$2:$A$51,0))))</f>
-        <v>31.7841369874163</v>
+        <v>28.832824734598</v>
       </c>
       <c r="J41" s="15">
         <f>MIN(I41+F41*Assumptions!$C$7,F41*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B41,Raw!$A$2:$A$51,0))))</f>
-        <v>38.7131369874163</v>
+        <v>35.546824734598</v>
       </c>
       <c r="K41" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B41,Raw!$A$2:$A$51,0))=1,G41&gt;I41),0,ROUNDUP(MAX(0,J41-G41),0))</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L41" s="17">
         <f>K41*INDEX(Raw!$I$2:$I$51,MATCH($B41,Raw!$A$2:$A$51,0))</f>
-        <v>31.2</v>
+        <v>0</v>
       </c>
       <c r="M41" s="15">
         <f>IFERROR(G41/F41,0)</f>
-        <v>2.16481454755376</v>
+        <v>7.14924039320822</v>
       </c>
       <c r="N41" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B41,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M41&lt;Assumptions!$C$6,"Order now",IF(K41&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O41" s="16">
         <f>IF(OR(SelCat="All",D41=SelCat),1,0)</f>
@@ -4065,23 +4065,23 @@
       </c>
       <c r="F42" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B42,Raw!$A$2:$A$51,0))</f>
-        <v>2.857</v>
+        <v>2.679</v>
       </c>
       <c r="G42" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B42,Raw!$A$2:$A$51,0))</f>
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="H42" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B42,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.03039422792207</v>
+        <v>6.82748447581538</v>
       </c>
       <c r="I42" s="15">
         <f>MIN(F42*(Assumptions!$C$6+Assumptions!$C$7)+H42,F42*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B42,Raw!$A$2:$A$51,0))))</f>
-        <v>15.6013942279221</v>
+        <v>14.8644844758154</v>
       </c>
       <c r="J42" s="15">
         <f>MIN(I42+F42*Assumptions!$C$7,F42*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B42,Raw!$A$2:$A$51,0))))</f>
-        <v>18.4583942279221</v>
+        <v>17.5434844758154</v>
       </c>
       <c r="K42" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B42,Raw!$A$2:$A$51,0))=1,G42&gt;I42),0,ROUNDUP(MAX(0,J42-G42),0))</f>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M42" s="15">
         <f>IFERROR(G42/F42,0)</f>
-        <v>6.65033251662583</v>
+        <v>12.3180291153415</v>
       </c>
       <c r="N42" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B42,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M42&lt;Assumptions!$C$6,"Order now",IF(K42&gt;0,"Order","OK")))</f>
@@ -4124,23 +4124,23 @@
       </c>
       <c r="F43" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B43,Raw!$A$2:$A$51,0))</f>
-        <v>5.286</v>
+        <v>5</v>
       </c>
       <c r="G43" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B43,Raw!$A$2:$A$51,0))</f>
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="H43" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B43,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.16471476804904</v>
+        <v>7.29617742434352</v>
       </c>
       <c r="I43" s="15">
         <f>MIN(F43*(Assumptions!$C$6+Assumptions!$C$7)+H43,F43*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B43,Raw!$A$2:$A$51,0))))</f>
-        <v>23.022714768049</v>
+        <v>22.2961774243435</v>
       </c>
       <c r="J43" s="15">
         <f>MIN(I43+F43*Assumptions!$C$7,F43*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B43,Raw!$A$2:$A$51,0))))</f>
-        <v>28.308714768049</v>
+        <v>27.2961774243435</v>
       </c>
       <c r="K43" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B43,Raw!$A$2:$A$51,0))=1,G43&gt;I43),0,ROUNDUP(MAX(0,J43-G43),0))</f>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="M43" s="15">
         <f>IFERROR(G43/F43,0)</f>
-        <v>1.70261066969353</v>
+        <v>5.6</v>
       </c>
       <c r="N43" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B43,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M43&lt;Assumptions!$C$6,"Order now",IF(K43&gt;0,"Order","OK")))</f>
@@ -4183,39 +4183,39 @@
       </c>
       <c r="F44" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B44,Raw!$A$2:$A$51,0))</f>
-        <v>2.786</v>
+        <v>2.893</v>
       </c>
       <c r="G44" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B44,Raw!$A$2:$A$51,0))</f>
-        <v>1</v>
+        <v>31</v>
       </c>
       <c r="H44" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B44,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.38451248177964</v>
+        <v>4.3554149607127</v>
       </c>
       <c r="I44" s="15">
         <f>MIN(F44*(Assumptions!$C$6+Assumptions!$C$7)+H44,F44*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B44,Raw!$A$2:$A$51,0))))</f>
-        <v>14.7425124817796</v>
+        <v>13.0344149607127</v>
       </c>
       <c r="J44" s="15">
         <f>MIN(I44+F44*Assumptions!$C$7,F44*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B44,Raw!$A$2:$A$51,0))))</f>
-        <v>17.5285124817796</v>
+        <v>15.9274149607127</v>
       </c>
       <c r="K44" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B44,Raw!$A$2:$A$51,0))=1,G44&gt;I44),0,ROUNDUP(MAX(0,J44-G44),0))</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L44" s="17">
         <f>K44*INDEX(Raw!$I$2:$I$51,MATCH($B44,Raw!$A$2:$A$51,0))</f>
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="M44" s="15">
         <f>IFERROR(G44/F44,0)</f>
-        <v>0.358937544867193</v>
+        <v>10.7155202212236</v>
       </c>
       <c r="N44" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B44,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M44&lt;Assumptions!$C$6,"Order now",IF(K44&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O44" s="16">
         <f>IF(OR(SelCat="All",D44=SelCat),1,0)</f>
@@ -4242,39 +4242,39 @@
       </c>
       <c r="F45" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B45,Raw!$A$2:$A$51,0))</f>
-        <v>4.607</v>
+        <v>5.357</v>
       </c>
       <c r="G45" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B45,Raw!$A$2:$A$51,0))</f>
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="H45" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B45,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.27045646985112</v>
+        <v>8.6336670579482</v>
       </c>
       <c r="I45" s="15">
         <f>MIN(F45*(Assumptions!$C$6+Assumptions!$C$7)+H45,F45*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B45,Raw!$A$2:$A$51,0))))</f>
-        <v>21.0914564698511</v>
+        <v>24.7046670579482</v>
       </c>
       <c r="J45" s="15">
         <f>MIN(I45+F45*Assumptions!$C$7,F45*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B45,Raw!$A$2:$A$51,0))))</f>
-        <v>25.6984564698511</v>
+        <v>30.0616670579482</v>
       </c>
       <c r="K45" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B45,Raw!$A$2:$A$51,0))=1,G45&gt;I45),0,ROUNDUP(MAX(0,J45-G45),0))</f>
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="L45" s="17">
         <f>K45*INDEX(Raw!$I$2:$I$51,MATCH($B45,Raw!$A$2:$A$51,0))</f>
-        <v>28.8</v>
+        <v>0</v>
       </c>
       <c r="M45" s="15">
         <f>IFERROR(G45/F45,0)</f>
-        <v>1.73648795311483</v>
+        <v>7.09352249393317</v>
       </c>
       <c r="N45" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B45,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M45&lt;Assumptions!$C$6,"Order now",IF(K45&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O45" s="16">
         <f>IF(OR(SelCat="All",D45=SelCat),1,0)</f>
@@ -4301,39 +4301,39 @@
       </c>
       <c r="F46" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B46,Raw!$A$2:$A$51,0))</f>
-        <v>2.321</v>
+        <v>1.714</v>
       </c>
       <c r="G46" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B46,Raw!$A$2:$A$51,0))</f>
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="H46" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B46,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>4.12106848644863</v>
+        <v>3.55234960378339</v>
       </c>
       <c r="I46" s="15">
         <f>MIN(F46*(Assumptions!$C$6+Assumptions!$C$7)+H46,F46*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B46,Raw!$A$2:$A$51,0))))</f>
-        <v>11.0840684864486</v>
+        <v>8.69434960378339</v>
       </c>
       <c r="J46" s="15">
         <f>MIN(I46+F46*Assumptions!$C$7,F46*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B46,Raw!$A$2:$A$51,0))))</f>
-        <v>13.4050684864486</v>
+        <v>10.4083496037834</v>
       </c>
       <c r="K46" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B46,Raw!$A$2:$A$51,0))=1,G46&gt;I46),0,ROUNDUP(MAX(0,J46-G46),0))</f>
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L46" s="17">
         <f>K46*INDEX(Raw!$I$2:$I$51,MATCH($B46,Raw!$A$2:$A$51,0))</f>
-        <v>90.2</v>
+        <v>0</v>
       </c>
       <c r="M46" s="15">
         <f>IFERROR(G46/F46,0)</f>
-        <v>1.292546316243</v>
+        <v>9.91831971995333</v>
       </c>
       <c r="N46" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B46,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M46&lt;Assumptions!$C$6,"Order now",IF(K46&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O46" s="16">
         <f>IF(OR(SelCat="All",D46=SelCat),1,0)</f>
@@ -4360,39 +4360,39 @@
       </c>
       <c r="F47" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B47,Raw!$A$2:$A$51,0))</f>
-        <v>3.214</v>
+        <v>2.107</v>
       </c>
       <c r="G47" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B47,Raw!$A$2:$A$51,0))</f>
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="H47" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B47,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>5.18134338830192</v>
+        <v>3.91530085050945</v>
       </c>
       <c r="I47" s="15">
         <f>MIN(F47*(Assumptions!$C$6+Assumptions!$C$7)+H47,F47*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B47,Raw!$A$2:$A$51,0))))</f>
-        <v>14.8233433883019</v>
+        <v>10.2363008505094</v>
       </c>
       <c r="J47" s="15">
         <f>MIN(I47+F47*Assumptions!$C$7,F47*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B47,Raw!$A$2:$A$51,0))))</f>
-        <v>18.0373433883019</v>
+        <v>12.3433008505094</v>
       </c>
       <c r="K47" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B47,Raw!$A$2:$A$51,0))=1,G47&gt;I47),0,ROUNDUP(MAX(0,J47-G47),0))</f>
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L47" s="17">
         <f>K47*INDEX(Raw!$I$2:$I$51,MATCH($B47,Raw!$A$2:$A$51,0))</f>
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="M47" s="15">
         <f>IFERROR(G47/F47,0)</f>
-        <v>4.35594275046671</v>
+        <v>10.9159943046986</v>
       </c>
       <c r="N47" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B47,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M47&lt;Assumptions!$C$6,"Order now",IF(K47&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O47" s="16">
         <f>IF(OR(SelCat="All",D47=SelCat),1,0)</f>
@@ -4419,39 +4419,39 @@
       </c>
       <c r="F48" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B48,Raw!$A$2:$A$51,0))</f>
-        <v>1.286</v>
+        <v>0.643</v>
       </c>
       <c r="G48" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B48,Raw!$A$2:$A$51,0))</f>
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H48" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B48,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>3.95531122416429</v>
+        <v>2.7178475246967</v>
       </c>
       <c r="I48" s="15">
         <f>MIN(F48*(Assumptions!$C$6+Assumptions!$C$7)+H48,F48*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B48,Raw!$A$2:$A$51,0))))</f>
-        <v>7.81331122416429</v>
+        <v>4.6468475246967</v>
       </c>
       <c r="J48" s="15">
         <f>MIN(I48+F48*Assumptions!$C$7,F48*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B48,Raw!$A$2:$A$51,0))))</f>
-        <v>9.09931122416429</v>
+        <v>5.2898475246967</v>
       </c>
       <c r="K48" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B48,Raw!$A$2:$A$51,0))=1,G48&gt;I48),0,ROUNDUP(MAX(0,J48-G48),0))</f>
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L48" s="17">
         <f>K48*INDEX(Raw!$I$2:$I$51,MATCH($B48,Raw!$A$2:$A$51,0))</f>
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="M48" s="15">
         <f>IFERROR(G48/F48,0)</f>
-        <v>3.1104199066874</v>
+        <v>13.9968895800933</v>
       </c>
       <c r="N48" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B48,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M48&lt;Assumptions!$C$6,"Order now",IF(K48&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O48" s="16">
         <f>IF(OR(SelCat="All",D48=SelCat),1,0)</f>
@@ -4478,39 +4478,39 @@
       </c>
       <c r="F49" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B49,Raw!$A$2:$A$51,0))</f>
-        <v>5.536</v>
+        <v>5.5</v>
       </c>
       <c r="G49" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B49,Raw!$A$2:$A$51,0))</f>
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="H49" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B49,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.43907161596795</v>
+        <v>6.89035792013013</v>
       </c>
       <c r="I49" s="15">
         <f>MIN(F49*(Assumptions!$C$6+Assumptions!$C$7)+H49,F49*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B49,Raw!$A$2:$A$51,0))))</f>
-        <v>24.0470716159679</v>
+        <v>23.3903579201301</v>
       </c>
       <c r="J49" s="15">
         <f>MIN(I49+F49*Assumptions!$C$7,F49*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B49,Raw!$A$2:$A$51,0))))</f>
-        <v>29.5830716159679</v>
+        <v>28.8903579201301</v>
       </c>
       <c r="K49" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B49,Raw!$A$2:$A$51,0))=1,G49&gt;I49),0,ROUNDUP(MAX(0,J49-G49),0))</f>
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="L49" s="17">
         <f>K49*INDEX(Raw!$I$2:$I$51,MATCH($B49,Raw!$A$2:$A$51,0))</f>
-        <v>76.7</v>
+        <v>0</v>
       </c>
       <c r="M49" s="15">
         <f>IFERROR(G49/F49,0)</f>
-        <v>3.07080924855491</v>
+        <v>8.54545454545455</v>
       </c>
       <c r="N49" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B49,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M49&lt;Assumptions!$C$6,"Order now",IF(K49&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O49" s="16">
         <f>IF(OR(SelCat="All",D49=SelCat),1,0)</f>
@@ -4537,23 +4537,23 @@
       </c>
       <c r="F50" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B50,Raw!$A$2:$A$51,0))</f>
-        <v>7.107</v>
+        <v>8.071</v>
       </c>
       <c r="G50" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B50,Raw!$A$2:$A$51,0))</f>
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="H50" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B50,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.22758821236379</v>
+        <v>9.89685171190819</v>
       </c>
       <c r="I50" s="15">
         <f>MIN(F50*(Assumptions!$C$6+Assumptions!$C$7)+H50,F50*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B50,Raw!$A$2:$A$51,0))))</f>
-        <v>28.5485882123638</v>
+        <v>34.1098517119082</v>
       </c>
       <c r="J50" s="15">
         <f>MIN(I50+F50*Assumptions!$C$7,F50*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B50,Raw!$A$2:$A$51,0))))</f>
-        <v>35.535</v>
+        <v>40.355</v>
       </c>
       <c r="K50" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B50,Raw!$A$2:$A$51,0))=1,G50&gt;I50),0,ROUNDUP(MAX(0,J50-G50),0))</f>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="M50" s="15">
         <f>IFERROR(G50/F50,0)</f>
-        <v>4.64330941325454</v>
+        <v>8.54912650229216</v>
       </c>
       <c r="N50" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B50,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M50&lt;Assumptions!$C$6,"Order now",IF(K50&gt;0,"Order","OK")))</f>
@@ -4596,23 +4596,23 @@
       </c>
       <c r="F51" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B51,Raw!$A$2:$A$51,0))</f>
-        <v>32.429</v>
+        <v>31.607</v>
       </c>
       <c r="G51" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B51,Raw!$A$2:$A$51,0))</f>
-        <v>121</v>
+        <v>270</v>
       </c>
       <c r="H51" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B51,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>22.920228336559</v>
+        <v>18.9477698093997</v>
       </c>
       <c r="I51" s="15">
         <f>MIN(F51*(Assumptions!$C$6+Assumptions!$C$7)+H51,F51*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B51,Raw!$A$2:$A$51,0))))</f>
-        <v>120.207228336559</v>
+        <v>113.7687698094</v>
       </c>
       <c r="J51" s="15">
         <f>MIN(I51+F51*Assumptions!$C$7,F51*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B51,Raw!$A$2:$A$51,0))))</f>
-        <v>152.636228336559</v>
+        <v>145.3757698094</v>
       </c>
       <c r="K51" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B51,Raw!$A$2:$A$51,0))=1,G51&gt;I51),0,ROUNDUP(MAX(0,J51-G51),0))</f>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M51" s="15">
         <f>IFERROR(G51/F51,0)</f>
-        <v>3.73122822165346</v>
+        <v>8.54241149112538</v>
       </c>
       <c r="N51" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B51,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M51&lt;Assumptions!$C$6,"Order now",IF(K51&gt;0,"Order","OK")))</f>
@@ -4655,23 +4655,23 @@
       </c>
       <c r="F52" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B52,Raw!$A$2:$A$51,0))</f>
-        <v>3.929</v>
+        <v>4.5</v>
       </c>
       <c r="G52" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B52,Raw!$A$2:$A$51,0))</f>
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H52" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B52,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>5.8157935991144</v>
+        <v>7.91348033216107</v>
       </c>
       <c r="I52" s="15">
         <f>MIN(F52*(Assumptions!$C$6+Assumptions!$C$7)+H52,F52*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B52,Raw!$A$2:$A$51,0))))</f>
-        <v>17.6027935991144</v>
+        <v>21.4134803321611</v>
       </c>
       <c r="J52" s="15">
         <f>MIN(I52+F52*Assumptions!$C$7,F52*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B52,Raw!$A$2:$A$51,0))))</f>
-        <v>21.5317935991144</v>
+        <v>25.9134803321611</v>
       </c>
       <c r="K52" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B52,Raw!$A$2:$A$51,0))=1,G52&gt;I52),0,ROUNDUP(MAX(0,J52-G52),0))</f>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="M52" s="15">
         <f>IFERROR(G52/F52,0)</f>
-        <v>8.14456604734029</v>
+        <v>10.6666666666667</v>
       </c>
       <c r="N52" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B52,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M52&lt;Assumptions!$C$6,"Order now",IF(K52&gt;0,"Order","OK")))</f>
@@ -4714,39 +4714,39 @@
       </c>
       <c r="F53" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B53,Raw!$A$2:$A$51,0))</f>
-        <v>17.357</v>
+        <v>15.821</v>
       </c>
       <c r="G53" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B53,Raw!$A$2:$A$51,0))</f>
-        <v>6</v>
+        <v>106</v>
       </c>
       <c r="H53" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B53,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>17.0815716667846</v>
+        <v>13.6749741384582</v>
       </c>
       <c r="I53" s="15">
         <f>MIN(F53*(Assumptions!$C$6+Assumptions!$C$7)+H53,F53*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B53,Raw!$A$2:$A$51,0))))</f>
-        <v>69.1525716667846</v>
+        <v>61.1379741384582</v>
       </c>
       <c r="J53" s="15">
         <f>MIN(I53+F53*Assumptions!$C$7,F53*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B53,Raw!$A$2:$A$51,0))))</f>
-        <v>86.5095716667846</v>
+        <v>76.9589741384582</v>
       </c>
       <c r="K53" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B53,Raw!$A$2:$A$51,0))=1,G53&gt;I53),0,ROUNDUP(MAX(0,J53-G53),0))</f>
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="L53" s="17">
         <f>K53*INDEX(Raw!$I$2:$I$51,MATCH($B53,Raw!$A$2:$A$51,0))</f>
-        <v>259.2</v>
+        <v>0</v>
       </c>
       <c r="M53" s="15">
         <f>IFERROR(G53/F53,0)</f>
-        <v>0.345681857463847</v>
+        <v>6.69995575500917</v>
       </c>
       <c r="N53" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B53,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M53&lt;Assumptions!$C$6,"Order now",IF(K53&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O53" s="16">
         <f>IF(OR(SelCat="All",D53=SelCat),1,0)</f>
@@ -4773,39 +4773,39 @@
       </c>
       <c r="F54" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B54,Raw!$A$2:$A$51,0))</f>
-        <v>8.821</v>
+        <v>9.143</v>
       </c>
       <c r="G54" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B54,Raw!$A$2:$A$51,0))</f>
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="H54" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B54,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.52220958848115</v>
+        <v>9.22810689510584</v>
       </c>
       <c r="I54" s="15">
         <f>MIN(F54*(Assumptions!$C$6+Assumptions!$C$7)+H54,F54*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B54,Raw!$A$2:$A$51,0))))</f>
-        <v>34.9852095884812</v>
+        <v>36.6571068951058</v>
       </c>
       <c r="J54" s="15">
         <f>MIN(I54+F54*Assumptions!$C$7,F54*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B54,Raw!$A$2:$A$51,0))))</f>
-        <v>43.8062095884811</v>
+        <v>45.8001068951058</v>
       </c>
       <c r="K54" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B54,Raw!$A$2:$A$51,0))=1,G54&gt;I54),0,ROUNDUP(MAX(0,J54-G54),0))</f>
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="L54" s="17">
         <f>K54*INDEX(Raw!$I$2:$I$51,MATCH($B54,Raw!$A$2:$A$51,0))</f>
-        <v>40.8</v>
+        <v>0</v>
       </c>
       <c r="M54" s="15">
         <f>IFERROR(G54/F54,0)</f>
-        <v>3.06087745153611</v>
+        <v>8.09362353713223</v>
       </c>
       <c r="N54" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B54,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M54&lt;Assumptions!$C$6,"Order now",IF(K54&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O54" s="16">
         <f>IF(OR(SelCat="All",D54=SelCat),1,0)</f>
@@ -4832,39 +4832,39 @@
       </c>
       <c r="F55" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B55,Raw!$A$2:$A$51,0))</f>
-        <v>10.75</v>
+        <v>10.107</v>
       </c>
       <c r="G55" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B55,Raw!$A$2:$A$51,0))</f>
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="H55" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B55,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>14.229403601961</v>
+        <v>10.954268729929</v>
       </c>
       <c r="I55" s="15">
         <f>MIN(F55*(Assumptions!$C$6+Assumptions!$C$7)+H55,F55*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B55,Raw!$A$2:$A$51,0))))</f>
-        <v>46.479403601961</v>
+        <v>41.275268729929</v>
       </c>
       <c r="J55" s="15">
         <f>MIN(I55+F55*Assumptions!$C$7,F55*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B55,Raw!$A$2:$A$51,0))))</f>
-        <v>57.229403601961</v>
+        <v>51.382268729929</v>
       </c>
       <c r="K55" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B55,Raw!$A$2:$A$51,0))=1,G55&gt;I55),0,ROUNDUP(MAX(0,J55-G55),0))</f>
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="L55" s="17">
         <f>K55*INDEX(Raw!$I$2:$I$51,MATCH($B55,Raw!$A$2:$A$51,0))</f>
-        <v>64.6</v>
+        <v>0</v>
       </c>
       <c r="M55" s="15">
         <f>IFERROR(G55/F55,0)</f>
-        <v>1.86046511627907</v>
+        <v>8.21213020678738</v>
       </c>
       <c r="N55" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B55,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M55&lt;Assumptions!$C$6,"Order now",IF(K55&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O55" s="16">
         <f>IF(OR(SelCat="All",D55=SelCat),1,0)</f>
@@ -4891,39 +4891,39 @@
       </c>
       <c r="F56" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B56,Raw!$A$2:$A$51,0))</f>
-        <v>10.357</v>
+        <v>9.357</v>
       </c>
       <c r="G56" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B56,Raw!$A$2:$A$51,0))</f>
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="H56" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B56,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>11.1143102245483</v>
+        <v>9.99687764604529</v>
       </c>
       <c r="I56" s="15">
         <f>MIN(F56*(Assumptions!$C$6+Assumptions!$C$7)+H56,F56*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B56,Raw!$A$2:$A$51,0))))</f>
-        <v>42.1853102245483</v>
+        <v>38.0678776460453</v>
       </c>
       <c r="J56" s="15">
         <f>MIN(I56+F56*Assumptions!$C$7,F56*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B56,Raw!$A$2:$A$51,0))))</f>
-        <v>52.5423102245483</v>
+        <v>47.4248776460453</v>
       </c>
       <c r="K56" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B56,Raw!$A$2:$A$51,0))=1,G56&gt;I56),0,ROUNDUP(MAX(0,J56-G56),0))</f>
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="L56" s="17">
         <f>K56*INDEX(Raw!$I$2:$I$51,MATCH($B56,Raw!$A$2:$A$51,0))</f>
-        <v>96.2</v>
+        <v>0</v>
       </c>
       <c r="M56" s="15">
         <f>IFERROR(G56/F56,0)</f>
-        <v>1.54484889446751</v>
+        <v>7.90851768729294</v>
       </c>
       <c r="N56" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B56,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M56&lt;Assumptions!$C$6,"Order now",IF(K56&gt;0,"Order","OK")))</f>
-        <v>Order now</v>
+        <v>OK</v>
       </c>
       <c r="O56" s="16">
         <f>IF(OR(SelCat="All",D56=SelCat),1,0)</f>
@@ -4950,39 +4950,39 @@
       </c>
       <c r="F57" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B57,Raw!$A$2:$A$51,0))</f>
-        <v>21.321</v>
+        <v>20.679</v>
       </c>
       <c r="G57" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B57,Raw!$A$2:$A$51,0))</f>
-        <v>57</v>
+        <v>170</v>
       </c>
       <c r="H57" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B57,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>18.5533818405163</v>
+        <v>19.1964057028262</v>
       </c>
       <c r="I57" s="15">
         <f>MIN(F57*(Assumptions!$C$6+Assumptions!$C$7)+H57,F57*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B57,Raw!$A$2:$A$51,0))))</f>
-        <v>82.5163818405163</v>
+        <v>81.2334057028262</v>
       </c>
       <c r="J57" s="15">
         <f>MIN(I57+F57*Assumptions!$C$7,F57*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B57,Raw!$A$2:$A$51,0))))</f>
-        <v>103.837381840516</v>
+        <v>101.912405702826</v>
       </c>
       <c r="K57" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B57,Raw!$A$2:$A$51,0))=1,G57&gt;I57),0,ROUNDUP(MAX(0,J57-G57),0))</f>
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="L57" s="17">
         <f>K57*INDEX(Raw!$I$2:$I$51,MATCH($B57,Raw!$A$2:$A$51,0))</f>
-        <v>98.7</v>
+        <v>0</v>
       </c>
       <c r="M57" s="15">
         <f>IFERROR(G57/F57,0)</f>
-        <v>2.67342057126776</v>
+        <v>8.22090043038832</v>
       </c>
       <c r="N57" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B57,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M57&lt;Assumptions!$C$6,"Order now",IF(K57&gt;0,"Order","OK")))</f>
-        <v>Order</v>
+        <v>OK</v>
       </c>
       <c r="O57" s="16">
         <f>IF(OR(SelCat="All",D57=SelCat),1,0)</f>
@@ -5001,18 +5001,18 @@
       <c r="F58" s="20" t="n"/>
       <c r="G58" s="21">
         <f>SUM(G8:G57)</f>
-        <v>1491</v>
+        <v>4212</v>
       </c>
       <c r="H58" s="20" t="n"/>
       <c r="I58" s="20" t="n"/>
       <c r="J58" s="20" t="n"/>
       <c r="K58" s="21">
         <f>SUM(K8:K57)</f>
-        <v>844</v>
+        <v>0</v>
       </c>
       <c r="L58" s="22">
         <f>SUM(L8:L57)</f>
-        <v>2958.3</v>
+        <v>0</v>
       </c>
       <c r="M58" s="20" t="n"/>
       <c r="N58" s="19" t="n"/>
@@ -5053,11 +5053,11 @@
       </c>
       <c r="C64" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B64,$O$8:$O$57,1)</f>
-        <v>256.4</v>
+        <v>0</v>
       </c>
       <c r="D64" s="16">
         <f>COUNTIFS($E$8:$E$57,$B64,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -5068,11 +5068,11 @@
       </c>
       <c r="C65" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B65,$O$8:$O$57,1)</f>
-        <v>173.8</v>
+        <v>0</v>
       </c>
       <c r="D65" s="16">
         <f>COUNTIFS($E$8:$E$57,$B65,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -5083,11 +5083,11 @@
       </c>
       <c r="C66" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B66,$O$8:$O$57,1)</f>
-        <v>311.2</v>
+        <v>0</v>
       </c>
       <c r="D66" s="16">
         <f>COUNTIFS($E$8:$E$57,$B66,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -5098,11 +5098,11 @@
       </c>
       <c r="C67" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B67,$O$8:$O$57,1)</f>
-        <v>323.8</v>
+        <v>0</v>
       </c>
       <c r="D67" s="16">
         <f>COUNTIFS($E$8:$E$57,$B67,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -5113,11 +5113,11 @@
       </c>
       <c r="C68" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B68,$O$8:$O$57,1)</f>
-        <v>591.7</v>
+        <v>0</v>
       </c>
       <c r="D68" s="16">
         <f>COUNTIFS($E$8:$E$57,$B68,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -5128,11 +5128,11 @@
       </c>
       <c r="C69" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B69,$O$8:$O$57,1)</f>
-        <v>106.6</v>
+        <v>0</v>
       </c>
       <c r="D69" s="16">
         <f>COUNTIFS($E$8:$E$57,$B69,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -5143,11 +5143,11 @@
       </c>
       <c r="C70" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B70,$O$8:$O$57,1)</f>
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="D70" s="16">
         <f>COUNTIFS($E$8:$E$57,$B70,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -5158,11 +5158,11 @@
       </c>
       <c r="C71" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B71,$O$8:$O$57,1)</f>
-        <v>56.4</v>
+        <v>0</v>
       </c>
       <c r="D71" s="16">
         <f>COUNTIFS($E$8:$E$57,$B71,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -5173,11 +5173,11 @@
       </c>
       <c r="C72" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B72,$O$8:$O$57,1)</f>
-        <v>124.2</v>
+        <v>0</v>
       </c>
       <c r="D72" s="16">
         <f>COUNTIFS($E$8:$E$57,$B72,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -5188,11 +5188,11 @@
       </c>
       <c r="C73" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B73,$O$8:$O$57,1)</f>
-        <v>108.8</v>
+        <v>0</v>
       </c>
       <c r="D73" s="16">
         <f>COUNTIFS($E$8:$E$57,$B73,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -5203,11 +5203,11 @@
       </c>
       <c r="C74" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B74,$O$8:$O$57,1)</f>
-        <v>361.1</v>
+        <v>0</v>
       </c>
       <c r="D74" s="16">
         <f>COUNTIFS($E$8:$E$57,$B74,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -5218,11 +5218,11 @@
       </c>
       <c r="C75" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B75,$O$8:$O$57,1)</f>
-        <v>179.4</v>
+        <v>0</v>
       </c>
       <c r="D75" s="16">
         <f>COUNTIFS($E$8:$E$57,$B75,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -5233,11 +5233,11 @@
       </c>
       <c r="C76" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B76,$O$8:$O$57,1)</f>
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="D76" s="16">
         <f>COUNTIFS($E$8:$E$57,$B76,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -5248,11 +5248,11 @@
       </c>
       <c r="C77" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B77,$O$8:$O$57,1)</f>
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="D77" s="16">
         <f>COUNTIFS($E$8:$E$57,$B77,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -5278,11 +5278,11 @@
       </c>
       <c r="C79" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B79,$O$8:$O$57,1)</f>
-        <v>194.9</v>
+        <v>0</v>
       </c>
       <c r="D79" s="16">
         <f>COUNTIFS($E$8:$E$57,$B79,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -5293,11 +5293,11 @@
       </c>
       <c r="C80" s="22">
         <f>SUM(C64:C79)</f>
-        <v>2958.3</v>
+        <v>0</v>
       </c>
       <c r="D80" s="21">
         <f>SUM(D64:D79)</f>
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>98</v>
+        <v>333</v>
       </c>
       <c r="D8" s="23" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="23" t="n">
-        <v>98</v>
+        <v>333</v>
       </c>
     </row>
     <row r="9">
@@ -5616,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="M9" s="23" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="23" t="n">
-        <v>69</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10">
@@ -5644,19 +5644,19 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>192</v>
+        <v>631</v>
       </c>
       <c r="E10" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>39</v>
+        <v>114</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="23" t="n">
-        <v>28</v>
+        <v>56</v>
       </c>
       <c r="P10" s="23" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="23" t="n">
-        <v>288</v>
+        <v>838</v>
       </c>
     </row>
     <row r="11">
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>238</v>
+        <v>643</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>0</v>
@@ -5741,7 +5741,7 @@
         <v>0</v>
       </c>
       <c r="O11" s="23" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="P11" s="23" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>266</v>
+        <v>703</v>
       </c>
     </row>
     <row r="12">
@@ -5778,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>192</v>
+        <v>535</v>
       </c>
     </row>
     <row r="13">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>0</v>
@@ -5839,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="J13" s="23" t="n">
         <v>0</v>
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>98</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>25</v>
+        <v>89</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>0</v>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="H14" s="23" t="n">
         <v>0</v>
@@ -5903,13 +5903,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="23" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="L14" s="23" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="23" t="n">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="N14" s="23" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="23" t="n">
-        <v>122</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15">
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="23" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="O15" s="23" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
@@ -6016,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="23" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="K16" s="23" t="n">
         <v>0</v>
@@ -6040,7 +6040,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="23" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -6092,13 +6092,13 @@
         <v>0</v>
       </c>
       <c r="P17" s="23" t="n">
-        <v>186</v>
+        <v>387</v>
       </c>
       <c r="Q17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="23" t="n">
-        <v>186</v>
+        <v>387</v>
       </c>
     </row>
     <row r="18">
@@ -6117,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="F18" s="23" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="23" t="n">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="L18" s="23" t="n">
         <v>0</v>
@@ -6153,10 +6153,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="23" t="n">
-        <v>73</v>
+        <v>244</v>
       </c>
       <c r="R18" s="23" t="n">
-        <v>126</v>
+        <v>507</v>
       </c>
     </row>
     <row r="19">
@@ -6166,55 +6166,55 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>58</v>
+        <v>158</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>98</v>
+        <v>333</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>192</v>
+        <v>631</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>26</v>
+        <v>189</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>277</v>
+        <v>757</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>192</v>
+        <v>535</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>94</v>
+        <v>210</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>35</v>
+        <v>79</v>
       </c>
       <c r="K19" s="23" t="n">
-        <v>47</v>
+        <v>138</v>
       </c>
       <c r="L19" s="23" t="n">
-        <v>69</v>
+        <v>159</v>
       </c>
       <c r="M19" s="23" t="n">
-        <v>39</v>
+        <v>144</v>
       </c>
       <c r="N19" s="23" t="n">
-        <v>11</v>
+        <v>55</v>
       </c>
       <c r="O19" s="23" t="n">
-        <v>56</v>
+        <v>116</v>
       </c>
       <c r="P19" s="23" t="n">
-        <v>186</v>
+        <v>387</v>
       </c>
       <c r="Q19" s="23" t="n">
-        <v>73</v>
+        <v>244</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>1491</v>
+        <v>4212</v>
       </c>
     </row>
   </sheetData>
@@ -6299,38 +6299,38 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>SNK002</t>
+          <t>BAK001</t>
         </is>
       </c>
       <c r="B2" s="25" t="inlineStr">
         <is>
-          <t>Chocolate Block 200g</t>
+          <t>Toast Bread White</t>
         </is>
       </c>
       <c r="C2" s="25" t="inlineStr">
         <is>
-          <t>Snacks &amp; Confectionery</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Confectionery Ltd</t>
+          <t>Auckland Bakehouse</t>
         </is>
       </c>
       <c r="E2" s="26" t="n">
-        <v>17.357</v>
+        <v>20.286</v>
       </c>
       <c r="F2" s="26" t="n">
-        <v>5.977</v>
+        <v>6.879</v>
       </c>
       <c r="G2" s="27" t="n">
-        <v>6</v>
+        <v>181</v>
       </c>
       <c r="H2" s="25" t="n">
-        <v>270</v>
+        <v>5</v>
       </c>
       <c r="I2" s="28" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="J2" s="25" t="n">
         <v>0</v>
@@ -6339,38 +6339,38 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>BEV001</t>
+          <t>BAK002</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>Energy Drink 500ml</t>
+          <t>Wholemeal Loaf</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D3" s="25" t="inlineStr">
         <is>
-          <t>Beverage Dist.</t>
+          <t>Auckland Bakehouse</t>
         </is>
       </c>
       <c r="E3" s="26" t="n">
-        <v>26.964</v>
+        <v>9.929</v>
       </c>
       <c r="F3" s="26" t="n">
-        <v>11.902</v>
+        <v>4.337</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="H3" s="25" t="n">
-        <v>365</v>
+        <v>5</v>
       </c>
       <c r="I3" s="28" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="J3" s="25" t="n">
         <v>0</v>
@@ -6379,38 +6379,38 @@
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>DRY010</t>
+          <t>BAK003</t>
         </is>
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>Butter 500g</t>
+          <t>Croissant 4pk</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D4" s="25" t="inlineStr">
         <is>
-          <t>Dairy Co-op</t>
+          <t>Auckland Bakehouse</t>
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>7.25</v>
+        <v>7.286</v>
       </c>
       <c r="F4" s="26" t="n">
-        <v>4.664</v>
+        <v>3.376</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="H4" s="25" t="n">
-        <v>60</v>
+        <v>3</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>5.6</v>
+        <v>3.3</v>
       </c>
       <c r="J4" s="25" t="n">
         <v>0</v>
@@ -6419,38 +6419,38 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>LIQ004</t>
+          <t>BBT001</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Pinot Noir 750ml</t>
+          <t>Bubble Tea Kit</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Beer &amp; Wine</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>Liquor Dist.</t>
+          <t>Asia Imports</t>
         </is>
       </c>
       <c r="E5" s="26" t="n">
-        <v>2.107</v>
+        <v>5.607</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>1.75</v>
+        <v>3.01</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>730</v>
+        <v>90</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>12.8</v>
+        <v>3.9</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>0</v>
@@ -6459,38 +6459,38 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>FRZ004</t>
+          <t>BEV001</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>Frozen Dumplings 1kg</t>
+          <t>Energy Drink 500ml</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Asia Imports</t>
+          <t>Beverage Dist.</t>
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>4.75</v>
+        <v>30.5</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>1.506</v>
+        <v>14.658</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>4</v>
+        <v>235</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>365</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>7.1</v>
+        <v>2.15</v>
       </c>
       <c r="J6" s="25" t="n">
         <v>0</v>
@@ -6499,38 +6499,38 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>GRO001</t>
+          <t>BEV002</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>Instant Noodles 5pk</t>
+          <t>Cola 1.5L</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D7" s="25" t="inlineStr">
         <is>
-          <t>Asia Imports</t>
+          <t>Beverage Dist.</t>
         </is>
       </c>
       <c r="E7" s="26" t="n">
-        <v>14.036</v>
+        <v>14.214</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>4.384</v>
+        <v>4.879</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>25</v>
+        <v>119</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>365</v>
+        <v>270</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
       <c r="J7" s="25" t="n">
         <v>0</v>
@@ -6539,38 +6539,38 @@
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>GRO008</t>
+          <t>BEV003</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>Coffee Beans 200g</t>
+          <t>Sparkling Water 1L</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D8" s="25" t="inlineStr">
         <is>
-          <t>Pantry Brands</t>
+          <t>Beverage Dist.</t>
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>3.357</v>
+        <v>11.679</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>1.768</v>
+        <v>3.982</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>5</v>
+        <v>106</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>180</v>
+        <v>365</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>7.6</v>
+        <v>1.1</v>
       </c>
       <c r="J8" s="25" t="n">
         <v>0</v>
@@ -6579,38 +6579,38 @@
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>SNK003</t>
+          <t>BEV004</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Muesli Bar 6pk</t>
+          <t>Iced Coffee 500ml</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
         <is>
-          <t>Snacks &amp; Confectionery</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>Snack Foods NZ</t>
+          <t>Dairy Co-op</t>
         </is>
       </c>
       <c r="E9" s="26" t="n">
-        <v>10.357</v>
+        <v>12.5</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>3.889</v>
+        <v>4.726</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>16</v>
+        <v>114</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>240</v>
+        <v>30</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J9" s="25" t="n">
         <v>0</v>
@@ -6619,38 +6619,38 @@
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>PHM002</t>
+          <t>BEV005</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Sunscreen SPF50</t>
+          <t>Kombucha 330ml</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Pharma Dist.</t>
+          <t>Plant Foods NZ</t>
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>2.321</v>
+        <v>4.571</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>1.442</v>
+        <v>2.755</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>3</v>
+        <v>56</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>730</v>
+        <v>120</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>8.199999999999999</v>
+        <v>2.6</v>
       </c>
       <c r="J10" s="25" t="n">
         <v>0</v>
@@ -6659,38 +6659,38 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>GRO006</t>
+          <t>BEV006</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>Taco Kit</t>
+          <t>Bottled Water 750ml</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>Latin Pantry</t>
+          <t>Beverage Dist.</t>
         </is>
       </c>
       <c r="E11" s="26" t="n">
-        <v>2.786</v>
+        <v>17.393</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>2.234</v>
+        <v>5.101</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>1</v>
+        <v>171</v>
       </c>
       <c r="H11" s="25" t="n">
         <v>365</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>4</v>
+        <v>0.95</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>0</v>
@@ -6699,38 +6699,38 @@
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>SNK005</t>
+          <t>DRY010</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Lollies Bag 200g</t>
+          <t>Butter 500g</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>Snacks &amp; Confectionery</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Confectionery Ltd</t>
+          <t>Dairy Co-op</t>
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>10.75</v>
+        <v>6.786</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>4.979</v>
+        <v>4.677</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>300</v>
+        <v>60</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>1.7</v>
+        <v>5.6</v>
       </c>
       <c r="J12" s="25" t="n">
         <v>0</v>
@@ -6739,38 +6739,38 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>BAK003</t>
+          <t>DRY011</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Croissant 4pk</t>
+          <t>Greek Yoghurt 1kg</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D13" s="25" t="inlineStr">
         <is>
-          <t>Auckland Bakehouse</t>
+          <t>Dairy Co-op</t>
         </is>
       </c>
       <c r="E13" s="26" t="n">
-        <v>6.75</v>
+        <v>4.893</v>
       </c>
       <c r="F13" s="26" t="n">
-        <v>3.122</v>
+        <v>2.299</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>7</v>
+        <v>51</v>
       </c>
       <c r="H13" s="25" t="n">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>3.3</v>
+        <v>5.1</v>
       </c>
       <c r="J13" s="25" t="n">
         <v>0</v>
@@ -6779,78 +6779,78 @@
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>GRO004</t>
+          <t>DRY012</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Simmer Sauce 485g</t>
+          <t>Cheese Block 1kg</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D14" s="25" t="inlineStr">
         <is>
-          <t>Pantry Brands</t>
+          <t>Dairy Co-op</t>
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>5.286</v>
+        <v>5.214</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>2.507</v>
+        <v>2.378</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>540</v>
+        <v>90</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>2.3</v>
+        <v>10.4</v>
       </c>
       <c r="J14" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>GRO002</t>
+          <t>FRZ001</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>Canned Soup 500g</t>
+          <t>Ice Cream Tub 2L</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>Pantry Brands</t>
+          <t>Frozen Foods NZ</t>
         </is>
       </c>
       <c r="E15" s="26" t="n">
-        <v>6.143</v>
+        <v>7.071</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>2.46</v>
+        <v>3.126</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>10</v>
+        <v>62</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>730</v>
+        <v>365</v>
       </c>
       <c r="I15" s="28" t="n">
-        <v>1.9</v>
+        <v>5.4</v>
       </c>
       <c r="J15" s="25" t="n">
         <v>0</v>
@@ -6859,38 +6859,38 @@
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>PHM001</t>
+          <t>FRZ002</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Paracetamol 20pk</t>
+          <t>Ice Block Single</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
         <is>
-          <t>Health &amp; Beauty</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="D16" s="25" t="inlineStr">
         <is>
-          <t>Pharma Dist.</t>
+          <t>Frozen Foods NZ</t>
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>4.607</v>
+        <v>9.893000000000001</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>2.544</v>
+        <v>3.975</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>8</v>
+        <v>102</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>730</v>
+        <v>365</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
       <c r="J16" s="25" t="n">
         <v>0</v>
@@ -6899,38 +6899,38 @@
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>FTG003</t>
+          <t>FRZ003</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>Hot Pie Mince &amp; Cheese</t>
+          <t>Frozen Pizza</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
         <is>
-          <t>Food To Go</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="D17" s="25" t="inlineStr">
         <is>
-          <t>FreshKitchen</t>
+          <t>Frozen Foods NZ</t>
         </is>
       </c>
       <c r="E17" s="26" t="n">
-        <v>18.179</v>
+        <v>5.964</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>4.347</v>
+        <v>3.361</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>2</v>
+        <v>365</v>
       </c>
       <c r="I17" s="28" t="n">
-        <v>2.4</v>
+        <v>4.7</v>
       </c>
       <c r="J17" s="25" t="n">
         <v>0</v>
@@ -6939,38 +6939,38 @@
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>MLK001</t>
+          <t>FRZ004</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>Milk Standard 2L</t>
+          <t>Frozen Dumplings 1kg</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>Dairy Co-op</t>
+          <t>Asia Imports</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>34.179</v>
+        <v>4.464</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>14.368</v>
+        <v>2.457</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>135</v>
+        <v>32</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>10</v>
+        <v>365</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>3.55</v>
+        <v>7.1</v>
       </c>
       <c r="J18" s="25" t="n">
         <v>0</v>
@@ -6979,38 +6979,38 @@
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>LIQ003</t>
+          <t>FTG001</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>RTD 4pk</t>
+          <t>Chicken Sandwich</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Beer &amp; Wine</t>
+          <t>Food To Go</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>Liquor Dist.</t>
+          <t>FreshKitchen</t>
         </is>
       </c>
       <c r="E19" s="26" t="n">
-        <v>4.179</v>
+        <v>19.357</v>
       </c>
       <c r="F19" s="26" t="n">
-        <v>2.374</v>
+        <v>5.411</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>365</v>
+        <v>2</v>
       </c>
       <c r="I19" s="28" t="n">
-        <v>11.9</v>
+        <v>3.9</v>
       </c>
       <c r="J19" s="25" t="n">
         <v>0</v>
@@ -7019,38 +7019,38 @@
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>BAK001</t>
+          <t>FTG002</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Toast Bread White</t>
+          <t>Sushi Pack 8pc</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Food To Go</t>
         </is>
       </c>
       <c r="D20" s="25" t="inlineStr">
         <is>
-          <t>Auckland Bakehouse</t>
+          <t>FreshKitchen</t>
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>20.786</v>
+        <v>9.214</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>6.511</v>
+        <v>3.224</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>44</v>
+        <v>117</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>2.2</v>
+        <v>5.6</v>
       </c>
       <c r="J20" s="25" t="n">
         <v>0</v>
@@ -7059,38 +7059,38 @@
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>GRO007</t>
+          <t>FTG003</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>Eggs Free Range 12pk</t>
+          <t>Hot Pie Mince &amp; Cheese</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Food To Go</t>
         </is>
       </c>
       <c r="D21" s="25" t="inlineStr">
         <is>
-          <t>Farm Fresh</t>
+          <t>FreshKitchen</t>
         </is>
       </c>
       <c r="E21" s="26" t="n">
-        <v>9.464</v>
+        <v>18.143</v>
       </c>
       <c r="F21" s="26" t="n">
-        <v>4.55</v>
+        <v>6.346</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>38</v>
+        <v>129</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I21" s="28" t="n">
-        <v>8.199999999999999</v>
+        <v>2.4</v>
       </c>
       <c r="J21" s="25" t="n">
         <v>0</v>
@@ -7099,38 +7099,38 @@
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>MLK002</t>
+          <t>FTG004</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>Milk Lite 2L</t>
+          <t>Salad Bowl</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Food To Go</t>
         </is>
       </c>
       <c r="D22" s="25" t="inlineStr">
         <is>
-          <t>Dairy Co-op</t>
+          <t>FreshKitchen</t>
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>15.857</v>
+        <v>6.286</v>
       </c>
       <c r="F22" s="26" t="n">
-        <v>4.942</v>
+        <v>2.637</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H22" s="25" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="J22" s="25" t="n">
         <v>0</v>
@@ -7139,38 +7139,38 @@
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>SNK001</t>
+          <t>FTG005</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>Potato Chips 150g</t>
+          <t>Filled Roll</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
         <is>
-          <t>Snacks &amp; Confectionery</t>
+          <t>Food To Go</t>
         </is>
       </c>
       <c r="D23" s="25" t="inlineStr">
         <is>
-          <t>Snack Foods NZ</t>
+          <t>FreshKitchen</t>
         </is>
       </c>
       <c r="E23" s="26" t="n">
-        <v>21.321</v>
+        <v>11</v>
       </c>
       <c r="F23" s="26" t="n">
-        <v>6.492</v>
+        <v>4.823</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="H23" s="25" t="n">
-        <v>180</v>
+        <v>2</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="J23" s="25" t="n">
         <v>0</v>
@@ -7179,38 +7179,38 @@
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>HHD001</t>
+          <t>GRO001</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Toilet Paper 6pk</t>
+          <t>Instant Noodles 5pk</t>
         </is>
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Asia Imports</t>
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>5.536</v>
+        <v>11.857</v>
       </c>
       <c r="F24" s="26" t="n">
-        <v>2.603</v>
+        <v>4.369</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>17</v>
+        <v>89</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>3650</v>
+        <v>365</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>5.9</v>
+        <v>2.6</v>
       </c>
       <c r="J24" s="25" t="n">
         <v>0</v>
@@ -7219,38 +7219,38 @@
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>BEV004</t>
+          <t>GRO002</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Iced Coffee 500ml</t>
+          <t>Canned Soup 500g</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>Dairy Co-op</t>
+          <t>Pantry Brands</t>
         </is>
       </c>
       <c r="E25" s="26" t="n">
-        <v>13.143</v>
+        <v>5.786</v>
       </c>
       <c r="F25" s="26" t="n">
-        <v>4.461</v>
+        <v>3.201</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H25" s="25" t="n">
-        <v>30</v>
+        <v>730</v>
       </c>
       <c r="I25" s="28" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J25" s="25" t="n">
         <v>0</v>
@@ -7259,38 +7259,38 @@
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>DRY012</t>
+          <t>GRO003</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>Cheese Block 1kg</t>
+          <t>Pasta 500g</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D26" s="25" t="inlineStr">
         <is>
-          <t>Dairy Co-op</t>
+          <t>Pantry Brands</t>
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>5.321</v>
+        <v>6.714</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>2.229</v>
+        <v>3.041</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
       <c r="H26" s="25" t="n">
-        <v>90</v>
+        <v>730</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>10.4</v>
+        <v>1.3</v>
       </c>
       <c r="J26" s="25" t="n">
         <v>0</v>
@@ -7299,78 +7299,78 @@
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>BEV002</t>
+          <t>GRO004</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>Cola 1.5L</t>
+          <t>Simmer Sauce 485g</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D27" s="25" t="inlineStr">
         <is>
-          <t>Beverage Dist.</t>
+          <t>Pantry Brands</t>
         </is>
       </c>
       <c r="E27" s="26" t="n">
-        <v>14.321</v>
+        <v>5</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>4.839</v>
+        <v>2.553</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>270</v>
+        <v>540</v>
       </c>
       <c r="I27" s="28" t="n">
         <v>2.3</v>
       </c>
       <c r="J27" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>FRZ003</t>
+          <t>GRO005</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Frozen Pizza</t>
+          <t>Salsa 300g</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>Frozen Foods NZ</t>
+          <t>Latin Pantry</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>5.214</v>
+        <v>2.679</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>2.807</v>
+        <v>2.389</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="H28" s="25" t="n">
         <v>365</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>4.7</v>
+        <v>2.9</v>
       </c>
       <c r="J28" s="25" t="n">
         <v>0</v>
@@ -7379,38 +7379,38 @@
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>LIQ002</t>
+          <t>GRO006</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>Sauvignon Blanc 750ml</t>
+          <t>Taco Kit</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
         <is>
-          <t>Beer &amp; Wine</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D29" s="25" t="inlineStr">
         <is>
-          <t>Liquor Dist.</t>
+          <t>Latin Pantry</t>
         </is>
       </c>
       <c r="E29" s="26" t="n">
-        <v>4.571</v>
+        <v>2.893</v>
       </c>
       <c r="F29" s="26" t="n">
-        <v>2.268</v>
+        <v>1.524</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="H29" s="25" t="n">
-        <v>730</v>
+        <v>365</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>10.2</v>
+        <v>4</v>
       </c>
       <c r="J29" s="25" t="n">
         <v>0</v>
@@ -7419,38 +7419,38 @@
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>SNK004</t>
+          <t>GRO007</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Corn Chips 230g</t>
+          <t>Eggs Free Range 12pk</t>
         </is>
       </c>
       <c r="C30" s="25" t="inlineStr">
         <is>
-          <t>Snacks &amp; Confectionery</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>Latin Pantry</t>
+          <t>Farm Fresh</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>8.821</v>
+        <v>9.393000000000001</v>
       </c>
       <c r="F30" s="26" t="n">
-        <v>2.982</v>
+        <v>3.573</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>27</v>
+        <v>77</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>2.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30" s="25" t="n">
         <v>0</v>
@@ -7459,38 +7459,38 @@
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>HHD003</t>
+          <t>GRO008</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Phone Charger Cable</t>
+          <t>Coffee Beans 200g</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Pantry Brands</t>
         </is>
       </c>
       <c r="E31" s="26" t="n">
-        <v>1.286</v>
+        <v>3.643</v>
       </c>
       <c r="F31" s="26" t="n">
-        <v>1.384</v>
+        <v>2.147</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>3650</v>
+        <v>180</v>
       </c>
       <c r="I31" s="28" t="n">
-        <v>5.5</v>
+        <v>7.6</v>
       </c>
       <c r="J31" s="25" t="n">
         <v>0</v>
@@ -7499,38 +7499,38 @@
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>GRO003</t>
+          <t>HHD001</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>Pasta 500g</t>
+          <t>Toilet Paper 6pk</t>
         </is>
       </c>
       <c r="C32" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
         <is>
-          <t>Pantry Brands</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>6.929</v>
+        <v>5.5</v>
       </c>
       <c r="F32" s="26" t="n">
-        <v>3.848</v>
+        <v>2.411</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>730</v>
+        <v>3650</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>1.3</v>
+        <v>5.9</v>
       </c>
       <c r="J32" s="25" t="n">
         <v>0</v>
@@ -7539,38 +7539,38 @@
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>MLK003</t>
+          <t>HHD002</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Oat Milk 1L</t>
+          <t>Dishwash Liquid</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D33" s="25" t="inlineStr">
         <is>
-          <t>Plant Foods NZ</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E33" s="26" t="n">
-        <v>7.357</v>
+        <v>2.107</v>
       </c>
       <c r="F33" s="26" t="n">
-        <v>2.697</v>
+        <v>1.37</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>60</v>
+        <v>1095</v>
       </c>
       <c r="I33" s="28" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
       <c r="J33" s="25" t="n">
         <v>0</v>
@@ -7579,12 +7579,12 @@
     <row r="34">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>HHD002</t>
+          <t>HHD003</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Dishwash Liquid</t>
+          <t>Phone Charger Cable</t>
         </is>
       </c>
       <c r="C34" s="25" t="inlineStr">
@@ -7598,19 +7598,19 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>3.214</v>
+        <v>0.643</v>
       </c>
       <c r="F34" s="26" t="n">
-        <v>1.813</v>
+        <v>0.951</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>1095</v>
+        <v>3650</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J34" s="25" t="n">
         <v>0</v>
@@ -7619,38 +7619,38 @@
     <row r="35">
       <c r="A35" s="25" t="inlineStr">
         <is>
-          <t>BAK002</t>
+          <t>LIQ001</t>
         </is>
       </c>
       <c r="B35" s="25" t="inlineStr">
         <is>
-          <t>Wholemeal Loaf</t>
+          <t>Craft Beer 6pk</t>
         </is>
       </c>
       <c r="C35" s="25" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Beer &amp; Wine</t>
         </is>
       </c>
       <c r="D35" s="25" t="inlineStr">
         <is>
-          <t>Auckland Bakehouse</t>
+          <t>Liquor Dist.</t>
         </is>
       </c>
       <c r="E35" s="26" t="n">
-        <v>10.393</v>
+        <v>4.857</v>
       </c>
       <c r="F35" s="26" t="n">
-        <v>3.804</v>
+        <v>2.649</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H35" s="25" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="I35" s="28" t="n">
-        <v>2.7</v>
+        <v>15.3</v>
       </c>
       <c r="J35" s="25" t="n">
         <v>0</v>
@@ -7659,38 +7659,38 @@
     <row r="36">
       <c r="A36" s="25" t="inlineStr">
         <is>
-          <t>BBT001</t>
+          <t>LIQ002</t>
         </is>
       </c>
       <c r="B36" s="25" t="inlineStr">
         <is>
-          <t>Bubble Tea Kit</t>
+          <t>Sauvignon Blanc 750ml</t>
         </is>
       </c>
       <c r="C36" s="25" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Beer &amp; Wine</t>
         </is>
       </c>
       <c r="D36" s="25" t="inlineStr">
         <is>
-          <t>Asia Imports</t>
+          <t>Liquor Dist.</t>
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>5.5</v>
+        <v>5.286</v>
       </c>
       <c r="F36" s="26" t="n">
-        <v>2.546</v>
+        <v>3.017</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="H36" s="25" t="n">
-        <v>90</v>
+        <v>730</v>
       </c>
       <c r="I36" s="28" t="n">
-        <v>3.9</v>
+        <v>10.2</v>
       </c>
       <c r="J36" s="25" t="n">
         <v>0</v>
@@ -7699,38 +7699,38 @@
     <row r="37">
       <c r="A37" s="25" t="inlineStr">
         <is>
-          <t>BEV003</t>
+          <t>LIQ003</t>
         </is>
       </c>
       <c r="B37" s="25" t="inlineStr">
         <is>
-          <t>Sparkling Water 1L</t>
+          <t>RTD 4pk</t>
         </is>
       </c>
       <c r="C37" s="25" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Beer &amp; Wine</t>
         </is>
       </c>
       <c r="D37" s="25" t="inlineStr">
         <is>
-          <t>Beverage Dist.</t>
+          <t>Liquor Dist.</t>
         </is>
       </c>
       <c r="E37" s="26" t="n">
-        <v>11.143</v>
+        <v>3.857</v>
       </c>
       <c r="F37" s="26" t="n">
-        <v>3.669</v>
+        <v>2.05</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="H37" s="25" t="n">
         <v>365</v>
       </c>
       <c r="I37" s="28" t="n">
-        <v>1.1</v>
+        <v>11.9</v>
       </c>
       <c r="J37" s="25" t="n">
         <v>0</v>
@@ -7739,38 +7739,38 @@
     <row r="38">
       <c r="A38" s="25" t="inlineStr">
         <is>
-          <t>BEV005</t>
+          <t>LIQ004</t>
         </is>
       </c>
       <c r="B38" s="25" t="inlineStr">
         <is>
-          <t>Kombucha 330ml</t>
+          <t>Pinot Noir 750ml</t>
         </is>
       </c>
       <c r="C38" s="25" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Beer &amp; Wine</t>
         </is>
       </c>
       <c r="D38" s="25" t="inlineStr">
         <is>
-          <t>Plant Foods NZ</t>
+          <t>Liquor Dist.</t>
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>5.143</v>
+        <v>1.929</v>
       </c>
       <c r="F38" s="26" t="n">
-        <v>3.535</v>
+        <v>1.904</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="H38" s="25" t="n">
-        <v>120</v>
+        <v>730</v>
       </c>
       <c r="I38" s="28" t="n">
-        <v>2.6</v>
+        <v>12.8</v>
       </c>
       <c r="J38" s="25" t="n">
         <v>0</v>
@@ -7779,38 +7779,38 @@
     <row r="39">
       <c r="A39" s="25" t="inlineStr">
         <is>
-          <t>BEV006</t>
+          <t>MLK001</t>
         </is>
       </c>
       <c r="B39" s="25" t="inlineStr">
         <is>
-          <t>Bottled Water 750ml</t>
+          <t>Milk Standard 2L</t>
         </is>
       </c>
       <c r="C39" s="25" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D39" s="25" t="inlineStr">
         <is>
-          <t>Beverage Dist.</t>
+          <t>Dairy Co-op</t>
         </is>
       </c>
       <c r="E39" s="26" t="n">
-        <v>15.964</v>
+        <v>34.286</v>
       </c>
       <c r="F39" s="26" t="n">
-        <v>4.623</v>
+        <v>13.424</v>
       </c>
       <c r="G39" s="27" t="n">
-        <v>73</v>
+        <v>344</v>
       </c>
       <c r="H39" s="25" t="n">
-        <v>365</v>
+        <v>10</v>
       </c>
       <c r="I39" s="28" t="n">
-        <v>0.95</v>
+        <v>3.55</v>
       </c>
       <c r="J39" s="25" t="n">
         <v>0</v>
@@ -7819,12 +7819,12 @@
     <row r="40">
       <c r="A40" s="25" t="inlineStr">
         <is>
-          <t>DRY011</t>
+          <t>MLK002</t>
         </is>
       </c>
       <c r="B40" s="25" t="inlineStr">
         <is>
-          <t>Greek Yoghurt 1kg</t>
+          <t>Milk Lite 2L</t>
         </is>
       </c>
       <c r="C40" s="25" t="inlineStr">
@@ -7838,19 +7838,19 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>5.107</v>
+        <v>14.607</v>
       </c>
       <c r="F40" s="26" t="n">
-        <v>2.544</v>
+        <v>4.113</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>24</v>
+        <v>145</v>
       </c>
       <c r="H40" s="25" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="I40" s="28" t="n">
-        <v>5.1</v>
+        <v>3.55</v>
       </c>
       <c r="J40" s="25" t="n">
         <v>0</v>
@@ -7859,38 +7859,38 @@
     <row r="41">
       <c r="A41" s="25" t="inlineStr">
         <is>
-          <t>FRZ001</t>
+          <t>MLK003</t>
         </is>
       </c>
       <c r="B41" s="25" t="inlineStr">
         <is>
-          <t>Ice Cream Tub 2L</t>
+          <t>Oat Milk 1L</t>
         </is>
       </c>
       <c r="C41" s="25" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D41" s="25" t="inlineStr">
         <is>
-          <t>Frozen Foods NZ</t>
+          <t>Plant Foods NZ</t>
         </is>
       </c>
       <c r="E41" s="26" t="n">
-        <v>5.214</v>
+        <v>8.071</v>
       </c>
       <c r="F41" s="26" t="n">
-        <v>2.872</v>
+        <v>4.225</v>
       </c>
       <c r="G41" s="27" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="H41" s="25" t="n">
-        <v>365</v>
+        <v>60</v>
       </c>
       <c r="I41" s="28" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="J41" s="25" t="n">
         <v>0</v>
@@ -7899,38 +7899,38 @@
     <row r="42">
       <c r="A42" s="25" t="inlineStr">
         <is>
-          <t>FRZ002</t>
+          <t>PHM001</t>
         </is>
       </c>
       <c r="B42" s="25" t="inlineStr">
         <is>
-          <t>Ice Block Single</t>
+          <t>Paracetamol 20pk</t>
         </is>
       </c>
       <c r="C42" s="25" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>Health &amp; Beauty</t>
         </is>
       </c>
       <c r="D42" s="25" t="inlineStr">
         <is>
-          <t>Frozen Foods NZ</t>
+          <t>Pharma Dist.</t>
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>10.679</v>
+        <v>5.357</v>
       </c>
       <c r="F42" s="26" t="n">
-        <v>3.549</v>
+        <v>3.021</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="H42" s="25" t="n">
-        <v>365</v>
+        <v>730</v>
       </c>
       <c r="I42" s="28" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="J42" s="25" t="n">
         <v>0</v>
@@ -7939,38 +7939,38 @@
     <row r="43">
       <c r="A43" s="25" t="inlineStr">
         <is>
-          <t>FTG001</t>
+          <t>PHM002</t>
         </is>
       </c>
       <c r="B43" s="25" t="inlineStr">
         <is>
-          <t>Chicken Sandwich</t>
+          <t>Sunscreen SPF50</t>
         </is>
       </c>
       <c r="C43" s="25" t="inlineStr">
         <is>
-          <t>Food To Go</t>
+          <t>Health &amp; Beauty</t>
         </is>
       </c>
       <c r="D43" s="25" t="inlineStr">
         <is>
-          <t>FreshKitchen</t>
+          <t>Pharma Dist.</t>
         </is>
       </c>
       <c r="E43" s="26" t="n">
-        <v>18.214</v>
+        <v>1.714</v>
       </c>
       <c r="F43" s="26" t="n">
-        <v>4.459</v>
+        <v>1.243</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="H43" s="25" t="n">
-        <v>2</v>
+        <v>730</v>
       </c>
       <c r="I43" s="28" t="n">
-        <v>3.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J43" s="25" t="n">
         <v>0</v>
@@ -7979,38 +7979,38 @@
     <row r="44">
       <c r="A44" s="25" t="inlineStr">
         <is>
-          <t>FTG002</t>
+          <t>PRD001</t>
         </is>
       </c>
       <c r="B44" s="25" t="inlineStr">
         <is>
-          <t>Sushi Pack 8pc</t>
+          <t>Bananas (each)</t>
         </is>
       </c>
       <c r="C44" s="25" t="inlineStr">
         <is>
-          <t>Food To Go</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="D44" s="25" t="inlineStr">
         <is>
-          <t>FreshKitchen</t>
+          <t>Produce Market</t>
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>10.857</v>
+        <v>31.607</v>
       </c>
       <c r="F44" s="26" t="n">
-        <v>6.029</v>
+        <v>6.63</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>60</v>
+        <v>270</v>
       </c>
       <c r="H44" s="25" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I44" s="28" t="n">
-        <v>5.6</v>
+        <v>0.38</v>
       </c>
       <c r="J44" s="25" t="n">
         <v>0</v>
@@ -8019,38 +8019,38 @@
     <row r="45">
       <c r="A45" s="25" t="inlineStr">
         <is>
-          <t>FTG004</t>
+          <t>PRD002</t>
         </is>
       </c>
       <c r="B45" s="25" t="inlineStr">
         <is>
-          <t>Salad Bowl</t>
+          <t>Avocado</t>
         </is>
       </c>
       <c r="C45" s="25" t="inlineStr">
         <is>
-          <t>Food To Go</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="D45" s="25" t="inlineStr">
         <is>
-          <t>FreshKitchen</t>
+          <t>Produce Market</t>
         </is>
       </c>
       <c r="E45" s="26" t="n">
-        <v>5.893</v>
+        <v>8.071</v>
       </c>
       <c r="F45" s="26" t="n">
-        <v>2.807</v>
+        <v>3.463</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="H45" s="25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I45" s="28" t="n">
-        <v>6.2</v>
+        <v>1.4</v>
       </c>
       <c r="J45" s="25" t="n">
         <v>0</v>
@@ -8059,38 +8059,38 @@
     <row r="46">
       <c r="A46" s="25" t="inlineStr">
         <is>
-          <t>FTG005</t>
+          <t>PRD003</t>
         </is>
       </c>
       <c r="B46" s="25" t="inlineStr">
         <is>
-          <t>Filled Roll</t>
+          <t>Tomatoes 500g</t>
         </is>
       </c>
       <c r="C46" s="25" t="inlineStr">
         <is>
-          <t>Food To Go</t>
+          <t>Produce</t>
         </is>
       </c>
       <c r="D46" s="25" t="inlineStr">
         <is>
-          <t>FreshKitchen</t>
+          <t>Produce Market</t>
         </is>
       </c>
       <c r="E46" s="26" t="n">
-        <v>11.893</v>
+        <v>4.5</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>3.891</v>
+        <v>2.769</v>
       </c>
       <c r="G46" s="27" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H46" s="25" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="I46" s="28" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="J46" s="25" t="n">
         <v>0</v>
@@ -8099,38 +8099,38 @@
     <row r="47">
       <c r="A47" s="25" t="inlineStr">
         <is>
-          <t>GRO005</t>
+          <t>SNK001</t>
         </is>
       </c>
       <c r="B47" s="25" t="inlineStr">
         <is>
-          <t>Salsa 300g</t>
+          <t>Potato Chips 150g</t>
         </is>
       </c>
       <c r="C47" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Snacks &amp; Confectionery</t>
         </is>
       </c>
       <c r="D47" s="25" t="inlineStr">
         <is>
-          <t>Latin Pantry</t>
+          <t>Snack Foods NZ</t>
         </is>
       </c>
       <c r="E47" s="26" t="n">
-        <v>2.857</v>
+        <v>20.679</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>2.46</v>
+        <v>6.717</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>19</v>
+        <v>170</v>
       </c>
       <c r="H47" s="25" t="n">
-        <v>365</v>
+        <v>180</v>
       </c>
       <c r="I47" s="28" t="n">
-        <v>2.9</v>
+        <v>2.1</v>
       </c>
       <c r="J47" s="25" t="n">
         <v>0</v>
@@ -8139,38 +8139,38 @@
     <row r="48">
       <c r="A48" s="25" t="inlineStr">
         <is>
-          <t>LIQ001</t>
+          <t>SNK002</t>
         </is>
       </c>
       <c r="B48" s="25" t="inlineStr">
         <is>
-          <t>Craft Beer 6pk</t>
+          <t>Chocolate Block 200g</t>
         </is>
       </c>
       <c r="C48" s="25" t="inlineStr">
         <is>
-          <t>Beer &amp; Wine</t>
+          <t>Snacks &amp; Confectionery</t>
         </is>
       </c>
       <c r="D48" s="25" t="inlineStr">
         <is>
-          <t>Liquor Dist.</t>
+          <t>Confectionery Ltd</t>
         </is>
       </c>
       <c r="E48" s="26" t="n">
-        <v>4.821</v>
+        <v>15.821</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>3.092</v>
+        <v>4.785</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>36</v>
+        <v>106</v>
       </c>
       <c r="H48" s="25" t="n">
-        <v>180</v>
+        <v>270</v>
       </c>
       <c r="I48" s="28" t="n">
-        <v>15.3</v>
+        <v>3.2</v>
       </c>
       <c r="J48" s="25" t="n">
         <v>0</v>
@@ -8179,38 +8179,38 @@
     <row r="49">
       <c r="A49" s="25" t="inlineStr">
         <is>
-          <t>PRD001</t>
+          <t>SNK003</t>
         </is>
       </c>
       <c r="B49" s="25" t="inlineStr">
         <is>
-          <t>Bananas (each)</t>
+          <t>Muesli Bar 6pk</t>
         </is>
       </c>
       <c r="C49" s="25" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Snacks &amp; Confectionery</t>
         </is>
       </c>
       <c r="D49" s="25" t="inlineStr">
         <is>
-          <t>Produce Market</t>
+          <t>Snack Foods NZ</t>
         </is>
       </c>
       <c r="E49" s="26" t="n">
-        <v>32.429</v>
+        <v>9.356999999999999</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>8.02</v>
+        <v>3.498</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>121</v>
+        <v>74</v>
       </c>
       <c r="H49" s="25" t="n">
-        <v>6</v>
+        <v>240</v>
       </c>
       <c r="I49" s="28" t="n">
-        <v>0.38</v>
+        <v>2.6</v>
       </c>
       <c r="J49" s="25" t="n">
         <v>0</v>
@@ -8219,38 +8219,38 @@
     <row r="50">
       <c r="A50" s="25" t="inlineStr">
         <is>
-          <t>PRD002</t>
+          <t>SNK004</t>
         </is>
       </c>
       <c r="B50" s="25" t="inlineStr">
         <is>
-          <t>Avocado</t>
+          <t>Corn Chips 230g</t>
         </is>
       </c>
       <c r="C50" s="25" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Snacks &amp; Confectionery</t>
         </is>
       </c>
       <c r="D50" s="25" t="inlineStr">
         <is>
-          <t>Produce Market</t>
+          <t>Latin Pantry</t>
         </is>
       </c>
       <c r="E50" s="26" t="n">
-        <v>7.107</v>
+        <v>9.143000000000001</v>
       </c>
       <c r="F50" s="26" t="n">
-        <v>2.529</v>
+        <v>3.229</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="H50" s="25" t="n">
-        <v>5</v>
+        <v>180</v>
       </c>
       <c r="I50" s="28" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="J50" s="25" t="n">
         <v>0</v>
@@ -8259,38 +8259,38 @@
     <row r="51">
       <c r="A51" s="25" t="inlineStr">
         <is>
-          <t>PRD003</t>
+          <t>SNK005</t>
         </is>
       </c>
       <c r="B51" s="25" t="inlineStr">
         <is>
-          <t>Tomatoes 500g</t>
+          <t>Lollies Bag 200g</t>
         </is>
       </c>
       <c r="C51" s="25" t="inlineStr">
         <is>
-          <t>Produce</t>
+          <t>Snacks &amp; Confectionery</t>
         </is>
       </c>
       <c r="D51" s="25" t="inlineStr">
         <is>
-          <t>Produce Market</t>
+          <t>Confectionery Ltd</t>
         </is>
       </c>
       <c r="E51" s="26" t="n">
-        <v>3.929</v>
+        <v>10.107</v>
       </c>
       <c r="F51" s="26" t="n">
-        <v>2.035</v>
+        <v>3.833</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>32</v>
+        <v>83</v>
       </c>
       <c r="H51" s="25" t="n">
-        <v>7</v>
+        <v>300</v>
       </c>
       <c r="I51" s="28" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
       <c r="J51" s="25" t="n">
         <v>0</v>
@@ -8641,7 +8641,7 @@
     <row r="6">
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 25 Sep 2026.  Shelly v1.4.0.</t>
+          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 04 Oct 2026.  Shelly v1.6.0.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 03 Oct 2026 05:51</t>
+          <t>Generated by Shelly on 04 Oct 2026 20:46</t>
         </is>
       </c>
     </row>

--- a/docs/reports/Shelly_Stock_Reorder.xlsx
+++ b/docs/reports/Shelly_Stock_Reorder.xlsx
@@ -586,13 +586,13 @@
       </sharedItems>
     </cacheField>
     <cacheField name="Daily demand" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="0.643" maxValue="34.286"/>
+      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1.143" maxValue="34.393"/>
     </cacheField>
     <cacheField name="Demand sd" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="0.951" maxValue="14.658"/>
+      <sharedItems count="0" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1.044" maxValue="19.56"/>
     </cacheField>
     <cacheField name="On hand" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
-      <sharedItems count="0" containsInteger="1" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="9" maxValue="344"/>
+      <sharedItems count="0" containsInteger="1" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="4" maxValue="344"/>
     </cacheField>
     <cacheField name="Shelf life days" uniqueList="1" numFmtId="0" sqlType="0" hierarchy="0" level="0" databaseField="1">
       <sharedItems count="0" containsInteger="1" containsNumber="1" containsSemiMixedTypes="0" containsString="0" minValue="1" maxValue="3650"/>
@@ -610,13 +610,25 @@
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50">
   <r>
+    <x v="32"/>
+    <x v="34"/>
+    <x v="8"/>
+    <x v="8"/>
+    <n v="1.143"/>
+    <n v="1.044"/>
+    <n v="4"/>
+    <n v="3650"/>
+    <n v="5.5"/>
+    <n v="0"/>
+  </r>
+  <r>
     <x v="0"/>
     <x v="46"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="20.286"/>
-    <n v="6.879"/>
-    <n v="181"/>
+    <n v="20.393"/>
+    <n v="6.154"/>
+    <n v="179"/>
     <n v="5"/>
     <n v="2.2"/>
     <n v="0"/>
@@ -626,9 +638,9 @@
     <x v="49"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="9.929"/>
-    <n v="4.337"/>
-    <n v="104"/>
+    <n v="11.893"/>
+    <n v="4.458"/>
+    <n v="95"/>
     <n v="5"/>
     <n v="2.7"/>
     <n v="0"/>
@@ -638,9 +650,9 @@
     <x v="13"/>
     <x v="0"/>
     <x v="1"/>
-    <n v="7.286"/>
-    <n v="3.376"/>
-    <n v="48"/>
+    <n v="6.929"/>
+    <n v="3.681"/>
+    <n v="51"/>
     <n v="3"/>
     <n v="3.3"/>
     <n v="0"/>
@@ -650,9 +662,9 @@
     <x v="3"/>
     <x v="2"/>
     <x v="0"/>
-    <n v="5.607"/>
-    <n v="3.01"/>
-    <n v="37"/>
+    <n v="5.107"/>
+    <n v="3.37"/>
+    <n v="45"/>
     <n v="90"/>
     <n v="3.9"/>
     <n v="0"/>
@@ -662,9 +674,9 @@
     <x v="16"/>
     <x v="2"/>
     <x v="2"/>
-    <n v="30.5"/>
-    <n v="14.658"/>
-    <n v="235"/>
+    <n v="31.321"/>
+    <n v="19.56"/>
+    <n v="238"/>
     <n v="365"/>
     <n v="2.15"/>
     <n v="0"/>
@@ -674,9 +686,9 @@
     <x v="10"/>
     <x v="2"/>
     <x v="2"/>
-    <n v="14.214"/>
-    <n v="4.879"/>
-    <n v="119"/>
+    <n v="14.071"/>
+    <n v="4.838"/>
+    <n v="127"/>
     <n v="270"/>
     <n v="2.3"/>
     <n v="0"/>
@@ -686,9 +698,9 @@
     <x v="42"/>
     <x v="2"/>
     <x v="2"/>
-    <n v="11.679"/>
-    <n v="3.982"/>
-    <n v="106"/>
+    <n v="11.964"/>
+    <n v="4.865"/>
+    <n v="105"/>
     <n v="365"/>
     <n v="1.1"/>
     <n v="0"/>
@@ -698,9 +710,9 @@
     <x v="24"/>
     <x v="2"/>
     <x v="4"/>
-    <n v="12.5"/>
-    <n v="4.726"/>
-    <n v="114"/>
+    <n v="12.929"/>
+    <n v="5.099"/>
+    <n v="121"/>
     <n v="30"/>
     <n v="2.7"/>
     <n v="0"/>
@@ -710,9 +722,9 @@
     <x v="26"/>
     <x v="2"/>
     <x v="13"/>
-    <n v="4.571"/>
-    <n v="2.755"/>
-    <n v="56"/>
+    <n v="4.857"/>
+    <n v="2.46"/>
+    <n v="54"/>
     <n v="120"/>
     <n v="2.6"/>
     <n v="0"/>
@@ -722,9 +734,9 @@
     <x v="2"/>
     <x v="2"/>
     <x v="2"/>
-    <n v="17.393"/>
-    <n v="5.101"/>
-    <n v="171"/>
+    <n v="18.071"/>
+    <n v="5.163"/>
+    <n v="177"/>
     <n v="365"/>
     <n v="0.95"/>
     <n v="0"/>
@@ -734,9 +746,9 @@
     <x v="4"/>
     <x v="3"/>
     <x v="4"/>
-    <n v="6.786"/>
-    <n v="4.677"/>
-    <n v="53"/>
+    <n v="6.714"/>
+    <n v="3.75"/>
+    <n v="46"/>
     <n v="60"/>
     <n v="5.6"/>
     <n v="0"/>
@@ -746,9 +758,9 @@
     <x v="20"/>
     <x v="3"/>
     <x v="4"/>
-    <n v="4.893"/>
-    <n v="2.299"/>
-    <n v="51"/>
+    <n v="4.179"/>
+    <n v="2.195"/>
+    <n v="43"/>
     <n v="21"/>
     <n v="5.1"/>
     <n v="0"/>
@@ -758,9 +770,9 @@
     <x v="6"/>
     <x v="3"/>
     <x v="4"/>
-    <n v="5.214"/>
-    <n v="2.378"/>
-    <n v="50"/>
+    <n v="6"/>
+    <n v="2.994"/>
+    <n v="42"/>
     <n v="90"/>
     <n v="10.4"/>
     <n v="0"/>
@@ -770,9 +782,9 @@
     <x v="23"/>
     <x v="5"/>
     <x v="7"/>
-    <n v="7.071"/>
-    <n v="3.126"/>
-    <n v="62"/>
+    <n v="6.536"/>
+    <n v="3.18"/>
+    <n v="63"/>
     <n v="365"/>
     <n v="5.4"/>
     <n v="0"/>
@@ -782,9 +794,9 @@
     <x v="22"/>
     <x v="5"/>
     <x v="7"/>
-    <n v="9.893000000000001"/>
-    <n v="3.975"/>
-    <n v="102"/>
+    <n v="11.393"/>
+    <n v="5.159"/>
+    <n v="90"/>
     <n v="365"/>
     <n v="1.2"/>
     <n v="0"/>
@@ -794,9 +806,9 @@
     <x v="19"/>
     <x v="5"/>
     <x v="7"/>
-    <n v="5.964"/>
-    <n v="3.361"/>
-    <n v="46"/>
+    <n v="6.25"/>
+    <n v="2.81"/>
+    <n v="41"/>
     <n v="365"/>
     <n v="4.7"/>
     <n v="0"/>
@@ -806,9 +818,9 @@
     <x v="18"/>
     <x v="5"/>
     <x v="0"/>
-    <n v="4.464"/>
-    <n v="2.457"/>
-    <n v="32"/>
+    <n v="4.786"/>
+    <n v="3.304"/>
+    <n v="36"/>
     <n v="365"/>
     <n v="7.1"/>
     <n v="0"/>
@@ -818,8 +830,8 @@
     <x v="7"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="19.357"/>
-    <n v="5.411"/>
+    <n v="20.357"/>
+    <n v="6.384"/>
     <n v="147"/>
     <n v="2"/>
     <n v="3.9"/>
@@ -830,9 +842,9 @@
     <x v="44"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="9.214"/>
-    <n v="3.224"/>
-    <n v="117"/>
+    <n v="11.75"/>
+    <n v="4.68"/>
+    <n v="108"/>
     <n v="1"/>
     <n v="5.6"/>
     <n v="0"/>
@@ -842,8 +854,8 @@
     <x v="21"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="18.143"/>
-    <n v="6.346"/>
+    <n v="16.75"/>
+    <n v="5.089"/>
     <n v="129"/>
     <n v="2"/>
     <n v="2.4"/>
@@ -854,9 +866,9 @@
     <x v="38"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="6.286"/>
-    <n v="2.637"/>
-    <n v="51"/>
+    <n v="5.464"/>
+    <n v="2.219"/>
+    <n v="52"/>
     <n v="2"/>
     <n v="6.2"/>
     <n v="0"/>
@@ -866,9 +878,9 @@
     <x v="17"/>
     <x v="4"/>
     <x v="6"/>
-    <n v="11"/>
-    <n v="4.823"/>
-    <n v="91"/>
+    <n v="10.536"/>
+    <n v="3.512"/>
+    <n v="98"/>
     <n v="2"/>
     <n v="3.2"/>
     <n v="0"/>
@@ -878,9 +890,9 @@
     <x v="25"/>
     <x v="6"/>
     <x v="0"/>
-    <n v="11.857"/>
-    <n v="4.369"/>
-    <n v="89"/>
+    <n v="14.393"/>
+    <n v="4.779"/>
+    <n v="101"/>
     <n v="365"/>
     <n v="2.6"/>
     <n v="0"/>
@@ -890,9 +902,9 @@
     <x v="5"/>
     <x v="6"/>
     <x v="11"/>
-    <n v="5.786"/>
-    <n v="3.201"/>
-    <n v="40"/>
+    <n v="5.75"/>
+    <n v="3.524"/>
+    <n v="34"/>
     <n v="730"/>
     <n v="1.9"/>
     <n v="0"/>
@@ -902,9 +914,9 @@
     <x v="33"/>
     <x v="6"/>
     <x v="11"/>
-    <n v="6.714"/>
-    <n v="3.041"/>
-    <n v="48"/>
+    <n v="5.929"/>
+    <n v="2.652"/>
+    <n v="55"/>
     <n v="730"/>
     <n v="1.3"/>
     <n v="0"/>
@@ -914,9 +926,9 @@
     <x v="41"/>
     <x v="6"/>
     <x v="11"/>
-    <n v="5"/>
-    <n v="2.553"/>
-    <n v="28"/>
+    <n v="5.321"/>
+    <n v="3.244"/>
+    <n v="29"/>
     <n v="540"/>
     <n v="2.3"/>
     <n v="1"/>
@@ -926,9 +938,9 @@
     <x v="39"/>
     <x v="6"/>
     <x v="9"/>
-    <n v="2.679"/>
-    <n v="2.389"/>
-    <n v="33"/>
+    <n v="3.429"/>
+    <n v="2.008"/>
+    <n v="36"/>
     <n v="365"/>
     <n v="2.9"/>
     <n v="0"/>
@@ -938,9 +950,9 @@
     <x v="45"/>
     <x v="6"/>
     <x v="9"/>
-    <n v="2.893"/>
-    <n v="1.524"/>
-    <n v="31"/>
+    <n v="3.536"/>
+    <n v="2.186"/>
+    <n v="30"/>
     <n v="365"/>
     <n v="4"/>
     <n v="0"/>
@@ -950,9 +962,9 @@
     <x v="15"/>
     <x v="6"/>
     <x v="5"/>
-    <n v="9.393000000000001"/>
-    <n v="3.573"/>
-    <n v="77"/>
+    <n v="9.893000000000001"/>
+    <n v="4.184"/>
+    <n v="80"/>
     <n v="35"/>
     <n v="8.199999999999999"/>
     <n v="0"/>
@@ -962,9 +974,9 @@
     <x v="9"/>
     <x v="6"/>
     <x v="11"/>
-    <n v="3.643"/>
-    <n v="2.147"/>
-    <n v="28"/>
+    <n v="3"/>
+    <n v="2.108"/>
+    <n v="20"/>
     <n v="180"/>
     <n v="7.6"/>
     <n v="0"/>
@@ -974,9 +986,9 @@
     <x v="47"/>
     <x v="8"/>
     <x v="8"/>
-    <n v="5.5"/>
-    <n v="2.411"/>
-    <n v="47"/>
+    <n v="4.357"/>
+    <n v="2.831"/>
+    <n v="44"/>
     <n v="3650"/>
     <n v="5.9"/>
     <n v="0"/>
@@ -986,23 +998,11 @@
     <x v="14"/>
     <x v="8"/>
     <x v="8"/>
-    <n v="2.107"/>
-    <n v="1.37"/>
-    <n v="23"/>
+    <n v="3.536"/>
+    <n v="2.027"/>
+    <n v="32"/>
     <n v="1095"/>
     <n v="2.9"/>
-    <n v="0"/>
-  </r>
-  <r>
-    <x v="32"/>
-    <x v="34"/>
-    <x v="8"/>
-    <x v="8"/>
-    <n v="0.643"/>
-    <n v="0.951"/>
-    <n v="9"/>
-    <n v="3650"/>
-    <n v="5.5"/>
     <n v="0"/>
   </r>
   <r>
@@ -1010,9 +1010,9 @@
     <x v="12"/>
     <x v="1"/>
     <x v="10"/>
-    <n v="4.857"/>
-    <n v="2.649"/>
-    <n v="49"/>
+    <n v="5.643"/>
+    <n v="3.423"/>
+    <n v="51"/>
     <n v="180"/>
     <n v="15.3"/>
     <n v="0"/>
@@ -1022,9 +1022,9 @@
     <x v="40"/>
     <x v="1"/>
     <x v="10"/>
-    <n v="5.286"/>
-    <n v="3.017"/>
-    <n v="54"/>
+    <n v="4.286"/>
+    <n v="2.813"/>
+    <n v="43"/>
     <n v="730"/>
     <n v="10.2"/>
     <n v="0"/>
@@ -1034,9 +1034,9 @@
     <x v="37"/>
     <x v="1"/>
     <x v="10"/>
-    <n v="3.857"/>
-    <n v="2.05"/>
-    <n v="42"/>
+    <n v="4.393"/>
+    <n v="2.409"/>
+    <n v="36"/>
     <n v="365"/>
     <n v="11.9"/>
     <n v="0"/>
@@ -1046,9 +1046,9 @@
     <x v="35"/>
     <x v="1"/>
     <x v="10"/>
-    <n v="1.929"/>
-    <n v="1.904"/>
-    <n v="14"/>
+    <n v="2.321"/>
+    <n v="1.926"/>
+    <n v="16"/>
     <n v="730"/>
     <n v="12.8"/>
     <n v="0"/>
@@ -1058,8 +1058,8 @@
     <x v="29"/>
     <x v="3"/>
     <x v="4"/>
-    <n v="34.286"/>
-    <n v="13.424"/>
+    <n v="34.393"/>
+    <n v="13.593"/>
     <n v="344"/>
     <n v="10"/>
     <n v="3.55"/>
@@ -1070,9 +1070,9 @@
     <x v="28"/>
     <x v="3"/>
     <x v="4"/>
-    <n v="14.607"/>
-    <n v="4.113"/>
-    <n v="145"/>
+    <n v="16.107"/>
+    <n v="3.975"/>
+    <n v="138"/>
     <n v="10"/>
     <n v="3.55"/>
     <n v="0"/>
@@ -1082,8 +1082,8 @@
     <x v="31"/>
     <x v="3"/>
     <x v="13"/>
-    <n v="8.071"/>
-    <n v="4.225"/>
+    <n v="6.679"/>
+    <n v="3.151"/>
     <n v="60"/>
     <n v="60"/>
     <n v="2.7"/>
@@ -1094,9 +1094,9 @@
     <x v="32"/>
     <x v="7"/>
     <x v="12"/>
-    <n v="5.357"/>
-    <n v="3.021"/>
-    <n v="38"/>
+    <n v="3.929"/>
+    <n v="2.493"/>
+    <n v="37"/>
     <n v="730"/>
     <n v="1.6"/>
     <n v="0"/>
@@ -1106,9 +1106,9 @@
     <x v="43"/>
     <x v="7"/>
     <x v="12"/>
-    <n v="1.714"/>
-    <n v="1.243"/>
-    <n v="17"/>
+    <n v="2.036"/>
+    <n v="1.666"/>
+    <n v="13"/>
     <n v="730"/>
     <n v="8.199999999999999"/>
     <n v="0"/>
@@ -1118,9 +1118,9 @@
     <x v="1"/>
     <x v="9"/>
     <x v="14"/>
-    <n v="31.607"/>
-    <n v="6.63"/>
-    <n v="270"/>
+    <n v="31.071"/>
+    <n v="7.717"/>
+    <n v="269"/>
     <n v="6"/>
     <n v="0.38"/>
     <n v="0"/>
@@ -1130,9 +1130,9 @@
     <x v="0"/>
     <x v="9"/>
     <x v="14"/>
-    <n v="8.071"/>
-    <n v="3.463"/>
-    <n v="69"/>
+    <n v="7.75"/>
+    <n v="3.384"/>
+    <n v="70"/>
     <n v="5"/>
     <n v="1.4"/>
     <n v="0"/>
@@ -1142,9 +1142,9 @@
     <x v="48"/>
     <x v="9"/>
     <x v="14"/>
-    <n v="4.5"/>
-    <n v="2.769"/>
-    <n v="48"/>
+    <n v="4.464"/>
+    <n v="2.912"/>
+    <n v="45"/>
     <n v="7"/>
     <n v="2.6"/>
     <n v="0"/>
@@ -1154,9 +1154,9 @@
     <x v="36"/>
     <x v="10"/>
     <x v="15"/>
-    <n v="20.679"/>
-    <n v="6.717"/>
-    <n v="170"/>
+    <n v="22.786"/>
+    <n v="6.551"/>
+    <n v="165"/>
     <n v="180"/>
     <n v="2.1"/>
     <n v="0"/>
@@ -1166,9 +1166,9 @@
     <x v="8"/>
     <x v="10"/>
     <x v="3"/>
-    <n v="15.821"/>
-    <n v="4.785"/>
-    <n v="106"/>
+    <n v="17.429"/>
+    <n v="5.196"/>
+    <n v="110"/>
     <n v="270"/>
     <n v="3.2"/>
     <n v="0"/>
@@ -1178,9 +1178,9 @@
     <x v="30"/>
     <x v="10"/>
     <x v="15"/>
-    <n v="9.356999999999999"/>
-    <n v="3.498"/>
-    <n v="74"/>
+    <n v="9.179"/>
+    <n v="3.443"/>
+    <n v="71"/>
     <n v="240"/>
     <n v="2.6"/>
     <n v="0"/>
@@ -1190,9 +1190,9 @@
     <x v="11"/>
     <x v="10"/>
     <x v="9"/>
-    <n v="9.143000000000001"/>
-    <n v="3.229"/>
-    <n v="74"/>
+    <n v="9.393000000000001"/>
+    <n v="3.224"/>
+    <n v="64"/>
     <n v="180"/>
     <n v="2.4"/>
     <n v="0"/>
@@ -1202,9 +1202,9 @@
     <x v="27"/>
     <x v="10"/>
     <x v="3"/>
-    <n v="10.107"/>
-    <n v="3.833"/>
-    <n v="83"/>
+    <n v="9.679"/>
+    <n v="3.682"/>
+    <n v="78"/>
     <n v="300"/>
     <n v="1.7"/>
     <n v="0"/>
@@ -1738,7 +1738,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Demo Neighbourhood Store (Eden Terrace format) · stock position at 04 Oct 2026</t>
+          <t>Demo Neighbourhood Store (Eden Terrace format) · stock position at 11 Oct 2026</t>
         </is>
       </c>
       <c r="C3" s="1" t="n"/>
@@ -1804,12 +1804,12 @@
     <row r="10">
       <c r="B10" s="10">
         <f>SUMIFS(Model!$L$8:$L$57,Model!$O$8:$O$57,1)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D10" s="9" t="n"/>
       <c r="E10" s="11">
         <f>COUNTIFS(Model!$K$8:$K$57,"&gt;0",Model!$O$8:$O$57,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="9" t="n"/>
       <c r="H10" s="11">
@@ -2059,23 +2059,23 @@
       </c>
       <c r="F8" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B8,Raw!$A$2:$A$51,0))</f>
-        <v>7.286</v>
+        <v>6.929</v>
       </c>
       <c r="G8" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B8,Raw!$A$2:$A$51,0))</f>
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="H8" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B8,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>9.64821581848167</v>
+        <v>10.5198703873907</v>
       </c>
       <c r="I8" s="15">
         <f>MIN(F8*(Assumptions!$C$6+Assumptions!$C$7)+H8,F8*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B8,Raw!$A$2:$A$51,0))))</f>
-        <v>21.858</v>
+        <v>20.787</v>
       </c>
       <c r="J8" s="15">
         <f>MIN(I8+F8*Assumptions!$C$7,F8*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B8,Raw!$A$2:$A$51,0))))</f>
-        <v>21.858</v>
+        <v>20.787</v>
       </c>
       <c r="K8" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B8,Raw!$A$2:$A$51,0))=1,G8&gt;I8),0,ROUNDUP(MAX(0,J8-G8),0))</f>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="M8" s="15">
         <f>IFERROR(G8/F8,0)</f>
-        <v>6.5879769420807</v>
+        <v>7.36036946168278</v>
       </c>
       <c r="N8" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B8,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M8&lt;Assumptions!$C$6,"Order now",IF(K8&gt;0,"Order","OK")))</f>
@@ -2118,23 +2118,23 @@
       </c>
       <c r="F9" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B9,Raw!$A$2:$A$51,0))</f>
-        <v>20.286</v>
+        <v>20.393</v>
       </c>
       <c r="G9" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B9,Raw!$A$2:$A$51,0))</f>
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H9" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B9,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>19.6593828836894</v>
+        <v>17.5874171051351</v>
       </c>
       <c r="I9" s="15">
         <f>MIN(F9*(Assumptions!$C$6+Assumptions!$C$7)+H9,F9*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B9,Raw!$A$2:$A$51,0))))</f>
-        <v>80.5173828836894</v>
+        <v>78.7664171051351</v>
       </c>
       <c r="J9" s="15">
         <f>MIN(I9+F9*Assumptions!$C$7,F9*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B9,Raw!$A$2:$A$51,0))))</f>
-        <v>100.803382883689</v>
+        <v>99.1594171051351</v>
       </c>
       <c r="K9" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B9,Raw!$A$2:$A$51,0))=1,G9&gt;I9),0,ROUNDUP(MAX(0,J9-G9),0))</f>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="M9" s="15">
         <f>IFERROR(G9/F9,0)</f>
-        <v>8.92240954352756</v>
+        <v>8.77752169862208</v>
       </c>
       <c r="N9" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B9,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M9&lt;Assumptions!$C$6,"Order now",IF(K9&gt;0,"Order","OK")))</f>
@@ -2177,23 +2177,23 @@
       </c>
       <c r="F10" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B10,Raw!$A$2:$A$51,0))</f>
-        <v>9.929</v>
+        <v>11.893</v>
       </c>
       <c r="G10" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B10,Raw!$A$2:$A$51,0))</f>
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="H10" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B10,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>12.3946421815033</v>
+        <v>12.7404461252344</v>
       </c>
       <c r="I10" s="15">
         <f>MIN(F10*(Assumptions!$C$6+Assumptions!$C$7)+H10,F10*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B10,Raw!$A$2:$A$51,0))))</f>
-        <v>42.1816421815033</v>
+        <v>48.4194461252344</v>
       </c>
       <c r="J10" s="15">
         <f>MIN(I10+F10*Assumptions!$C$7,F10*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B10,Raw!$A$2:$A$51,0))))</f>
-        <v>49.645</v>
+        <v>59.465</v>
       </c>
       <c r="K10" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B10,Raw!$A$2:$A$51,0))=1,G10&gt;I10),0,ROUNDUP(MAX(0,J10-G10),0))</f>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="M10" s="15">
         <f>IFERROR(G10/F10,0)</f>
-        <v>10.4743680128915</v>
+        <v>7.98789203733289</v>
       </c>
       <c r="N10" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B10,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M10&lt;Assumptions!$C$6,"Order now",IF(K10&gt;0,"Order","OK")))</f>
@@ -2236,23 +2236,23 @@
       </c>
       <c r="F11" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B11,Raw!$A$2:$A$51,0))</f>
-        <v>4.857</v>
+        <v>5.643</v>
       </c>
       <c r="G11" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B11,Raw!$A$2:$A$51,0))</f>
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H11" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B11,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.57053427226243</v>
+        <v>9.78253635860864</v>
       </c>
       <c r="I11" s="15">
         <f>MIN(F11*(Assumptions!$C$6+Assumptions!$C$7)+H11,F11*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B11,Raw!$A$2:$A$51,0))))</f>
-        <v>22.1415342722624</v>
+        <v>26.7115363586086</v>
       </c>
       <c r="J11" s="15">
         <f>MIN(I11+F11*Assumptions!$C$7,F11*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B11,Raw!$A$2:$A$51,0))))</f>
-        <v>26.9985342722624</v>
+        <v>32.3545363586086</v>
       </c>
       <c r="K11" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B11,Raw!$A$2:$A$51,0))=1,G11&gt;I11),0,ROUNDUP(MAX(0,J11-G11),0))</f>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M11" s="15">
         <f>IFERROR(G11/F11,0)</f>
-        <v>10.0885320156475</v>
+        <v>9.03774587985114</v>
       </c>
       <c r="N11" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B11,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M11&lt;Assumptions!$C$6,"Order now",IF(K11&gt;0,"Order","OK")))</f>
@@ -2295,23 +2295,23 @@
       </c>
       <c r="F12" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B12,Raw!$A$2:$A$51,0))</f>
-        <v>1.929</v>
+        <v>2.321</v>
       </c>
       <c r="G12" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B12,Raw!$A$2:$A$51,0))</f>
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H12" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B12,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>5.44141081705838</v>
+        <v>5.50428426137313</v>
       </c>
       <c r="I12" s="15">
         <f>MIN(F12*(Assumptions!$C$6+Assumptions!$C$7)+H12,F12*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B12,Raw!$A$2:$A$51,0))))</f>
-        <v>11.2284108170584</v>
+        <v>12.4672842613731</v>
       </c>
       <c r="J12" s="15">
         <f>MIN(I12+F12*Assumptions!$C$7,F12*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B12,Raw!$A$2:$A$51,0))))</f>
-        <v>13.1574108170584</v>
+        <v>14.7882842613731</v>
       </c>
       <c r="K12" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B12,Raw!$A$2:$A$51,0))=1,G12&gt;I12),0,ROUNDUP(MAX(0,J12-G12),0))</f>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="M12" s="15">
         <f>IFERROR(G12/F12,0)</f>
-        <v>7.25764644893727</v>
+        <v>6.89358035329599</v>
       </c>
       <c r="N12" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B12,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M12&lt;Assumptions!$C$6,"Order now",IF(K12&gt;0,"Order","OK")))</f>
@@ -2354,23 +2354,23 @@
       </c>
       <c r="F13" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B13,Raw!$A$2:$A$51,0))</f>
-        <v>3.857</v>
+        <v>4.393</v>
       </c>
       <c r="G13" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B13,Raw!$A$2:$A$51,0))</f>
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H13" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B13,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>5.85866185660173</v>
+        <v>6.88464215246515</v>
       </c>
       <c r="I13" s="15">
         <f>MIN(F13*(Assumptions!$C$6+Assumptions!$C$7)+H13,F13*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B13,Raw!$A$2:$A$51,0))))</f>
-        <v>17.4296618566017</v>
+        <v>20.0636421524652</v>
       </c>
       <c r="J13" s="15">
         <f>MIN(I13+F13*Assumptions!$C$7,F13*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B13,Raw!$A$2:$A$51,0))))</f>
-        <v>21.2866618566017</v>
+        <v>24.4566421524652</v>
       </c>
       <c r="K13" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B13,Raw!$A$2:$A$51,0))=1,G13&gt;I13),0,ROUNDUP(MAX(0,J13-G13),0))</f>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="M13" s="15">
         <f>IFERROR(G13/F13,0)</f>
-        <v>10.8892921960073</v>
+        <v>8.19485545185522</v>
       </c>
       <c r="N13" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B13,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M13&lt;Assumptions!$C$6,"Order now",IF(K13&gt;0,"Order","OK")))</f>
@@ -2413,23 +2413,23 @@
       </c>
       <c r="F14" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B14,Raw!$A$2:$A$51,0))</f>
-        <v>5.286</v>
+        <v>4.286</v>
       </c>
       <c r="G14" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B14,Raw!$A$2:$A$51,0))</f>
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H14" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B14,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.62223552261825</v>
+        <v>8.03922722079057</v>
       </c>
       <c r="I14" s="15">
         <f>MIN(F14*(Assumptions!$C$6+Assumptions!$C$7)+H14,F14*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B14,Raw!$A$2:$A$51,0))))</f>
-        <v>24.4802355226182</v>
+        <v>20.8972272207906</v>
       </c>
       <c r="J14" s="15">
         <f>MIN(I14+F14*Assumptions!$C$7,F14*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B14,Raw!$A$2:$A$51,0))))</f>
-        <v>29.7662355226182</v>
+        <v>25.1832272207906</v>
       </c>
       <c r="K14" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B14,Raw!$A$2:$A$51,0))=1,G14&gt;I14),0,ROUNDUP(MAX(0,J14-G14),0))</f>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="M14" s="15">
         <f>IFERROR(G14/F14,0)</f>
-        <v>10.2156640181612</v>
+        <v>10.0326644890341</v>
       </c>
       <c r="N14" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B14,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M14&lt;Assumptions!$C$6,"Order now",IF(K14&gt;0,"Order","OK")))</f>
@@ -2472,23 +2472,23 @@
       </c>
       <c r="F15" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B15,Raw!$A$2:$A$51,0))</f>
-        <v>17.393</v>
+        <v>18.071</v>
       </c>
       <c r="G15" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B15,Raw!$A$2:$A$51,0))</f>
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H15" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B15,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>14.5780654295246</v>
+        <v>14.7552542271389</v>
       </c>
       <c r="I15" s="15">
         <f>MIN(F15*(Assumptions!$C$6+Assumptions!$C$7)+H15,F15*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B15,Raw!$A$2:$A$51,0))))</f>
-        <v>66.7570654295246</v>
+        <v>68.9682542271389</v>
       </c>
       <c r="J15" s="15">
         <f>MIN(I15+F15*Assumptions!$C$7,F15*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B15,Raw!$A$2:$A$51,0))))</f>
-        <v>84.1500654295246</v>
+        <v>87.0392542271389</v>
       </c>
       <c r="K15" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B15,Raw!$A$2:$A$51,0))=1,G15&gt;I15),0,ROUNDUP(MAX(0,J15-G15),0))</f>
@@ -2500,7 +2500,7 @@
       </c>
       <c r="M15" s="15">
         <f>IFERROR(G15/F15,0)</f>
-        <v>9.83154142471109</v>
+        <v>9.79469868850645</v>
       </c>
       <c r="N15" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B15,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M15&lt;Assumptions!$C$6,"Order now",IF(K15&gt;0,"Order","OK")))</f>
@@ -2531,23 +2531,23 @@
       </c>
       <c r="F16" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B16,Raw!$A$2:$A$51,0))</f>
-        <v>5.607</v>
+        <v>5.107</v>
       </c>
       <c r="G16" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B16,Raw!$A$2:$A$51,0))</f>
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H16" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B16,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.60223033579083</v>
+        <v>9.63106851548674</v>
       </c>
       <c r="I16" s="15">
         <f>MIN(F16*(Assumptions!$C$6+Assumptions!$C$7)+H16,F16*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B16,Raw!$A$2:$A$51,0))))</f>
-        <v>25.4232303357908</v>
+        <v>24.9520685154867</v>
       </c>
       <c r="J16" s="15">
         <f>MIN(I16+F16*Assumptions!$C$7,F16*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B16,Raw!$A$2:$A$51,0))))</f>
-        <v>31.0302303357908</v>
+        <v>30.0590685154867</v>
       </c>
       <c r="K16" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B16,Raw!$A$2:$A$51,0))=1,G16&gt;I16),0,ROUNDUP(MAX(0,J16-G16),0))</f>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="M16" s="15">
         <f>IFERROR(G16/F16,0)</f>
-        <v>6.59889423934368</v>
+        <v>8.81143528490307</v>
       </c>
       <c r="N16" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B16,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M16&lt;Assumptions!$C$6,"Order now",IF(K16&gt;0,"Order","OK")))</f>
@@ -2590,23 +2590,23 @@
       </c>
       <c r="F17" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B17,Raw!$A$2:$A$51,0))</f>
-        <v>14.214</v>
+        <v>14.071</v>
       </c>
       <c r="G17" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B17,Raw!$A$2:$A$51,0))</f>
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="H17" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B17,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.9436152187121</v>
+        <v>13.8264419815801</v>
       </c>
       <c r="I17" s="15">
         <f>MIN(F17*(Assumptions!$C$6+Assumptions!$C$7)+H17,F17*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B17,Raw!$A$2:$A$51,0))))</f>
-        <v>56.5856152187121</v>
+        <v>56.0394419815801</v>
       </c>
       <c r="J17" s="15">
         <f>MIN(I17+F17*Assumptions!$C$7,F17*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B17,Raw!$A$2:$A$51,0))))</f>
-        <v>70.7996152187121</v>
+        <v>70.1104419815801</v>
       </c>
       <c r="K17" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B17,Raw!$A$2:$A$51,0))=1,G17&gt;I17),0,ROUNDUP(MAX(0,J17-G17),0))</f>
@@ -2618,7 +2618,7 @@
       </c>
       <c r="M17" s="15">
         <f>IFERROR(G17/F17,0)</f>
-        <v>8.37202757844379</v>
+        <v>9.02565560372397</v>
       </c>
       <c r="N17" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B17,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M17&lt;Assumptions!$C$6,"Order now",IF(K17&gt;0,"Order","OK")))</f>
@@ -2649,23 +2649,23 @@
       </c>
       <c r="F18" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B18,Raw!$A$2:$A$51,0))</f>
-        <v>30.5</v>
+        <v>31.321</v>
       </c>
       <c r="G18" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B18,Raw!$A$2:$A$51,0))</f>
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="H18" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B18,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>41.8908612166186</v>
+        <v>55.9002077634779</v>
       </c>
       <c r="I18" s="15">
         <f>MIN(F18*(Assumptions!$C$6+Assumptions!$C$7)+H18,F18*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B18,Raw!$A$2:$A$51,0))))</f>
-        <v>133.390861216619</v>
+        <v>149.863207763478</v>
       </c>
       <c r="J18" s="15">
         <f>MIN(I18+F18*Assumptions!$C$7,F18*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B18,Raw!$A$2:$A$51,0))))</f>
-        <v>163.890861216619</v>
+        <v>181.184207763478</v>
       </c>
       <c r="K18" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B18,Raw!$A$2:$A$51,0))=1,G18&gt;I18),0,ROUNDUP(MAX(0,J18-G18),0))</f>
@@ -2677,7 +2677,7 @@
       </c>
       <c r="M18" s="15">
         <f>IFERROR(G18/F18,0)</f>
-        <v>7.70491803278689</v>
+        <v>7.59873567255196</v>
       </c>
       <c r="N18" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B18,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M18&lt;Assumptions!$C$6,"Order now",IF(K18&gt;0,"Order","OK")))</f>
@@ -2708,23 +2708,23 @@
       </c>
       <c r="F19" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B19,Raw!$A$2:$A$51,0))</f>
-        <v>12.5</v>
+        <v>12.929</v>
       </c>
       <c r="G19" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B19,Raw!$A$2:$A$51,0))</f>
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="H19" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B19,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.5063589923413</v>
+        <v>14.5723496618596</v>
       </c>
       <c r="I19" s="15">
         <f>MIN(F19*(Assumptions!$C$6+Assumptions!$C$7)+H19,F19*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B19,Raw!$A$2:$A$51,0))))</f>
-        <v>51.0063589923414</v>
+        <v>53.3593496618596</v>
       </c>
       <c r="J19" s="15">
         <f>MIN(I19+F19*Assumptions!$C$7,F19*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B19,Raw!$A$2:$A$51,0))))</f>
-        <v>63.5063589923414</v>
+        <v>66.2883496618596</v>
       </c>
       <c r="K19" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B19,Raw!$A$2:$A$51,0))=1,G19&gt;I19),0,ROUNDUP(MAX(0,J19-G19),0))</f>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="M19" s="15">
         <f>IFERROR(G19/F19,0)</f>
-        <v>9.12</v>
+        <v>9.35880578544358</v>
       </c>
       <c r="N19" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B19,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M19&lt;Assumptions!$C$6,"Order now",IF(K19&gt;0,"Order","OK")))</f>
@@ -2767,23 +2767,23 @@
       </c>
       <c r="F20" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B20,Raw!$A$2:$A$51,0))</f>
-        <v>4.571</v>
+        <v>4.857</v>
       </c>
       <c r="G20" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B20,Raw!$A$2:$A$51,0))</f>
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H20" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B20,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.87346995850622</v>
+        <v>7.03039422792207</v>
       </c>
       <c r="I20" s="15">
         <f>MIN(F20*(Assumptions!$C$6+Assumptions!$C$7)+H20,F20*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B20,Raw!$A$2:$A$51,0))))</f>
-        <v>21.5864699585062</v>
+        <v>21.6013942279221</v>
       </c>
       <c r="J20" s="15">
         <f>MIN(I20+F20*Assumptions!$C$7,F20*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B20,Raw!$A$2:$A$51,0))))</f>
-        <v>26.1574699585062</v>
+        <v>26.4583942279221</v>
       </c>
       <c r="K20" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B20,Raw!$A$2:$A$51,0))=1,G20&gt;I20),0,ROUNDUP(MAX(0,J20-G20),0))</f>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="M20" s="15">
         <f>IFERROR(G20/F20,0)</f>
-        <v>12.2511485451761</v>
+        <v>11.1179740580605</v>
       </c>
       <c r="N20" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B20,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M20&lt;Assumptions!$C$6,"Order now",IF(K20&gt;0,"Order","OK")))</f>
@@ -2826,23 +2826,23 @@
       </c>
       <c r="F21" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B21,Raw!$A$2:$A$51,0))</f>
-        <v>11.679</v>
+        <v>11.964</v>
       </c>
       <c r="G21" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B21,Raw!$A$2:$A$51,0))</f>
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="H21" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B21,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>11.3800934209698</v>
+        <v>13.9036048450573</v>
       </c>
       <c r="I21" s="15">
         <f>MIN(F21*(Assumptions!$C$6+Assumptions!$C$7)+H21,F21*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B21,Raw!$A$2:$A$51,0))))</f>
-        <v>46.4170934209698</v>
+        <v>49.7956048450573</v>
       </c>
       <c r="J21" s="15">
         <f>MIN(I21+F21*Assumptions!$C$7,F21*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B21,Raw!$A$2:$A$51,0))))</f>
-        <v>58.0960934209698</v>
+        <v>61.7596048450573</v>
       </c>
       <c r="K21" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B21,Raw!$A$2:$A$51,0))=1,G21&gt;I21),0,ROUNDUP(MAX(0,J21-G21),0))</f>
@@ -2854,7 +2854,7 @@
       </c>
       <c r="M21" s="15">
         <f>IFERROR(G21/F21,0)</f>
-        <v>9.07611953078174</v>
+        <v>8.77632898696088</v>
       </c>
       <c r="N21" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B21,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M21&lt;Assumptions!$C$6,"Order now",IF(K21&gt;0,"Order","OK")))</f>
@@ -2885,23 +2885,23 @@
       </c>
       <c r="F22" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B22,Raw!$A$2:$A$51,0))</f>
-        <v>6.786</v>
+        <v>6.714</v>
       </c>
       <c r="G22" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B22,Raw!$A$2:$A$51,0))</f>
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="H22" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B22,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.3663226845494</v>
+        <v>10.7170643718324</v>
       </c>
       <c r="I22" s="15">
         <f>MIN(F22*(Assumptions!$C$6+Assumptions!$C$7)+H22,F22*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B22,Raw!$A$2:$A$51,0))))</f>
-        <v>33.7243226845494</v>
+        <v>30.8590643718324</v>
       </c>
       <c r="J22" s="15">
         <f>MIN(I22+F22*Assumptions!$C$7,F22*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B22,Raw!$A$2:$A$51,0))))</f>
-        <v>40.5103226845494</v>
+        <v>37.5730643718324</v>
       </c>
       <c r="K22" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B22,Raw!$A$2:$A$51,0))=1,G22&gt;I22),0,ROUNDUP(MAX(0,J22-G22),0))</f>
@@ -2913,7 +2913,7 @@
       </c>
       <c r="M22" s="15">
         <f>IFERROR(G22/F22,0)</f>
-        <v>7.81019746536988</v>
+        <v>6.85135537682455</v>
       </c>
       <c r="N22" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B22,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M22&lt;Assumptions!$C$6,"Order now",IF(K22&gt;0,"Order","OK")))</f>
@@ -2944,23 +2944,23 @@
       </c>
       <c r="F23" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B23,Raw!$A$2:$A$51,0))</f>
-        <v>5.214</v>
+        <v>6</v>
       </c>
       <c r="G23" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B23,Raw!$A$2:$A$51,0))</f>
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H23" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B23,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.796047753658</v>
+        <v>8.55650419447101</v>
       </c>
       <c r="I23" s="15">
         <f>MIN(F23*(Assumptions!$C$6+Assumptions!$C$7)+H23,F23*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B23,Raw!$A$2:$A$51,0))))</f>
-        <v>22.438047753658</v>
+        <v>26.556504194471</v>
       </c>
       <c r="J23" s="15">
         <f>MIN(I23+F23*Assumptions!$C$7,F23*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B23,Raw!$A$2:$A$51,0))))</f>
-        <v>27.652047753658</v>
+        <v>32.556504194471</v>
       </c>
       <c r="K23" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B23,Raw!$A$2:$A$51,0))=1,G23&gt;I23),0,ROUNDUP(MAX(0,J23-G23),0))</f>
@@ -2972,7 +2972,7 @@
       </c>
       <c r="M23" s="15">
         <f>IFERROR(G23/F23,0)</f>
-        <v>9.58956655159187</v>
+        <v>7</v>
       </c>
       <c r="N23" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B23,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M23&lt;Assumptions!$C$6,"Order now",IF(K23&gt;0,"Order","OK")))</f>
@@ -3003,23 +3003,23 @@
       </c>
       <c r="F24" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B24,Raw!$A$2:$A$51,0))</f>
-        <v>4.893</v>
+        <v>4.179</v>
       </c>
       <c r="G24" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B24,Raw!$A$2:$A$51,0))</f>
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H24" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B24,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.5702749308914</v>
+        <v>6.27305501231258</v>
       </c>
       <c r="I24" s="15">
         <f>MIN(F24*(Assumptions!$C$6+Assumptions!$C$7)+H24,F24*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B24,Raw!$A$2:$A$51,0))))</f>
-        <v>21.2492749308914</v>
+        <v>18.8100550123126</v>
       </c>
       <c r="J24" s="15">
         <f>MIN(I24+F24*Assumptions!$C$7,F24*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B24,Raw!$A$2:$A$51,0))))</f>
-        <v>26.1422749308914</v>
+        <v>22.9890550123126</v>
       </c>
       <c r="K24" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B24,Raw!$A$2:$A$51,0))=1,G24&gt;I24),0,ROUNDUP(MAX(0,J24-G24),0))</f>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="M24" s="15">
         <f>IFERROR(G24/F24,0)</f>
-        <v>10.4230533415083</v>
+        <v>10.2895429528595</v>
       </c>
       <c r="N24" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B24,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M24&lt;Assumptions!$C$6,"Order now",IF(K24&gt;0,"Order","OK")))</f>
@@ -3062,23 +3062,23 @@
       </c>
       <c r="F25" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B25,Raw!$A$2:$A$51,0))</f>
-        <v>14.607</v>
+        <v>16.107</v>
       </c>
       <c r="G25" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B25,Raw!$A$2:$A$51,0))</f>
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H25" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B25,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>11.7544762030258</v>
+        <v>11.3600882341424</v>
       </c>
       <c r="I25" s="15">
         <f>MIN(F25*(Assumptions!$C$6+Assumptions!$C$7)+H25,F25*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B25,Raw!$A$2:$A$51,0))))</f>
-        <v>55.5754762030258</v>
+        <v>59.6810882341424</v>
       </c>
       <c r="J25" s="15">
         <f>MIN(I25+F25*Assumptions!$C$7,F25*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B25,Raw!$A$2:$A$51,0))))</f>
-        <v>70.1824762030258</v>
+        <v>75.7880882341424</v>
       </c>
       <c r="K25" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B25,Raw!$A$2:$A$51,0))=1,G25&gt;I25),0,ROUNDUP(MAX(0,J25-G25),0))</f>
@@ -3090,7 +3090,7 @@
       </c>
       <c r="M25" s="15">
         <f>IFERROR(G25/F25,0)</f>
-        <v>9.92674744985281</v>
+        <v>8.56770348295772</v>
       </c>
       <c r="N25" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B25,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M25&lt;Assumptions!$C$6,"Order now",IF(K25&gt;0,"Order","OK")))</f>
@@ -3121,7 +3121,7 @@
       </c>
       <c r="F26" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B26,Raw!$A$2:$A$51,0))</f>
-        <v>34.286</v>
+        <v>34.393</v>
       </c>
       <c r="G26" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B26,Raw!$A$2:$A$51,0))</f>
@@ -3129,15 +3129,15 @@
       </c>
       <c r="H26" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B26,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>38.3642325673276</v>
+        <v>38.8472149350182</v>
       </c>
       <c r="I26" s="15">
         <f>MIN(F26*(Assumptions!$C$6+Assumptions!$C$7)+H26,F26*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B26,Raw!$A$2:$A$51,0))))</f>
-        <v>141.222232567328</v>
+        <v>142.026214935018</v>
       </c>
       <c r="J26" s="15">
         <f>MIN(I26+F26*Assumptions!$C$7,F26*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B26,Raw!$A$2:$A$51,0))))</f>
-        <v>175.508232567328</v>
+        <v>176.419214935018</v>
       </c>
       <c r="K26" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B26,Raw!$A$2:$A$51,0))=1,G26&gt;I26),0,ROUNDUP(MAX(0,J26-G26),0))</f>
@@ -3149,7 +3149,7 @@
       </c>
       <c r="M26" s="15">
         <f>IFERROR(G26/F26,0)</f>
-        <v>10.033249722919</v>
+        <v>10.0020352978804</v>
       </c>
       <c r="N26" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B26,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M26&lt;Assumptions!$C$6,"Order now",IF(K26&gt;0,"Order","OK")))</f>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="F27" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B27,Raw!$A$2:$A$51,0))</f>
-        <v>8.071</v>
+        <v>6.679</v>
       </c>
       <c r="G27" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B27,Raw!$A$2:$A$51,0))</f>
@@ -3188,15 +3188,15 @@
       </c>
       <c r="H27" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B27,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>12.0745591922645</v>
+        <v>9.00519195617173</v>
       </c>
       <c r="I27" s="15">
         <f>MIN(F27*(Assumptions!$C$6+Assumptions!$C$7)+H27,F27*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B27,Raw!$A$2:$A$51,0))))</f>
-        <v>36.2875591922645</v>
+        <v>29.0421919561717</v>
       </c>
       <c r="J27" s="15">
         <f>MIN(I27+F27*Assumptions!$C$7,F27*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B27,Raw!$A$2:$A$51,0))))</f>
-        <v>44.3585591922645</v>
+        <v>35.7211919561717</v>
       </c>
       <c r="K27" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B27,Raw!$A$2:$A$51,0))=1,G27&gt;I27),0,ROUNDUP(MAX(0,J27-G27),0))</f>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="M27" s="15">
         <f>IFERROR(G27/F27,0)</f>
-        <v>7.43402304547144</v>
+        <v>8.9833807456206</v>
       </c>
       <c r="N27" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B27,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M27&lt;Assumptions!$C$6,"Order now",IF(K27&gt;0,"Order","OK")))</f>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="F28" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B28,Raw!$A$2:$A$51,0))</f>
-        <v>19.357</v>
+        <v>20.357</v>
       </c>
       <c r="G28" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B28,Raw!$A$2:$A$51,0))</f>
@@ -3247,15 +3247,15 @@
       </c>
       <c r="H28" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B28,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>15.4640094175961</v>
+        <v>18.2447303866075</v>
       </c>
       <c r="I28" s="15">
         <f>MIN(F28*(Assumptions!$C$6+Assumptions!$C$7)+H28,F28*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B28,Raw!$A$2:$A$51,0))))</f>
-        <v>38.714</v>
+        <v>40.714</v>
       </c>
       <c r="J28" s="15">
         <f>MIN(I28+F28*Assumptions!$C$7,F28*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B28,Raw!$A$2:$A$51,0))))</f>
-        <v>38.714</v>
+        <v>40.714</v>
       </c>
       <c r="K28" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B28,Raw!$A$2:$A$51,0))=1,G28&gt;I28),0,ROUNDUP(MAX(0,J28-G28),0))</f>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="M28" s="15">
         <f>IFERROR(G28/F28,0)</f>
-        <v>7.59415198636152</v>
+        <v>7.22110330598811</v>
       </c>
       <c r="N28" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B28,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M28&lt;Assumptions!$C$6,"Order now",IF(K28&gt;0,"Order","OK")))</f>
@@ -3298,23 +3298,23 @@
       </c>
       <c r="F29" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B29,Raw!$A$2:$A$51,0))</f>
-        <v>11</v>
+        <v>10.536</v>
       </c>
       <c r="G29" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B29,Raw!$A$2:$A$51,0))</f>
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H29" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B29,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.7835737240927</v>
+        <v>10.0368880197001</v>
       </c>
       <c r="I29" s="15">
         <f>MIN(F29*(Assumptions!$C$6+Assumptions!$C$7)+H29,F29*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B29,Raw!$A$2:$A$51,0))))</f>
-        <v>22</v>
+        <v>21.072</v>
       </c>
       <c r="J29" s="15">
         <f>MIN(I29+F29*Assumptions!$C$7,F29*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B29,Raw!$A$2:$A$51,0))))</f>
-        <v>22</v>
+        <v>21.072</v>
       </c>
       <c r="K29" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B29,Raw!$A$2:$A$51,0))=1,G29&gt;I29),0,ROUNDUP(MAX(0,J29-G29),0))</f>
@@ -3326,7 +3326,7 @@
       </c>
       <c r="M29" s="15">
         <f>IFERROR(G29/F29,0)</f>
-        <v>8.27272727272727</v>
+        <v>9.30144267274108</v>
       </c>
       <c r="N29" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B29,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M29&lt;Assumptions!$C$6,"Order now",IF(K29&gt;0,"Order","OK")))</f>
@@ -3357,7 +3357,7 @@
       </c>
       <c r="F30" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B30,Raw!$A$2:$A$51,0))</f>
-        <v>18.143</v>
+        <v>16.75</v>
       </c>
       <c r="G30" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B30,Raw!$A$2:$A$51,0))</f>
@@ -3365,15 +3365,15 @@
       </c>
       <c r="H30" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B30,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>18.136130800973</v>
+        <v>14.5437708235347</v>
       </c>
       <c r="I30" s="15">
         <f>MIN(F30*(Assumptions!$C$6+Assumptions!$C$7)+H30,F30*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B30,Raw!$A$2:$A$51,0))))</f>
-        <v>36.286</v>
+        <v>33.5</v>
       </c>
       <c r="J30" s="15">
         <f>MIN(I30+F30*Assumptions!$C$7,F30*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B30,Raw!$A$2:$A$51,0))))</f>
-        <v>36.286</v>
+        <v>33.5</v>
       </c>
       <c r="K30" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B30,Raw!$A$2:$A$51,0))=1,G30&gt;I30),0,ROUNDUP(MAX(0,J30-G30),0))</f>
@@ -3385,7 +3385,7 @@
       </c>
       <c r="M30" s="15">
         <f>IFERROR(G30/F30,0)</f>
-        <v>7.1101802348013</v>
+        <v>7.70149253731343</v>
       </c>
       <c r="N30" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B30,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M30&lt;Assumptions!$C$6,"Order now",IF(K30&gt;0,"Order","OK")))</f>
@@ -3416,23 +3416,23 @@
       </c>
       <c r="F31" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B31,Raw!$A$2:$A$51,0))</f>
-        <v>6.286</v>
+        <v>5.464</v>
       </c>
       <c r="G31" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B31,Raw!$A$2:$A$51,0))</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H31" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B31,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.53623966627256</v>
+        <v>6.34164422429231</v>
       </c>
       <c r="I31" s="15">
         <f>MIN(F31*(Assumptions!$C$6+Assumptions!$C$7)+H31,F31*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B31,Raw!$A$2:$A$51,0))))</f>
-        <v>12.572</v>
+        <v>10.928</v>
       </c>
       <c r="J31" s="15">
         <f>MIN(I31+F31*Assumptions!$C$7,F31*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B31,Raw!$A$2:$A$51,0))))</f>
-        <v>12.572</v>
+        <v>10.928</v>
       </c>
       <c r="K31" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B31,Raw!$A$2:$A$51,0))=1,G31&gt;I31),0,ROUNDUP(MAX(0,J31-G31),0))</f>
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M31" s="15">
         <f>IFERROR(G31/F31,0)</f>
-        <v>8.11326757874642</v>
+        <v>9.51683748169839</v>
       </c>
       <c r="N31" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B31,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M31&lt;Assumptions!$C$6,"Order now",IF(K31&gt;0,"Order","OK")))</f>
@@ -3475,23 +3475,23 @@
       </c>
       <c r="F32" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B32,Raw!$A$2:$A$51,0))</f>
-        <v>9.214</v>
+        <v>11.75</v>
       </c>
       <c r="G32" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B32,Raw!$A$2:$A$51,0))</f>
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H32" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B32,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>9.2138174759434</v>
+        <v>13.3748963360469</v>
       </c>
       <c r="I32" s="15">
         <f>MIN(F32*(Assumptions!$C$6+Assumptions!$C$7)+H32,F32*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B32,Raw!$A$2:$A$51,0))))</f>
-        <v>9.214</v>
+        <v>11.75</v>
       </c>
       <c r="J32" s="15">
         <f>MIN(I32+F32*Assumptions!$C$7,F32*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B32,Raw!$A$2:$A$51,0))))</f>
-        <v>9.214</v>
+        <v>11.75</v>
       </c>
       <c r="K32" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B32,Raw!$A$2:$A$51,0))=1,G32&gt;I32),0,ROUNDUP(MAX(0,J32-G32),0))</f>
@@ -3503,7 +3503,7 @@
       </c>
       <c r="M32" s="15">
         <f>IFERROR(G32/F32,0)</f>
-        <v>12.6980681571522</v>
+        <v>9.19148936170213</v>
       </c>
       <c r="N32" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B32,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M32&lt;Assumptions!$C$6,"Order now",IF(K32&gt;0,"Order","OK")))</f>
@@ -3534,23 +3534,23 @@
       </c>
       <c r="F33" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B33,Raw!$A$2:$A$51,0))</f>
-        <v>4.464</v>
+        <v>4.786</v>
       </c>
       <c r="G33" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B33,Raw!$A$2:$A$51,0))</f>
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H33" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B33,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.02182057642461</v>
+        <v>9.44244818254249</v>
       </c>
       <c r="I33" s="15">
         <f>MIN(F33*(Assumptions!$C$6+Assumptions!$C$7)+H33,F33*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B33,Raw!$A$2:$A$51,0))))</f>
-        <v>20.4138205764246</v>
+        <v>23.8004481825425</v>
       </c>
       <c r="J33" s="15">
         <f>MIN(I33+F33*Assumptions!$C$7,F33*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B33,Raw!$A$2:$A$51,0))))</f>
-        <v>24.8778205764246</v>
+        <v>28.5864481825425</v>
       </c>
       <c r="K33" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B33,Raw!$A$2:$A$51,0))=1,G33&gt;I33),0,ROUNDUP(MAX(0,J33-G33),0))</f>
@@ -3562,7 +3562,7 @@
       </c>
       <c r="M33" s="15">
         <f>IFERROR(G33/F33,0)</f>
-        <v>7.16845878136201</v>
+        <v>7.52193898871709</v>
       </c>
       <c r="N33" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B33,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M33&lt;Assumptions!$C$6,"Order now",IF(K33&gt;0,"Order","OK")))</f>
@@ -3593,23 +3593,23 @@
       </c>
       <c r="F34" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B34,Raw!$A$2:$A$51,0))</f>
-        <v>5.964</v>
+        <v>6.25</v>
       </c>
       <c r="G34" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B34,Raw!$A$2:$A$51,0))</f>
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="H34" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B34,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>9.60534756099434</v>
+        <v>8.0306535692931</v>
       </c>
       <c r="I34" s="15">
         <f>MIN(F34*(Assumptions!$C$6+Assumptions!$C$7)+H34,F34*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B34,Raw!$A$2:$A$51,0))))</f>
-        <v>27.4973475609944</v>
+        <v>26.7806535692931</v>
       </c>
       <c r="J34" s="15">
         <f>MIN(I34+F34*Assumptions!$C$7,F34*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B34,Raw!$A$2:$A$51,0))))</f>
-        <v>33.4613475609944</v>
+        <v>33.0306535692931</v>
       </c>
       <c r="K34" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B34,Raw!$A$2:$A$51,0))=1,G34&gt;I34),0,ROUNDUP(MAX(0,J34-G34),0))</f>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="M34" s="15">
         <f>IFERROR(G34/F34,0)</f>
-        <v>7.71294433266264</v>
+        <v>6.56</v>
       </c>
       <c r="N34" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B34,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M34&lt;Assumptions!$C$6,"Order now",IF(K34&gt;0,"Order","OK")))</f>
@@ -3652,23 +3652,23 @@
       </c>
       <c r="F35" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B35,Raw!$A$2:$A$51,0))</f>
-        <v>9.893</v>
+        <v>11.393</v>
       </c>
       <c r="G35" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B35,Raw!$A$2:$A$51,0))</f>
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="H35" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B35,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>11.3600882341424</v>
+        <v>14.7438226918089</v>
       </c>
       <c r="I35" s="15">
         <f>MIN(F35*(Assumptions!$C$6+Assumptions!$C$7)+H35,F35*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B35,Raw!$A$2:$A$51,0))))</f>
-        <v>41.0390882341424</v>
+        <v>48.9228226918089</v>
       </c>
       <c r="J35" s="15">
         <f>MIN(I35+F35*Assumptions!$C$7,F35*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B35,Raw!$A$2:$A$51,0))))</f>
-        <v>50.9320882341424</v>
+        <v>60.3158226918089</v>
       </c>
       <c r="K35" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B35,Raw!$A$2:$A$51,0))=1,G35&gt;I35),0,ROUNDUP(MAX(0,J35-G35),0))</f>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="M35" s="15">
         <f>IFERROR(G35/F35,0)</f>
-        <v>10.3103204285859</v>
+        <v>7.89958746598789</v>
       </c>
       <c r="N35" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B35,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M35&lt;Assumptions!$C$6,"Order now",IF(K35&gt;0,"Order","OK")))</f>
@@ -3711,23 +3711,23 @@
       </c>
       <c r="F36" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B36,Raw!$A$2:$A$51,0))</f>
-        <v>7.071</v>
+        <v>6.536</v>
       </c>
       <c r="G36" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B36,Raw!$A$2:$A$51,0))</f>
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H36" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B36,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.93374486035951</v>
+        <v>9.0880705873139</v>
       </c>
       <c r="I36" s="15">
         <f>MIN(F36*(Assumptions!$C$6+Assumptions!$C$7)+H36,F36*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B36,Raw!$A$2:$A$51,0))))</f>
-        <v>30.1467448603595</v>
+        <v>28.6960705873139</v>
       </c>
       <c r="J36" s="15">
         <f>MIN(I36+F36*Assumptions!$C$7,F36*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B36,Raw!$A$2:$A$51,0))))</f>
-        <v>37.2177448603595</v>
+        <v>35.2320705873139</v>
       </c>
       <c r="K36" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B36,Raw!$A$2:$A$51,0))=1,G36&gt;I36),0,ROUNDUP(MAX(0,J36-G36),0))</f>
@@ -3739,7 +3739,7 @@
       </c>
       <c r="M36" s="15">
         <f>IFERROR(G36/F36,0)</f>
-        <v>8.76820817423278</v>
+        <v>9.63892288861689</v>
       </c>
       <c r="N36" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B36,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M36&lt;Assumptions!$C$6,"Order now",IF(K36&gt;0,"Order","OK")))</f>
@@ -3770,23 +3770,23 @@
       </c>
       <c r="F37" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B37,Raw!$A$2:$A$51,0))</f>
-        <v>5.786</v>
+        <v>5.75</v>
       </c>
       <c r="G37" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B37,Raw!$A$2:$A$51,0))</f>
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H37" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B37,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>9.14808614779616</v>
+        <v>10.07118262569</v>
       </c>
       <c r="I37" s="15">
         <f>MIN(F37*(Assumptions!$C$6+Assumptions!$C$7)+H37,F37*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B37,Raw!$A$2:$A$51,0))))</f>
-        <v>26.5060861477962</v>
+        <v>27.32118262569</v>
       </c>
       <c r="J37" s="15">
         <f>MIN(I37+F37*Assumptions!$C$7,F37*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B37,Raw!$A$2:$A$51,0))))</f>
-        <v>32.2920861477962</v>
+        <v>33.07118262569</v>
       </c>
       <c r="K37" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B37,Raw!$A$2:$A$51,0))=1,G37&gt;I37),0,ROUNDUP(MAX(0,J37-G37),0))</f>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="M37" s="15">
         <f>IFERROR(G37/F37,0)</f>
-        <v>6.91323885240235</v>
+        <v>5.91304347826087</v>
       </c>
       <c r="N37" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B37,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M37&lt;Assumptions!$C$6,"Order now",IF(K37&gt;0,"Order","OK")))</f>
@@ -3829,23 +3829,23 @@
       </c>
       <c r="F38" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B38,Raw!$A$2:$A$51,0))</f>
-        <v>3.643</v>
+        <v>3</v>
       </c>
       <c r="G38" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B38,Raw!$A$2:$A$51,0))</f>
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="H38" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B38,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.13587658835313</v>
+        <v>6.02441911888607</v>
       </c>
       <c r="I38" s="15">
         <f>MIN(F38*(Assumptions!$C$6+Assumptions!$C$7)+H38,F38*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B38,Raw!$A$2:$A$51,0))))</f>
-        <v>17.0648765883531</v>
+        <v>15.0244191188861</v>
       </c>
       <c r="J38" s="15">
         <f>MIN(I38+F38*Assumptions!$C$7,F38*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B38,Raw!$A$2:$A$51,0))))</f>
-        <v>20.7078765883531</v>
+        <v>18.0244191188861</v>
       </c>
       <c r="K38" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B38,Raw!$A$2:$A$51,0))=1,G38&gt;I38),0,ROUNDUP(MAX(0,J38-G38),0))</f>
@@ -3857,7 +3857,7 @@
       </c>
       <c r="M38" s="15">
         <f>IFERROR(G38/F38,0)</f>
-        <v>7.68597309909415</v>
+        <v>6.66666666666667</v>
       </c>
       <c r="N38" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B38,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M38&lt;Assumptions!$C$6,"Order now",IF(K38&gt;0,"Order","OK")))</f>
@@ -3888,23 +3888,23 @@
       </c>
       <c r="F39" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B39,Raw!$A$2:$A$51,0))</f>
-        <v>9.393</v>
+        <v>9.893</v>
       </c>
       <c r="G39" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B39,Raw!$A$2:$A$51,0))</f>
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H39" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B39,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>10.2112189334819</v>
+        <v>11.9573859551325</v>
       </c>
       <c r="I39" s="15">
         <f>MIN(F39*(Assumptions!$C$6+Assumptions!$C$7)+H39,F39*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B39,Raw!$A$2:$A$51,0))))</f>
-        <v>38.3902189334819</v>
+        <v>41.6363859551325</v>
       </c>
       <c r="J39" s="15">
         <f>MIN(I39+F39*Assumptions!$C$7,F39*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B39,Raw!$A$2:$A$51,0))))</f>
-        <v>47.7832189334819</v>
+        <v>51.5293859551325</v>
       </c>
       <c r="K39" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B39,Raw!$A$2:$A$51,0))=1,G39&gt;I39),0,ROUNDUP(MAX(0,J39-G39),0))</f>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="M39" s="15">
         <f>IFERROR(G39/F39,0)</f>
-        <v>8.19759395294368</v>
+        <v>8.08652582634186</v>
       </c>
       <c r="N39" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B39,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M39&lt;Assumptions!$C$6,"Order now",IF(K39&gt;0,"Order","OK")))</f>
@@ -3947,23 +3947,23 @@
       </c>
       <c r="F40" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B40,Raw!$A$2:$A$51,0))</f>
-        <v>11.857</v>
+        <v>14.393</v>
       </c>
       <c r="G40" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B40,Raw!$A$2:$A$51,0))</f>
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="H40" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B40,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>12.4860944641429</v>
+        <v>13.6578268354632</v>
       </c>
       <c r="I40" s="15">
         <f>MIN(F40*(Assumptions!$C$6+Assumptions!$C$7)+H40,F40*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B40,Raw!$A$2:$A$51,0))))</f>
-        <v>48.0570944641429</v>
+        <v>56.8368268354633</v>
       </c>
       <c r="J40" s="15">
         <f>MIN(I40+F40*Assumptions!$C$7,F40*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B40,Raw!$A$2:$A$51,0))))</f>
-        <v>59.9140944641429</v>
+        <v>71.2298268354633</v>
       </c>
       <c r="K40" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B40,Raw!$A$2:$A$51,0))=1,G40&gt;I40),0,ROUNDUP(MAX(0,J40-G40),0))</f>
@@ -3975,7 +3975,7 @@
       </c>
       <c r="M40" s="15">
         <f>IFERROR(G40/F40,0)</f>
-        <v>7.50611453150038</v>
+        <v>7.01730007642604</v>
       </c>
       <c r="N40" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B40,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M40&lt;Assumptions!$C$6,"Order now",IF(K40&gt;0,"Order","OK")))</f>
@@ -4006,23 +4006,23 @@
       </c>
       <c r="F41" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B41,Raw!$A$2:$A$51,0))</f>
-        <v>6.714</v>
+        <v>5.929</v>
       </c>
       <c r="G41" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B41,Raw!$A$2:$A$51,0))</f>
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H41" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B41,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.69082473459798</v>
+        <v>7.57910792375989</v>
       </c>
       <c r="I41" s="15">
         <f>MIN(F41*(Assumptions!$C$6+Assumptions!$C$7)+H41,F41*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B41,Raw!$A$2:$A$51,0))))</f>
-        <v>28.832824734598</v>
+        <v>25.3661079237599</v>
       </c>
       <c r="J41" s="15">
         <f>MIN(I41+F41*Assumptions!$C$7,F41*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B41,Raw!$A$2:$A$51,0))))</f>
-        <v>35.546824734598</v>
+        <v>31.2951079237599</v>
       </c>
       <c r="K41" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B41,Raw!$A$2:$A$51,0))=1,G41&gt;I41),0,ROUNDUP(MAX(0,J41-G41),0))</f>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="M41" s="15">
         <f>IFERROR(G41/F41,0)</f>
-        <v>7.14924039320822</v>
+        <v>9.27643784786642</v>
       </c>
       <c r="N41" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B41,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M41&lt;Assumptions!$C$6,"Order now",IF(K41&gt;0,"Order","OK")))</f>
@@ -4065,23 +4065,23 @@
       </c>
       <c r="F42" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B42,Raw!$A$2:$A$51,0))</f>
-        <v>2.679</v>
+        <v>3.429</v>
       </c>
       <c r="G42" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B42,Raw!$A$2:$A$51,0))</f>
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="H42" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B42,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.82748447581538</v>
+        <v>5.7386307356372</v>
       </c>
       <c r="I42" s="15">
         <f>MIN(F42*(Assumptions!$C$6+Assumptions!$C$7)+H42,F42*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B42,Raw!$A$2:$A$51,0))))</f>
-        <v>14.8644844758154</v>
+        <v>16.0256307356372</v>
       </c>
       <c r="J42" s="15">
         <f>MIN(I42+F42*Assumptions!$C$7,F42*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B42,Raw!$A$2:$A$51,0))))</f>
-        <v>17.5434844758154</v>
+        <v>19.4546307356372</v>
       </c>
       <c r="K42" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B42,Raw!$A$2:$A$51,0))=1,G42&gt;I42),0,ROUNDUP(MAX(0,J42-G42),0))</f>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="M42" s="15">
         <f>IFERROR(G42/F42,0)</f>
-        <v>12.3180291153415</v>
+        <v>10.498687664042</v>
       </c>
       <c r="N42" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B42,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M42&lt;Assumptions!$C$6,"Order now",IF(K42&gt;0,"Order","OK")))</f>
@@ -4124,23 +4124,23 @@
       </c>
       <c r="F43" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B43,Raw!$A$2:$A$51,0))</f>
-        <v>5</v>
+        <v>5.321</v>
       </c>
       <c r="G43" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B43,Raw!$A$2:$A$51,0))</f>
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="H43" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B43,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.29617742434352</v>
+        <v>9.27097515259317</v>
       </c>
       <c r="I43" s="15">
         <f>MIN(F43*(Assumptions!$C$6+Assumptions!$C$7)+H43,F43*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B43,Raw!$A$2:$A$51,0))))</f>
-        <v>22.2961774243435</v>
+        <v>25.2339751525932</v>
       </c>
       <c r="J43" s="15">
         <f>MIN(I43+F43*Assumptions!$C$7,F43*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B43,Raw!$A$2:$A$51,0))))</f>
-        <v>27.2961774243435</v>
+        <v>30.5549751525932</v>
       </c>
       <c r="K43" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B43,Raw!$A$2:$A$51,0))=1,G43&gt;I43),0,ROUNDUP(MAX(0,J43-G43),0))</f>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="M43" s="15">
         <f>IFERROR(G43/F43,0)</f>
-        <v>5.6</v>
+        <v>5.45010336402932</v>
       </c>
       <c r="N43" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B43,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M43&lt;Assumptions!$C$6,"Order now",IF(K43&gt;0,"Order","OK")))</f>
@@ -4183,23 +4183,23 @@
       </c>
       <c r="F44" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B44,Raw!$A$2:$A$51,0))</f>
-        <v>2.893</v>
+        <v>3.536</v>
       </c>
       <c r="G44" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B44,Raw!$A$2:$A$51,0))</f>
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H44" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B44,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>4.3554149607127</v>
+        <v>6.24733405782018</v>
       </c>
       <c r="I44" s="15">
         <f>MIN(F44*(Assumptions!$C$6+Assumptions!$C$7)+H44,F44*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B44,Raw!$A$2:$A$51,0))))</f>
-        <v>13.0344149607127</v>
+        <v>16.8553340578202</v>
       </c>
       <c r="J44" s="15">
         <f>MIN(I44+F44*Assumptions!$C$7,F44*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B44,Raw!$A$2:$A$51,0))))</f>
-        <v>15.9274149607127</v>
+        <v>20.3913340578202</v>
       </c>
       <c r="K44" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B44,Raw!$A$2:$A$51,0))=1,G44&gt;I44),0,ROUNDUP(MAX(0,J44-G44),0))</f>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="M44" s="15">
         <f>IFERROR(G44/F44,0)</f>
-        <v>10.7155202212236</v>
+        <v>8.4841628959276</v>
       </c>
       <c r="N44" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B44,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M44&lt;Assumptions!$C$6,"Order now",IF(K44&gt;0,"Order","OK")))</f>
@@ -4242,23 +4242,23 @@
       </c>
       <c r="F45" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B45,Raw!$A$2:$A$51,0))</f>
-        <v>5.357</v>
+        <v>3.929</v>
       </c>
       <c r="G45" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B45,Raw!$A$2:$A$51,0))</f>
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H45" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B45,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>8.6336670579482</v>
+        <v>7.1247043943942</v>
       </c>
       <c r="I45" s="15">
         <f>MIN(F45*(Assumptions!$C$6+Assumptions!$C$7)+H45,F45*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B45,Raw!$A$2:$A$51,0))))</f>
-        <v>24.7046670579482</v>
+        <v>18.9117043943942</v>
       </c>
       <c r="J45" s="15">
         <f>MIN(I45+F45*Assumptions!$C$7,F45*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B45,Raw!$A$2:$A$51,0))))</f>
-        <v>30.0616670579482</v>
+        <v>22.8407043943942</v>
       </c>
       <c r="K45" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B45,Raw!$A$2:$A$51,0))=1,G45&gt;I45),0,ROUNDUP(MAX(0,J45-G45),0))</f>
@@ -4270,7 +4270,7 @@
       </c>
       <c r="M45" s="15">
         <f>IFERROR(G45/F45,0)</f>
-        <v>7.09352249393317</v>
+        <v>9.41715449223721</v>
       </c>
       <c r="N45" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B45,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M45&lt;Assumptions!$C$6,"Order now",IF(K45&gt;0,"Order","OK")))</f>
@@ -4301,23 +4301,23 @@
       </c>
       <c r="F46" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B46,Raw!$A$2:$A$51,0))</f>
-        <v>1.714</v>
+        <v>2.036</v>
       </c>
       <c r="G46" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B46,Raw!$A$2:$A$51,0))</f>
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H46" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B46,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>3.55234960378339</v>
+        <v>4.76123446492609</v>
       </c>
       <c r="I46" s="15">
         <f>MIN(F46*(Assumptions!$C$6+Assumptions!$C$7)+H46,F46*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B46,Raw!$A$2:$A$51,0))))</f>
-        <v>8.69434960378339</v>
+        <v>10.8692344649261</v>
       </c>
       <c r="J46" s="15">
         <f>MIN(I46+F46*Assumptions!$C$7,F46*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B46,Raw!$A$2:$A$51,0))))</f>
-        <v>10.4083496037834</v>
+        <v>12.9052344649261</v>
       </c>
       <c r="K46" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B46,Raw!$A$2:$A$51,0))=1,G46&gt;I46),0,ROUNDUP(MAX(0,J46-G46),0))</f>
@@ -4329,7 +4329,7 @@
       </c>
       <c r="M46" s="15">
         <f>IFERROR(G46/F46,0)</f>
-        <v>9.91831971995333</v>
+        <v>6.38506876227898</v>
       </c>
       <c r="N46" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B46,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M46&lt;Assumptions!$C$6,"Order now",IF(K46&gt;0,"Order","OK")))</f>
@@ -4360,23 +4360,23 @@
       </c>
       <c r="F47" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B47,Raw!$A$2:$A$51,0))</f>
-        <v>2.107</v>
+        <v>3.536</v>
       </c>
       <c r="G47" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B47,Raw!$A$2:$A$51,0))</f>
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H47" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B47,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>3.91530085050945</v>
+        <v>5.79293052845449</v>
       </c>
       <c r="I47" s="15">
         <f>MIN(F47*(Assumptions!$C$6+Assumptions!$C$7)+H47,F47*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B47,Raw!$A$2:$A$51,0))))</f>
-        <v>10.2363008505094</v>
+        <v>16.4009305284545</v>
       </c>
       <c r="J47" s="15">
         <f>MIN(I47+F47*Assumptions!$C$7,F47*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B47,Raw!$A$2:$A$51,0))))</f>
-        <v>12.3433008505094</v>
+        <v>19.9369305284545</v>
       </c>
       <c r="K47" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B47,Raw!$A$2:$A$51,0))=1,G47&gt;I47),0,ROUNDUP(MAX(0,J47-G47),0))</f>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="M47" s="15">
         <f>IFERROR(G47/F47,0)</f>
-        <v>10.9159943046986</v>
+        <v>9.04977375565611</v>
       </c>
       <c r="N47" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B47,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M47&lt;Assumptions!$C$6,"Order now",IF(K47&gt;0,"Order","OK")))</f>
@@ -4419,39 +4419,39 @@
       </c>
       <c r="F48" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B48,Raw!$A$2:$A$51,0))</f>
-        <v>0.643</v>
+        <v>1.143</v>
       </c>
       <c r="G48" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B48,Raw!$A$2:$A$51,0))</f>
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H48" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B48,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>2.7178475246967</v>
+        <v>2.98363072111815</v>
       </c>
       <c r="I48" s="15">
         <f>MIN(F48*(Assumptions!$C$6+Assumptions!$C$7)+H48,F48*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B48,Raw!$A$2:$A$51,0))))</f>
-        <v>4.6468475246967</v>
+        <v>6.41263072111815</v>
       </c>
       <c r="J48" s="15">
         <f>MIN(I48+F48*Assumptions!$C$7,F48*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B48,Raw!$A$2:$A$51,0))))</f>
-        <v>5.2898475246967</v>
+        <v>7.55563072111815</v>
       </c>
       <c r="K48" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B48,Raw!$A$2:$A$51,0))=1,G48&gt;I48),0,ROUNDUP(MAX(0,J48-G48),0))</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L48" s="17">
         <f>K48*INDEX(Raw!$I$2:$I$51,MATCH($B48,Raw!$A$2:$A$51,0))</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M48" s="15">
         <f>IFERROR(G48/F48,0)</f>
-        <v>13.9968895800933</v>
+        <v>3.49956255468067</v>
       </c>
       <c r="N48" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B48,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M48&lt;Assumptions!$C$6,"Order now",IF(K48&gt;0,"Order","OK")))</f>
-        <v>OK</v>
+        <v>Order</v>
       </c>
       <c r="O48" s="16">
         <f>IF(OR(SelCat="All",D48=SelCat),1,0)</f>
@@ -4478,23 +4478,23 @@
       </c>
       <c r="F49" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B49,Raw!$A$2:$A$51,0))</f>
-        <v>5.5</v>
+        <v>4.357</v>
       </c>
       <c r="G49" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B49,Raw!$A$2:$A$51,0))</f>
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="H49" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B49,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>6.89035792013013</v>
+        <v>8.09066912977536</v>
       </c>
       <c r="I49" s="15">
         <f>MIN(F49*(Assumptions!$C$6+Assumptions!$C$7)+H49,F49*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B49,Raw!$A$2:$A$51,0))))</f>
-        <v>23.3903579201301</v>
+        <v>21.1616691297754</v>
       </c>
       <c r="J49" s="15">
         <f>MIN(I49+F49*Assumptions!$C$7,F49*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B49,Raw!$A$2:$A$51,0))))</f>
-        <v>28.8903579201301</v>
+        <v>25.5186691297754</v>
       </c>
       <c r="K49" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B49,Raw!$A$2:$A$51,0))=1,G49&gt;I49),0,ROUNDUP(MAX(0,J49-G49),0))</f>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="M49" s="15">
         <f>IFERROR(G49/F49,0)</f>
-        <v>8.54545454545455</v>
+        <v>10.0986917603856</v>
       </c>
       <c r="N49" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B49,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M49&lt;Assumptions!$C$6,"Order now",IF(K49&gt;0,"Order","OK")))</f>
@@ -4537,23 +4537,23 @@
       </c>
       <c r="F50" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B50,Raw!$A$2:$A$51,0))</f>
-        <v>8.071</v>
+        <v>7.75</v>
       </c>
       <c r="G50" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B50,Raw!$A$2:$A$51,0))</f>
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H50" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B50,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>9.89685171190819</v>
+        <v>9.67107888914158</v>
       </c>
       <c r="I50" s="15">
         <f>MIN(F50*(Assumptions!$C$6+Assumptions!$C$7)+H50,F50*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B50,Raw!$A$2:$A$51,0))))</f>
-        <v>34.1098517119082</v>
+        <v>32.9210788891416</v>
       </c>
       <c r="J50" s="15">
         <f>MIN(I50+F50*Assumptions!$C$7,F50*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B50,Raw!$A$2:$A$51,0))))</f>
-        <v>40.355</v>
+        <v>38.75</v>
       </c>
       <c r="K50" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B50,Raw!$A$2:$A$51,0))=1,G50&gt;I50),0,ROUNDUP(MAX(0,J50-G50),0))</f>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="M50" s="15">
         <f>IFERROR(G50/F50,0)</f>
-        <v>8.54912650229216</v>
+        <v>9.03225806451613</v>
       </c>
       <c r="N50" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B50,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M50&lt;Assumptions!$C$6,"Order now",IF(K50&gt;0,"Order","OK")))</f>
@@ -4596,23 +4596,23 @@
       </c>
       <c r="F51" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B51,Raw!$A$2:$A$51,0))</f>
-        <v>31.607</v>
+        <v>31.071</v>
       </c>
       <c r="G51" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B51,Raw!$A$2:$A$51,0))</f>
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H51" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B51,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>18.9477698093997</v>
+        <v>22.0542895353149</v>
       </c>
       <c r="I51" s="15">
         <f>MIN(F51*(Assumptions!$C$6+Assumptions!$C$7)+H51,F51*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B51,Raw!$A$2:$A$51,0))))</f>
-        <v>113.7687698094</v>
+        <v>115.267289535315</v>
       </c>
       <c r="J51" s="15">
         <f>MIN(I51+F51*Assumptions!$C$7,F51*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B51,Raw!$A$2:$A$51,0))))</f>
-        <v>145.3757698094</v>
+        <v>146.338289535315</v>
       </c>
       <c r="K51" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B51,Raw!$A$2:$A$51,0))=1,G51&gt;I51),0,ROUNDUP(MAX(0,J51-G51),0))</f>
@@ -4624,7 +4624,7 @@
       </c>
       <c r="M51" s="15">
         <f>IFERROR(G51/F51,0)</f>
-        <v>8.54241149112538</v>
+        <v>8.65759067941167</v>
       </c>
       <c r="N51" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B51,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M51&lt;Assumptions!$C$6,"Order now",IF(K51&gt;0,"Order","OK")))</f>
@@ -4655,23 +4655,23 @@
       </c>
       <c r="F52" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B52,Raw!$A$2:$A$51,0))</f>
-        <v>4.5</v>
+        <v>4.464</v>
       </c>
       <c r="G52" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B52,Raw!$A$2:$A$51,0))</f>
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H52" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B52,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>7.91348033216107</v>
+        <v>8.32215772020694</v>
       </c>
       <c r="I52" s="15">
         <f>MIN(F52*(Assumptions!$C$6+Assumptions!$C$7)+H52,F52*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B52,Raw!$A$2:$A$51,0))))</f>
-        <v>21.4134803321611</v>
+        <v>21.7141577202069</v>
       </c>
       <c r="J52" s="15">
         <f>MIN(I52+F52*Assumptions!$C$7,F52*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B52,Raw!$A$2:$A$51,0))))</f>
-        <v>25.9134803321611</v>
+        <v>26.1781577202069</v>
       </c>
       <c r="K52" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B52,Raw!$A$2:$A$51,0))=1,G52&gt;I52),0,ROUNDUP(MAX(0,J52-G52),0))</f>
@@ -4683,7 +4683,7 @@
       </c>
       <c r="M52" s="15">
         <f>IFERROR(G52/F52,0)</f>
-        <v>10.6666666666667</v>
+        <v>10.0806451612903</v>
       </c>
       <c r="N52" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B52,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M52&lt;Assumptions!$C$6,"Order now",IF(K52&gt;0,"Order","OK")))</f>
@@ -4714,23 +4714,23 @@
       </c>
       <c r="F53" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B53,Raw!$A$2:$A$51,0))</f>
-        <v>15.821</v>
+        <v>17.429</v>
       </c>
       <c r="G53" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B53,Raw!$A$2:$A$51,0))</f>
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H53" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B53,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>13.6749741384582</v>
+        <v>14.849564393611</v>
       </c>
       <c r="I53" s="15">
         <f>MIN(F53*(Assumptions!$C$6+Assumptions!$C$7)+H53,F53*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B53,Raw!$A$2:$A$51,0))))</f>
-        <v>61.1379741384582</v>
+        <v>67.136564393611</v>
       </c>
       <c r="J53" s="15">
         <f>MIN(I53+F53*Assumptions!$C$7,F53*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B53,Raw!$A$2:$A$51,0))))</f>
-        <v>76.9589741384582</v>
+        <v>84.565564393611</v>
       </c>
       <c r="K53" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B53,Raw!$A$2:$A$51,0))=1,G53&gt;I53),0,ROUNDUP(MAX(0,J53-G53),0))</f>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="M53" s="15">
         <f>IFERROR(G53/F53,0)</f>
-        <v>6.69995575500917</v>
+        <v>6.31132021343738</v>
       </c>
       <c r="N53" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B53,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M53&lt;Assumptions!$C$6,"Order now",IF(K53&gt;0,"Order","OK")))</f>
@@ -4773,23 +4773,23 @@
       </c>
       <c r="F54" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B54,Raw!$A$2:$A$51,0))</f>
-        <v>9.143</v>
+        <v>9.393</v>
       </c>
       <c r="G54" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B54,Raw!$A$2:$A$51,0))</f>
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H54" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B54,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>9.22810689510584</v>
+        <v>9.2138174759434</v>
       </c>
       <c r="I54" s="15">
         <f>MIN(F54*(Assumptions!$C$6+Assumptions!$C$7)+H54,F54*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B54,Raw!$A$2:$A$51,0))))</f>
-        <v>36.6571068951058</v>
+        <v>37.3928174759434</v>
       </c>
       <c r="J54" s="15">
         <f>MIN(I54+F54*Assumptions!$C$7,F54*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B54,Raw!$A$2:$A$51,0))))</f>
-        <v>45.8001068951058</v>
+        <v>46.7858174759434</v>
       </c>
       <c r="K54" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B54,Raw!$A$2:$A$51,0))=1,G54&gt;I54),0,ROUNDUP(MAX(0,J54-G54),0))</f>
@@ -4801,7 +4801,7 @@
       </c>
       <c r="M54" s="15">
         <f>IFERROR(G54/F54,0)</f>
-        <v>8.09362353713223</v>
+        <v>6.81358458426488</v>
       </c>
       <c r="N54" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B54,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M54&lt;Assumptions!$C$6,"Order now",IF(K54&gt;0,"Order","OK")))</f>
@@ -4832,23 +4832,23 @@
       </c>
       <c r="F55" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B55,Raw!$A$2:$A$51,0))</f>
-        <v>10.107</v>
+        <v>9.679</v>
       </c>
       <c r="G55" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B55,Raw!$A$2:$A$51,0))</f>
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H55" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B55,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>10.954268729929</v>
+        <v>10.5227282712232</v>
       </c>
       <c r="I55" s="15">
         <f>MIN(F55*(Assumptions!$C$6+Assumptions!$C$7)+H55,F55*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B55,Raw!$A$2:$A$51,0))))</f>
-        <v>41.275268729929</v>
+        <v>39.5597282712232</v>
       </c>
       <c r="J55" s="15">
         <f>MIN(I55+F55*Assumptions!$C$7,F55*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B55,Raw!$A$2:$A$51,0))))</f>
-        <v>51.382268729929</v>
+        <v>49.2387282712232</v>
       </c>
       <c r="K55" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B55,Raw!$A$2:$A$51,0))=1,G55&gt;I55),0,ROUNDUP(MAX(0,J55-G55),0))</f>
@@ -4860,7 +4860,7 @@
       </c>
       <c r="M55" s="15">
         <f>IFERROR(G55/F55,0)</f>
-        <v>8.21213020678738</v>
+        <v>8.05868374832111</v>
       </c>
       <c r="N55" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B55,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M55&lt;Assumptions!$C$6,"Order now",IF(K55&gt;0,"Order","OK")))</f>
@@ -4891,23 +4891,23 @@
       </c>
       <c r="F56" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B56,Raw!$A$2:$A$51,0))</f>
-        <v>9.357</v>
+        <v>9.179</v>
       </c>
       <c r="G56" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B56,Raw!$A$2:$A$51,0))</f>
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H56" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B56,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>9.99687764604529</v>
+        <v>9.83969403525841</v>
       </c>
       <c r="I56" s="15">
         <f>MIN(F56*(Assumptions!$C$6+Assumptions!$C$7)+H56,F56*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B56,Raw!$A$2:$A$51,0))))</f>
-        <v>38.0678776460453</v>
+        <v>37.3766940352584</v>
       </c>
       <c r="J56" s="15">
         <f>MIN(I56+F56*Assumptions!$C$7,F56*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B56,Raw!$A$2:$A$51,0))))</f>
-        <v>47.4248776460453</v>
+        <v>46.5556940352584</v>
       </c>
       <c r="K56" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B56,Raw!$A$2:$A$51,0))=1,G56&gt;I56),0,ROUNDUP(MAX(0,J56-G56),0))</f>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="M56" s="15">
         <f>IFERROR(G56/F56,0)</f>
-        <v>7.90851768729294</v>
+        <v>7.73504739078331</v>
       </c>
       <c r="N56" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B56,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M56&lt;Assumptions!$C$6,"Order now",IF(K56&gt;0,"Order","OK")))</f>
@@ -4950,23 +4950,23 @@
       </c>
       <c r="F57" s="15">
         <f>INDEX(Raw!$E$2:$E$51,MATCH($B57,Raw!$A$2:$A$51,0))</f>
-        <v>20.679</v>
+        <v>22.786</v>
       </c>
       <c r="G57" s="16">
         <f>INDEX(Raw!$G$2:$G$51,MATCH($B57,Raw!$A$2:$A$51,0))</f>
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H57" s="15">
         <f>Assumptions!$C$8*INDEX(Raw!$F$2:$F$51,MATCH($B57,Raw!$A$2:$A$51,0))*SQRT(Assumptions!$C$6+Assumptions!$C$7)</f>
-        <v>19.1964057028262</v>
+        <v>18.7219969866331</v>
       </c>
       <c r="I57" s="15">
         <f>MIN(F57*(Assumptions!$C$6+Assumptions!$C$7)+H57,F57*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B57,Raw!$A$2:$A$51,0))))</f>
-        <v>81.2334057028262</v>
+        <v>87.0799969866331</v>
       </c>
       <c r="J57" s="15">
         <f>MIN(I57+F57*Assumptions!$C$7,F57*MAX(1,INDEX(Raw!$H$2:$H$51,MATCH($B57,Raw!$A$2:$A$51,0))))</f>
-        <v>101.912405702826</v>
+        <v>109.865996986633</v>
       </c>
       <c r="K57" s="16">
         <f>IF(OR(INDEX(Raw!$J$2:$J$51,MATCH($B57,Raw!$A$2:$A$51,0))=1,G57&gt;I57),0,ROUNDUP(MAX(0,J57-G57),0))</f>
@@ -4978,7 +4978,7 @@
       </c>
       <c r="M57" s="15">
         <f>IFERROR(G57/F57,0)</f>
-        <v>8.22090043038832</v>
+        <v>7.2412885104889</v>
       </c>
       <c r="N57" s="14" t="str">
         <f>IF(INDEX(Raw!$J$2:$J$51,MATCH($B57,Raw!$A$2:$A$51,0))=1,"Blocked - recall",IF(M57&lt;Assumptions!$C$6,"Order now",IF(K57&gt;0,"Order","OK")))</f>
@@ -5001,18 +5001,18 @@
       <c r="F58" s="20" t="n"/>
       <c r="G58" s="21">
         <f>SUM(G8:G57)</f>
-        <v>4212</v>
+        <v>4162</v>
       </c>
       <c r="H58" s="20" t="n"/>
       <c r="I58" s="20" t="n"/>
       <c r="J58" s="20" t="n"/>
       <c r="K58" s="21">
         <f>SUM(K8:K57)</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L58" s="22">
         <f>SUM(L8:L57)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="M58" s="20" t="n"/>
       <c r="N58" s="19" t="n"/>
@@ -5173,11 +5173,11 @@
       </c>
       <c r="C72" s="17">
         <f>SUMIFS($L$8:$L$57,$E$8:$E$57,$B72,$O$8:$O$57,1)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D72" s="16">
         <f>COUNTIFS($E$8:$E$57,$B72,$K$8:$K$57,"&gt;0",$O$8:$O$57,1)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -5293,11 +5293,11 @@
       </c>
       <c r="C80" s="22">
         <f>SUM(C64:C79)</f>
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="D80" s="21">
         <f>SUM(D64:D79)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5531,7 +5531,7 @@
         <v>0</v>
       </c>
       <c r="C8" s="23" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D8" s="23" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="23" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="9">
@@ -5616,7 +5616,7 @@
         <v>0</v>
       </c>
       <c r="L9" s="23" t="n">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="M9" s="23" t="n">
         <v>0</v>
@@ -5634,7 +5634,7 @@
         <v>0</v>
       </c>
       <c r="R9" s="23" t="n">
-        <v>159</v>
+        <v>146</v>
       </c>
     </row>
     <row r="10">
@@ -5644,19 +5644,19 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C10" s="23" t="n">
         <v>0</v>
       </c>
       <c r="D10" s="23" t="n">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="E10" s="23" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G10" s="23" t="n">
         <v>0</v>
@@ -5683,7 +5683,7 @@
         <v>0</v>
       </c>
       <c r="O10" s="23" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="P10" s="23" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="R10" s="23" t="n">
-        <v>838</v>
+        <v>867</v>
       </c>
     </row>
     <row r="11">
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>643</v>
+        <v>613</v>
       </c>
       <c r="G11" s="23" t="n">
         <v>0</v>
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="R11" s="23" t="n">
-        <v>703</v>
+        <v>673</v>
       </c>
     </row>
     <row r="12">
@@ -5778,7 +5778,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I12" s="23" t="n">
         <v>0</v>
@@ -5808,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="23" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="13">
@@ -5818,7 +5818,7 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="C13" s="23" t="n">
         <v>0</v>
@@ -5839,7 +5839,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="23" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="J13" s="23" t="n">
         <v>0</v>
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="23" t="n">
-        <v>242</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14">
@@ -5876,7 +5876,7 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>89</v>
+        <v>101</v>
       </c>
       <c r="C14" s="23" t="n">
         <v>0</v>
@@ -5891,7 +5891,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="23" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H14" s="23" t="n">
         <v>0</v>
@@ -5903,13 +5903,13 @@
         <v>0</v>
       </c>
       <c r="K14" s="23" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="L14" s="23" t="n">
         <v>0</v>
       </c>
       <c r="M14" s="23" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="N14" s="23" t="n">
         <v>0</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="R14" s="23" t="n">
-        <v>374</v>
+        <v>385</v>
       </c>
     </row>
     <row r="15">
@@ -5970,7 +5970,7 @@
         <v>0</v>
       </c>
       <c r="N15" s="23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O15" s="23" t="n">
         <v>0</v>
@@ -5982,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="R15" s="23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
     </row>
     <row r="16">
@@ -6016,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="J16" s="23" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K16" s="23" t="n">
         <v>0</v>
@@ -6040,7 +6040,7 @@
         <v>0</v>
       </c>
       <c r="R16" s="23" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="17">
@@ -6092,13 +6092,13 @@
         <v>0</v>
       </c>
       <c r="P17" s="23" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q17" s="23" t="n">
         <v>0</v>
       </c>
       <c r="R17" s="23" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="18">
@@ -6117,7 +6117,7 @@
         <v>0</v>
       </c>
       <c r="E18" s="23" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F18" s="23" t="n">
         <v>0</v>
@@ -6135,7 +6135,7 @@
         <v>0</v>
       </c>
       <c r="K18" s="23" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="L18" s="23" t="n">
         <v>0</v>
@@ -6153,10 +6153,10 @@
         <v>0</v>
       </c>
       <c r="Q18" s="23" t="n">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="R18" s="23" t="n">
-        <v>507</v>
+        <v>488</v>
       </c>
     </row>
     <row r="19">
@@ -6166,55 +6166,55 @@
         </is>
       </c>
       <c r="B19" s="23" t="n">
-        <v>158</v>
+        <v>182</v>
       </c>
       <c r="C19" s="23" t="n">
-        <v>333</v>
+        <v>325</v>
       </c>
       <c r="D19" s="23" t="n">
-        <v>631</v>
+        <v>647</v>
       </c>
       <c r="E19" s="23" t="n">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F19" s="23" t="n">
-        <v>757</v>
+        <v>734</v>
       </c>
       <c r="G19" s="23" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="H19" s="23" t="n">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="I19" s="23" t="n">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="J19" s="23" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K19" s="23" t="n">
+        <v>130</v>
+      </c>
+      <c r="L19" s="23" t="n">
+        <v>146</v>
+      </c>
+      <c r="M19" s="23" t="n">
         <v>138</v>
       </c>
-      <c r="L19" s="23" t="n">
-        <v>159</v>
-      </c>
-      <c r="M19" s="23" t="n">
-        <v>144</v>
-      </c>
       <c r="N19" s="23" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="O19" s="23" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="P19" s="23" t="n">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="Q19" s="23" t="n">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="R19" s="23" t="n">
-        <v>4212</v>
+        <v>4162</v>
       </c>
     </row>
   </sheetData>
@@ -6299,38 +6299,38 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>BAK001</t>
+          <t>HHD003</t>
         </is>
       </c>
       <c r="B2" s="25" t="inlineStr">
         <is>
-          <t>Toast Bread White</t>
+          <t>Phone Charger Cable</t>
         </is>
       </c>
       <c r="C2" s="25" t="inlineStr">
         <is>
-          <t>Bakery</t>
+          <t>Household</t>
         </is>
       </c>
       <c r="D2" s="25" t="inlineStr">
         <is>
-          <t>Auckland Bakehouse</t>
+          <t>Home Supplies</t>
         </is>
       </c>
       <c r="E2" s="26" t="n">
-        <v>20.286</v>
+        <v>1.143</v>
       </c>
       <c r="F2" s="26" t="n">
-        <v>6.879</v>
+        <v>1.044</v>
       </c>
       <c r="G2" s="27" t="n">
-        <v>181</v>
+        <v>4</v>
       </c>
       <c r="H2" s="25" t="n">
-        <v>5</v>
+        <v>3650</v>
       </c>
       <c r="I2" s="28" t="n">
-        <v>2.2</v>
+        <v>5.5</v>
       </c>
       <c r="J2" s="25" t="n">
         <v>0</v>
@@ -6339,12 +6339,12 @@
     <row r="3">
       <c r="A3" s="25" t="inlineStr">
         <is>
-          <t>BAK002</t>
+          <t>BAK001</t>
         </is>
       </c>
       <c r="B3" s="25" t="inlineStr">
         <is>
-          <t>Wholemeal Loaf</t>
+          <t>Toast Bread White</t>
         </is>
       </c>
       <c r="C3" s="25" t="inlineStr">
@@ -6358,19 +6358,19 @@
         </is>
       </c>
       <c r="E3" s="26" t="n">
-        <v>9.929</v>
+        <v>20.393</v>
       </c>
       <c r="F3" s="26" t="n">
-        <v>4.337</v>
+        <v>6.154</v>
       </c>
       <c r="G3" s="27" t="n">
-        <v>104</v>
+        <v>179</v>
       </c>
       <c r="H3" s="25" t="n">
         <v>5</v>
       </c>
       <c r="I3" s="28" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="J3" s="25" t="n">
         <v>0</v>
@@ -6379,12 +6379,12 @@
     <row r="4">
       <c r="A4" s="25" t="inlineStr">
         <is>
-          <t>BAK003</t>
+          <t>BAK002</t>
         </is>
       </c>
       <c r="B4" s="25" t="inlineStr">
         <is>
-          <t>Croissant 4pk</t>
+          <t>Wholemeal Loaf</t>
         </is>
       </c>
       <c r="C4" s="25" t="inlineStr">
@@ -6398,19 +6398,19 @@
         </is>
       </c>
       <c r="E4" s="26" t="n">
-        <v>7.286</v>
+        <v>11.893</v>
       </c>
       <c r="F4" s="26" t="n">
-        <v>3.376</v>
+        <v>4.458</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>48</v>
+        <v>95</v>
       </c>
       <c r="H4" s="25" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" s="28" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J4" s="25" t="n">
         <v>0</v>
@@ -6419,38 +6419,38 @@
     <row r="5">
       <c r="A5" s="25" t="inlineStr">
         <is>
-          <t>BBT001</t>
+          <t>BAK003</t>
         </is>
       </c>
       <c r="B5" s="25" t="inlineStr">
         <is>
-          <t>Bubble Tea Kit</t>
+          <t>Croissant 4pk</t>
         </is>
       </c>
       <c r="C5" s="25" t="inlineStr">
         <is>
-          <t>Beverages</t>
+          <t>Bakery</t>
         </is>
       </c>
       <c r="D5" s="25" t="inlineStr">
         <is>
-          <t>Asia Imports</t>
+          <t>Auckland Bakehouse</t>
         </is>
       </c>
       <c r="E5" s="26" t="n">
-        <v>5.607</v>
+        <v>6.929</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>3.01</v>
+        <v>3.681</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>37</v>
+        <v>51</v>
       </c>
       <c r="H5" s="25" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="I5" s="28" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J5" s="25" t="n">
         <v>0</v>
@@ -6459,12 +6459,12 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>BEV001</t>
+          <t>BBT001</t>
         </is>
       </c>
       <c r="B6" s="25" t="inlineStr">
         <is>
-          <t>Energy Drink 500ml</t>
+          <t>Bubble Tea Kit</t>
         </is>
       </c>
       <c r="C6" s="25" t="inlineStr">
@@ -6474,23 +6474,23 @@
       </c>
       <c r="D6" s="25" t="inlineStr">
         <is>
-          <t>Beverage Dist.</t>
+          <t>Asia Imports</t>
         </is>
       </c>
       <c r="E6" s="26" t="n">
-        <v>30.5</v>
+        <v>5.107</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>14.658</v>
+        <v>3.37</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>235</v>
+        <v>45</v>
       </c>
       <c r="H6" s="25" t="n">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="I6" s="28" t="n">
-        <v>2.15</v>
+        <v>3.9</v>
       </c>
       <c r="J6" s="25" t="n">
         <v>0</v>
@@ -6499,12 +6499,12 @@
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>BEV002</t>
+          <t>BEV001</t>
         </is>
       </c>
       <c r="B7" s="25" t="inlineStr">
         <is>
-          <t>Cola 1.5L</t>
+          <t>Energy Drink 500ml</t>
         </is>
       </c>
       <c r="C7" s="25" t="inlineStr">
@@ -6518,19 +6518,19 @@
         </is>
       </c>
       <c r="E7" s="26" t="n">
-        <v>14.214</v>
+        <v>31.321</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>4.879</v>
+        <v>19.56</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>119</v>
+        <v>238</v>
       </c>
       <c r="H7" s="25" t="n">
-        <v>270</v>
+        <v>365</v>
       </c>
       <c r="I7" s="28" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="J7" s="25" t="n">
         <v>0</v>
@@ -6539,12 +6539,12 @@
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>BEV003</t>
+          <t>BEV002</t>
         </is>
       </c>
       <c r="B8" s="25" t="inlineStr">
         <is>
-          <t>Sparkling Water 1L</t>
+          <t>Cola 1.5L</t>
         </is>
       </c>
       <c r="C8" s="25" t="inlineStr">
@@ -6558,19 +6558,19 @@
         </is>
       </c>
       <c r="E8" s="26" t="n">
-        <v>11.679</v>
+        <v>14.071</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>3.982</v>
+        <v>4.838</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>106</v>
+        <v>127</v>
       </c>
       <c r="H8" s="25" t="n">
-        <v>365</v>
+        <v>270</v>
       </c>
       <c r="I8" s="28" t="n">
-        <v>1.1</v>
+        <v>2.3</v>
       </c>
       <c r="J8" s="25" t="n">
         <v>0</v>
@@ -6579,12 +6579,12 @@
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>BEV004</t>
+          <t>BEV003</t>
         </is>
       </c>
       <c r="B9" s="25" t="inlineStr">
         <is>
-          <t>Iced Coffee 500ml</t>
+          <t>Sparkling Water 1L</t>
         </is>
       </c>
       <c r="C9" s="25" t="inlineStr">
@@ -6594,23 +6594,23 @@
       </c>
       <c r="D9" s="25" t="inlineStr">
         <is>
-          <t>Dairy Co-op</t>
+          <t>Beverage Dist.</t>
         </is>
       </c>
       <c r="E9" s="26" t="n">
-        <v>12.5</v>
+        <v>11.964</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>4.726</v>
+        <v>4.865</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="H9" s="25" t="n">
-        <v>30</v>
+        <v>365</v>
       </c>
       <c r="I9" s="28" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J9" s="25" t="n">
         <v>0</v>
@@ -6619,12 +6619,12 @@
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>BEV005</t>
+          <t>BEV004</t>
         </is>
       </c>
       <c r="B10" s="25" t="inlineStr">
         <is>
-          <t>Kombucha 330ml</t>
+          <t>Iced Coffee 500ml</t>
         </is>
       </c>
       <c r="C10" s="25" t="inlineStr">
@@ -6634,23 +6634,23 @@
       </c>
       <c r="D10" s="25" t="inlineStr">
         <is>
-          <t>Plant Foods NZ</t>
+          <t>Dairy Co-op</t>
         </is>
       </c>
       <c r="E10" s="26" t="n">
-        <v>4.571</v>
+        <v>12.929</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>2.755</v>
+        <v>5.099</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>56</v>
+        <v>121</v>
       </c>
       <c r="H10" s="25" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="I10" s="28" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="J10" s="25" t="n">
         <v>0</v>
@@ -6659,12 +6659,12 @@
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
-          <t>BEV006</t>
+          <t>BEV005</t>
         </is>
       </c>
       <c r="B11" s="25" t="inlineStr">
         <is>
-          <t>Bottled Water 750ml</t>
+          <t>Kombucha 330ml</t>
         </is>
       </c>
       <c r="C11" s="25" t="inlineStr">
@@ -6674,23 +6674,23 @@
       </c>
       <c r="D11" s="25" t="inlineStr">
         <is>
-          <t>Beverage Dist.</t>
+          <t>Plant Foods NZ</t>
         </is>
       </c>
       <c r="E11" s="26" t="n">
-        <v>17.393</v>
+        <v>4.857</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>5.101</v>
+        <v>2.46</v>
       </c>
       <c r="G11" s="27" t="n">
-        <v>171</v>
+        <v>54</v>
       </c>
       <c r="H11" s="25" t="n">
-        <v>365</v>
+        <v>120</v>
       </c>
       <c r="I11" s="28" t="n">
-        <v>0.95</v>
+        <v>2.6</v>
       </c>
       <c r="J11" s="25" t="n">
         <v>0</v>
@@ -6699,38 +6699,38 @@
     <row r="12">
       <c r="A12" s="25" t="inlineStr">
         <is>
-          <t>DRY010</t>
+          <t>BEV006</t>
         </is>
       </c>
       <c r="B12" s="25" t="inlineStr">
         <is>
-          <t>Butter 500g</t>
+          <t>Bottled Water 750ml</t>
         </is>
       </c>
       <c r="C12" s="25" t="inlineStr">
         <is>
-          <t>Dairy</t>
+          <t>Beverages</t>
         </is>
       </c>
       <c r="D12" s="25" t="inlineStr">
         <is>
-          <t>Dairy Co-op</t>
+          <t>Beverage Dist.</t>
         </is>
       </c>
       <c r="E12" s="26" t="n">
-        <v>6.786</v>
+        <v>18.071</v>
       </c>
       <c r="F12" s="26" t="n">
-        <v>4.677</v>
+        <v>5.163</v>
       </c>
       <c r="G12" s="27" t="n">
-        <v>53</v>
+        <v>177</v>
       </c>
       <c r="H12" s="25" t="n">
-        <v>60</v>
+        <v>365</v>
       </c>
       <c r="I12" s="28" t="n">
-        <v>5.6</v>
+        <v>0.95</v>
       </c>
       <c r="J12" s="25" t="n">
         <v>0</v>
@@ -6739,12 +6739,12 @@
     <row r="13">
       <c r="A13" s="25" t="inlineStr">
         <is>
-          <t>DRY011</t>
+          <t>DRY010</t>
         </is>
       </c>
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>Greek Yoghurt 1kg</t>
+          <t>Butter 500g</t>
         </is>
       </c>
       <c r="C13" s="25" t="inlineStr">
@@ -6758,19 +6758,19 @@
         </is>
       </c>
       <c r="E13" s="26" t="n">
-        <v>4.893</v>
+        <v>6.714</v>
       </c>
       <c r="F13" s="26" t="n">
-        <v>2.299</v>
+        <v>3.75</v>
       </c>
       <c r="G13" s="27" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="H13" s="25" t="n">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="I13" s="28" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J13" s="25" t="n">
         <v>0</v>
@@ -6779,12 +6779,12 @@
     <row r="14">
       <c r="A14" s="25" t="inlineStr">
         <is>
-          <t>DRY012</t>
+          <t>DRY011</t>
         </is>
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Cheese Block 1kg</t>
+          <t>Greek Yoghurt 1kg</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -6798,19 +6798,19 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>5.214</v>
+        <v>4.179</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>2.378</v>
+        <v>2.195</v>
       </c>
       <c r="G14" s="27" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>90</v>
+        <v>21</v>
       </c>
       <c r="I14" s="28" t="n">
-        <v>10.4</v>
+        <v>5.1</v>
       </c>
       <c r="J14" s="25" t="n">
         <v>0</v>
@@ -6819,38 +6819,38 @@
     <row r="15">
       <c r="A15" s="25" t="inlineStr">
         <is>
-          <t>FRZ001</t>
+          <t>DRY012</t>
         </is>
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>Ice Cream Tub 2L</t>
+          <t>Cheese Block 1kg</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
-          <t>Frozen</t>
+          <t>Dairy</t>
         </is>
       </c>
       <c r="D15" s="25" t="inlineStr">
         <is>
-          <t>Frozen Foods NZ</t>
+          <t>Dairy Co-op</t>
         </is>
       </c>
       <c r="E15" s="26" t="n">
-        <v>7.071</v>
+        <v>6</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>3.126</v>
+        <v>2.994</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="I15" s="28" t="n">
-        <v>5.4</v>
+        <v>10.4</v>
       </c>
       <c r="J15" s="25" t="n">
         <v>0</v>
@@ -6859,12 +6859,12 @@
     <row r="16">
       <c r="A16" s="25" t="inlineStr">
         <is>
-          <t>FRZ002</t>
+          <t>FRZ001</t>
         </is>
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>Ice Block Single</t>
+          <t>Ice Cream Tub 2L</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
@@ -6878,19 +6878,19 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>9.893000000000001</v>
+        <v>6.536</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>3.975</v>
+        <v>3.18</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>102</v>
+        <v>63</v>
       </c>
       <c r="H16" s="25" t="n">
         <v>365</v>
       </c>
       <c r="I16" s="28" t="n">
-        <v>1.2</v>
+        <v>5.4</v>
       </c>
       <c r="J16" s="25" t="n">
         <v>0</v>
@@ -6899,12 +6899,12 @@
     <row r="17">
       <c r="A17" s="25" t="inlineStr">
         <is>
-          <t>FRZ003</t>
+          <t>FRZ002</t>
         </is>
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>Frozen Pizza</t>
+          <t>Ice Block Single</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
@@ -6918,19 +6918,19 @@
         </is>
       </c>
       <c r="E17" s="26" t="n">
-        <v>5.964</v>
+        <v>11.393</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>3.361</v>
+        <v>5.159</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>46</v>
+        <v>90</v>
       </c>
       <c r="H17" s="25" t="n">
         <v>365</v>
       </c>
       <c r="I17" s="28" t="n">
-        <v>4.7</v>
+        <v>1.2</v>
       </c>
       <c r="J17" s="25" t="n">
         <v>0</v>
@@ -6939,12 +6939,12 @@
     <row r="18">
       <c r="A18" s="25" t="inlineStr">
         <is>
-          <t>FRZ004</t>
+          <t>FRZ003</t>
         </is>
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>Frozen Dumplings 1kg</t>
+          <t>Frozen Pizza</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
@@ -6954,23 +6954,23 @@
       </c>
       <c r="D18" s="25" t="inlineStr">
         <is>
-          <t>Asia Imports</t>
+          <t>Frozen Foods NZ</t>
         </is>
       </c>
       <c r="E18" s="26" t="n">
-        <v>4.464</v>
+        <v>6.25</v>
       </c>
       <c r="F18" s="26" t="n">
-        <v>2.457</v>
+        <v>2.81</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="H18" s="25" t="n">
         <v>365</v>
       </c>
       <c r="I18" s="28" t="n">
-        <v>7.1</v>
+        <v>4.7</v>
       </c>
       <c r="J18" s="25" t="n">
         <v>0</v>
@@ -6979,38 +6979,38 @@
     <row r="19">
       <c r="A19" s="25" t="inlineStr">
         <is>
-          <t>FTG001</t>
+          <t>FRZ004</t>
         </is>
       </c>
       <c r="B19" s="25" t="inlineStr">
         <is>
-          <t>Chicken Sandwich</t>
+          <t>Frozen Dumplings 1kg</t>
         </is>
       </c>
       <c r="C19" s="25" t="inlineStr">
         <is>
-          <t>Food To Go</t>
+          <t>Frozen</t>
         </is>
       </c>
       <c r="D19" s="25" t="inlineStr">
         <is>
-          <t>FreshKitchen</t>
+          <t>Asia Imports</t>
         </is>
       </c>
       <c r="E19" s="26" t="n">
-        <v>19.357</v>
+        <v>4.786</v>
       </c>
       <c r="F19" s="26" t="n">
-        <v>5.411</v>
+        <v>3.304</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>2</v>
+        <v>365</v>
       </c>
       <c r="I19" s="28" t="n">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="J19" s="25" t="n">
         <v>0</v>
@@ -7019,12 +7019,12 @@
     <row r="20">
       <c r="A20" s="25" t="inlineStr">
         <is>
-          <t>FTG002</t>
+          <t>FTG001</t>
         </is>
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>Sushi Pack 8pc</t>
+          <t>Chicken Sandwich</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
@@ -7038,19 +7038,19 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>9.214</v>
+        <v>20.357</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>3.224</v>
+        <v>6.384</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>117</v>
+        <v>147</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I20" s="28" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="J20" s="25" t="n">
         <v>0</v>
@@ -7059,12 +7059,12 @@
     <row r="21">
       <c r="A21" s="25" t="inlineStr">
         <is>
-          <t>FTG003</t>
+          <t>FTG002</t>
         </is>
       </c>
       <c r="B21" s="25" t="inlineStr">
         <is>
-          <t>Hot Pie Mince &amp; Cheese</t>
+          <t>Sushi Pack 8pc</t>
         </is>
       </c>
       <c r="C21" s="25" t="inlineStr">
@@ -7078,19 +7078,19 @@
         </is>
       </c>
       <c r="E21" s="26" t="n">
-        <v>18.143</v>
+        <v>11.75</v>
       </c>
       <c r="F21" s="26" t="n">
-        <v>6.346</v>
+        <v>4.68</v>
       </c>
       <c r="G21" s="27" t="n">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="H21" s="25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" s="28" t="n">
-        <v>2.4</v>
+        <v>5.6</v>
       </c>
       <c r="J21" s="25" t="n">
         <v>0</v>
@@ -7099,12 +7099,12 @@
     <row r="22">
       <c r="A22" s="25" t="inlineStr">
         <is>
-          <t>FTG004</t>
+          <t>FTG003</t>
         </is>
       </c>
       <c r="B22" s="25" t="inlineStr">
         <is>
-          <t>Salad Bowl</t>
+          <t>Hot Pie Mince &amp; Cheese</t>
         </is>
       </c>
       <c r="C22" s="25" t="inlineStr">
@@ -7118,19 +7118,19 @@
         </is>
       </c>
       <c r="E22" s="26" t="n">
-        <v>6.286</v>
+        <v>16.75</v>
       </c>
       <c r="F22" s="26" t="n">
-        <v>2.637</v>
+        <v>5.089</v>
       </c>
       <c r="G22" s="27" t="n">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="H22" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I22" s="28" t="n">
-        <v>6.2</v>
+        <v>2.4</v>
       </c>
       <c r="J22" s="25" t="n">
         <v>0</v>
@@ -7139,12 +7139,12 @@
     <row r="23">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>FTG005</t>
+          <t>FTG004</t>
         </is>
       </c>
       <c r="B23" s="25" t="inlineStr">
         <is>
-          <t>Filled Roll</t>
+          <t>Salad Bowl</t>
         </is>
       </c>
       <c r="C23" s="25" t="inlineStr">
@@ -7158,19 +7158,19 @@
         </is>
       </c>
       <c r="E23" s="26" t="n">
-        <v>11</v>
+        <v>5.464</v>
       </c>
       <c r="F23" s="26" t="n">
-        <v>4.823</v>
+        <v>2.219</v>
       </c>
       <c r="G23" s="27" t="n">
-        <v>91</v>
+        <v>52</v>
       </c>
       <c r="H23" s="25" t="n">
         <v>2</v>
       </c>
       <c r="I23" s="28" t="n">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="J23" s="25" t="n">
         <v>0</v>
@@ -7179,38 +7179,38 @@
     <row r="24">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>GRO001</t>
+          <t>FTG005</t>
         </is>
       </c>
       <c r="B24" s="25" t="inlineStr">
         <is>
-          <t>Instant Noodles 5pk</t>
+          <t>Filled Roll</t>
         </is>
       </c>
       <c r="C24" s="25" t="inlineStr">
         <is>
-          <t>Grocery</t>
+          <t>Food To Go</t>
         </is>
       </c>
       <c r="D24" s="25" t="inlineStr">
         <is>
-          <t>Asia Imports</t>
+          <t>FreshKitchen</t>
         </is>
       </c>
       <c r="E24" s="26" t="n">
-        <v>11.857</v>
+        <v>10.536</v>
       </c>
       <c r="F24" s="26" t="n">
-        <v>4.369</v>
+        <v>3.512</v>
       </c>
       <c r="G24" s="27" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="H24" s="25" t="n">
-        <v>365</v>
+        <v>2</v>
       </c>
       <c r="I24" s="28" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="J24" s="25" t="n">
         <v>0</v>
@@ -7219,12 +7219,12 @@
     <row r="25">
       <c r="A25" s="25" t="inlineStr">
         <is>
-          <t>GRO002</t>
+          <t>GRO001</t>
         </is>
       </c>
       <c r="B25" s="25" t="inlineStr">
         <is>
-          <t>Canned Soup 500g</t>
+          <t>Instant Noodles 5pk</t>
         </is>
       </c>
       <c r="C25" s="25" t="inlineStr">
@@ -7234,23 +7234,23 @@
       </c>
       <c r="D25" s="25" t="inlineStr">
         <is>
-          <t>Pantry Brands</t>
+          <t>Asia Imports</t>
         </is>
       </c>
       <c r="E25" s="26" t="n">
-        <v>5.786</v>
+        <v>14.393</v>
       </c>
       <c r="F25" s="26" t="n">
-        <v>3.201</v>
+        <v>4.779</v>
       </c>
       <c r="G25" s="27" t="n">
-        <v>40</v>
+        <v>101</v>
       </c>
       <c r="H25" s="25" t="n">
-        <v>730</v>
+        <v>365</v>
       </c>
       <c r="I25" s="28" t="n">
-        <v>1.9</v>
+        <v>2.6</v>
       </c>
       <c r="J25" s="25" t="n">
         <v>0</v>
@@ -7259,12 +7259,12 @@
     <row r="26">
       <c r="A26" s="25" t="inlineStr">
         <is>
-          <t>GRO003</t>
+          <t>GRO002</t>
         </is>
       </c>
       <c r="B26" s="25" t="inlineStr">
         <is>
-          <t>Pasta 500g</t>
+          <t>Canned Soup 500g</t>
         </is>
       </c>
       <c r="C26" s="25" t="inlineStr">
@@ -7278,19 +7278,19 @@
         </is>
       </c>
       <c r="E26" s="26" t="n">
-        <v>6.714</v>
+        <v>5.75</v>
       </c>
       <c r="F26" s="26" t="n">
-        <v>3.041</v>
+        <v>3.524</v>
       </c>
       <c r="G26" s="27" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="H26" s="25" t="n">
         <v>730</v>
       </c>
       <c r="I26" s="28" t="n">
-        <v>1.3</v>
+        <v>1.9</v>
       </c>
       <c r="J26" s="25" t="n">
         <v>0</v>
@@ -7299,12 +7299,12 @@
     <row r="27">
       <c r="A27" s="25" t="inlineStr">
         <is>
-          <t>GRO004</t>
+          <t>GRO003</t>
         </is>
       </c>
       <c r="B27" s="25" t="inlineStr">
         <is>
-          <t>Simmer Sauce 485g</t>
+          <t>Pasta 500g</t>
         </is>
       </c>
       <c r="C27" s="25" t="inlineStr">
@@ -7318,33 +7318,33 @@
         </is>
       </c>
       <c r="E27" s="26" t="n">
-        <v>5</v>
+        <v>5.929</v>
       </c>
       <c r="F27" s="26" t="n">
-        <v>2.553</v>
+        <v>2.652</v>
       </c>
       <c r="G27" s="27" t="n">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="H27" s="25" t="n">
-        <v>540</v>
+        <v>730</v>
       </c>
       <c r="I27" s="28" t="n">
-        <v>2.3</v>
+        <v>1.3</v>
       </c>
       <c r="J27" s="25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="25" t="inlineStr">
         <is>
-          <t>GRO005</t>
+          <t>GRO004</t>
         </is>
       </c>
       <c r="B28" s="25" t="inlineStr">
         <is>
-          <t>Salsa 300g</t>
+          <t>Simmer Sauce 485g</t>
         </is>
       </c>
       <c r="C28" s="25" t="inlineStr">
@@ -7354,37 +7354,37 @@
       </c>
       <c r="D28" s="25" t="inlineStr">
         <is>
-          <t>Latin Pantry</t>
+          <t>Pantry Brands</t>
         </is>
       </c>
       <c r="E28" s="26" t="n">
-        <v>2.679</v>
+        <v>5.321</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>2.389</v>
+        <v>3.244</v>
       </c>
       <c r="G28" s="27" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H28" s="25" t="n">
-        <v>365</v>
+        <v>540</v>
       </c>
       <c r="I28" s="28" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="J28" s="25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="25" t="inlineStr">
         <is>
-          <t>GRO006</t>
+          <t>GRO005</t>
         </is>
       </c>
       <c r="B29" s="25" t="inlineStr">
         <is>
-          <t>Taco Kit</t>
+          <t>Salsa 300g</t>
         </is>
       </c>
       <c r="C29" s="25" t="inlineStr">
@@ -7398,19 +7398,19 @@
         </is>
       </c>
       <c r="E29" s="26" t="n">
-        <v>2.893</v>
+        <v>3.429</v>
       </c>
       <c r="F29" s="26" t="n">
-        <v>1.524</v>
+        <v>2.008</v>
       </c>
       <c r="G29" s="27" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H29" s="25" t="n">
         <v>365</v>
       </c>
       <c r="I29" s="28" t="n">
-        <v>4</v>
+        <v>2.9</v>
       </c>
       <c r="J29" s="25" t="n">
         <v>0</v>
@@ -7419,12 +7419,12 @@
     <row r="30">
       <c r="A30" s="25" t="inlineStr">
         <is>
-          <t>GRO007</t>
+          <t>GRO006</t>
         </is>
       </c>
       <c r="B30" s="25" t="inlineStr">
         <is>
-          <t>Eggs Free Range 12pk</t>
+          <t>Taco Kit</t>
         </is>
       </c>
       <c r="C30" s="25" t="inlineStr">
@@ -7434,23 +7434,23 @@
       </c>
       <c r="D30" s="25" t="inlineStr">
         <is>
-          <t>Farm Fresh</t>
+          <t>Latin Pantry</t>
         </is>
       </c>
       <c r="E30" s="26" t="n">
-        <v>9.393000000000001</v>
+        <v>3.536</v>
       </c>
       <c r="F30" s="26" t="n">
-        <v>3.573</v>
+        <v>2.186</v>
       </c>
       <c r="G30" s="27" t="n">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="H30" s="25" t="n">
-        <v>35</v>
+        <v>365</v>
       </c>
       <c r="I30" s="28" t="n">
-        <v>8.199999999999999</v>
+        <v>4</v>
       </c>
       <c r="J30" s="25" t="n">
         <v>0</v>
@@ -7459,12 +7459,12 @@
     <row r="31">
       <c r="A31" s="25" t="inlineStr">
         <is>
-          <t>GRO008</t>
+          <t>GRO007</t>
         </is>
       </c>
       <c r="B31" s="25" t="inlineStr">
         <is>
-          <t>Coffee Beans 200g</t>
+          <t>Eggs Free Range 12pk</t>
         </is>
       </c>
       <c r="C31" s="25" t="inlineStr">
@@ -7474,23 +7474,23 @@
       </c>
       <c r="D31" s="25" t="inlineStr">
         <is>
-          <t>Pantry Brands</t>
+          <t>Farm Fresh</t>
         </is>
       </c>
       <c r="E31" s="26" t="n">
-        <v>3.643</v>
+        <v>9.893000000000001</v>
       </c>
       <c r="F31" s="26" t="n">
-        <v>2.147</v>
+        <v>4.184</v>
       </c>
       <c r="G31" s="27" t="n">
-        <v>28</v>
+        <v>80</v>
       </c>
       <c r="H31" s="25" t="n">
-        <v>180</v>
+        <v>35</v>
       </c>
       <c r="I31" s="28" t="n">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J31" s="25" t="n">
         <v>0</v>
@@ -7499,38 +7499,38 @@
     <row r="32">
       <c r="A32" s="25" t="inlineStr">
         <is>
-          <t>HHD001</t>
+          <t>GRO008</t>
         </is>
       </c>
       <c r="B32" s="25" t="inlineStr">
         <is>
-          <t>Toilet Paper 6pk</t>
+          <t>Coffee Beans 200g</t>
         </is>
       </c>
       <c r="C32" s="25" t="inlineStr">
         <is>
-          <t>Household</t>
+          <t>Grocery</t>
         </is>
       </c>
       <c r="D32" s="25" t="inlineStr">
         <is>
-          <t>Home Supplies</t>
+          <t>Pantry Brands</t>
         </is>
       </c>
       <c r="E32" s="26" t="n">
-        <v>5.5</v>
+        <v>3</v>
       </c>
       <c r="F32" s="26" t="n">
-        <v>2.411</v>
+        <v>2.108</v>
       </c>
       <c r="G32" s="27" t="n">
-        <v>47</v>
+        <v>20</v>
       </c>
       <c r="H32" s="25" t="n">
-        <v>3650</v>
+        <v>180</v>
       </c>
       <c r="I32" s="28" t="n">
-        <v>5.9</v>
+        <v>7.6</v>
       </c>
       <c r="J32" s="25" t="n">
         <v>0</v>
@@ -7539,12 +7539,12 @@
     <row r="33">
       <c r="A33" s="25" t="inlineStr">
         <is>
-          <t>HHD002</t>
+          <t>HHD001</t>
         </is>
       </c>
       <c r="B33" s="25" t="inlineStr">
         <is>
-          <t>Dishwash Liquid</t>
+          <t>Toilet Paper 6pk</t>
         </is>
       </c>
       <c r="C33" s="25" t="inlineStr">
@@ -7558,19 +7558,19 @@
         </is>
       </c>
       <c r="E33" s="26" t="n">
-        <v>2.107</v>
+        <v>4.357</v>
       </c>
       <c r="F33" s="26" t="n">
-        <v>1.37</v>
+        <v>2.831</v>
       </c>
       <c r="G33" s="27" t="n">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="H33" s="25" t="n">
-        <v>1095</v>
+        <v>3650</v>
       </c>
       <c r="I33" s="28" t="n">
-        <v>2.9</v>
+        <v>5.9</v>
       </c>
       <c r="J33" s="25" t="n">
         <v>0</v>
@@ -7579,12 +7579,12 @@
     <row r="34">
       <c r="A34" s="25" t="inlineStr">
         <is>
-          <t>HHD003</t>
+          <t>HHD002</t>
         </is>
       </c>
       <c r="B34" s="25" t="inlineStr">
         <is>
-          <t>Phone Charger Cable</t>
+          <t>Dishwash Liquid</t>
         </is>
       </c>
       <c r="C34" s="25" t="inlineStr">
@@ -7598,19 +7598,19 @@
         </is>
       </c>
       <c r="E34" s="26" t="n">
-        <v>0.643</v>
+        <v>3.536</v>
       </c>
       <c r="F34" s="26" t="n">
-        <v>0.951</v>
+        <v>2.027</v>
       </c>
       <c r="G34" s="27" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="H34" s="25" t="n">
-        <v>3650</v>
+        <v>1095</v>
       </c>
       <c r="I34" s="28" t="n">
-        <v>5.5</v>
+        <v>2.9</v>
       </c>
       <c r="J34" s="25" t="n">
         <v>0</v>
@@ -7638,13 +7638,13 @@
         </is>
       </c>
       <c r="E35" s="26" t="n">
-        <v>4.857</v>
+        <v>5.643</v>
       </c>
       <c r="F35" s="26" t="n">
-        <v>2.649</v>
+        <v>3.423</v>
       </c>
       <c r="G35" s="27" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="H35" s="25" t="n">
         <v>180</v>
@@ -7678,13 +7678,13 @@
         </is>
       </c>
       <c r="E36" s="26" t="n">
-        <v>5.286</v>
+        <v>4.286</v>
       </c>
       <c r="F36" s="26" t="n">
-        <v>3.017</v>
+        <v>2.813</v>
       </c>
       <c r="G36" s="27" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="H36" s="25" t="n">
         <v>730</v>
@@ -7718,13 +7718,13 @@
         </is>
       </c>
       <c r="E37" s="26" t="n">
-        <v>3.857</v>
+        <v>4.393</v>
       </c>
       <c r="F37" s="26" t="n">
-        <v>2.05</v>
+        <v>2.409</v>
       </c>
       <c r="G37" s="27" t="n">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="H37" s="25" t="n">
         <v>365</v>
@@ -7758,13 +7758,13 @@
         </is>
       </c>
       <c r="E38" s="26" t="n">
-        <v>1.929</v>
+        <v>2.321</v>
       </c>
       <c r="F38" s="26" t="n">
-        <v>1.904</v>
+        <v>1.926</v>
       </c>
       <c r="G38" s="27" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H38" s="25" t="n">
         <v>730</v>
@@ -7798,10 +7798,10 @@
         </is>
       </c>
       <c r="E39" s="26" t="n">
-        <v>34.286</v>
+        <v>34.393</v>
       </c>
       <c r="F39" s="26" t="n">
-        <v>13.424</v>
+        <v>13.593</v>
       </c>
       <c r="G39" s="27" t="n">
         <v>344</v>
@@ -7838,13 +7838,13 @@
         </is>
       </c>
       <c r="E40" s="26" t="n">
-        <v>14.607</v>
+        <v>16.107</v>
       </c>
       <c r="F40" s="26" t="n">
-        <v>4.113</v>
+        <v>3.975</v>
       </c>
       <c r="G40" s="27" t="n">
-        <v>145</v>
+        <v>138</v>
       </c>
       <c r="H40" s="25" t="n">
         <v>10</v>
@@ -7878,10 +7878,10 @@
         </is>
       </c>
       <c r="E41" s="26" t="n">
-        <v>8.071</v>
+        <v>6.679</v>
       </c>
       <c r="F41" s="26" t="n">
-        <v>4.225</v>
+        <v>3.151</v>
       </c>
       <c r="G41" s="27" t="n">
         <v>60</v>
@@ -7918,13 +7918,13 @@
         </is>
       </c>
       <c r="E42" s="26" t="n">
-        <v>5.357</v>
+        <v>3.929</v>
       </c>
       <c r="F42" s="26" t="n">
-        <v>3.021</v>
+        <v>2.493</v>
       </c>
       <c r="G42" s="27" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H42" s="25" t="n">
         <v>730</v>
@@ -7958,13 +7958,13 @@
         </is>
       </c>
       <c r="E43" s="26" t="n">
-        <v>1.714</v>
+        <v>2.036</v>
       </c>
       <c r="F43" s="26" t="n">
-        <v>1.243</v>
+        <v>1.666</v>
       </c>
       <c r="G43" s="27" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="H43" s="25" t="n">
         <v>730</v>
@@ -7998,13 +7998,13 @@
         </is>
       </c>
       <c r="E44" s="26" t="n">
-        <v>31.607</v>
+        <v>31.071</v>
       </c>
       <c r="F44" s="26" t="n">
-        <v>6.63</v>
+        <v>7.717</v>
       </c>
       <c r="G44" s="27" t="n">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H44" s="25" t="n">
         <v>6</v>
@@ -8038,13 +8038,13 @@
         </is>
       </c>
       <c r="E45" s="26" t="n">
-        <v>8.071</v>
+        <v>7.75</v>
       </c>
       <c r="F45" s="26" t="n">
-        <v>3.463</v>
+        <v>3.384</v>
       </c>
       <c r="G45" s="27" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H45" s="25" t="n">
         <v>5</v>
@@ -8078,13 +8078,13 @@
         </is>
       </c>
       <c r="E46" s="26" t="n">
-        <v>4.5</v>
+        <v>4.464</v>
       </c>
       <c r="F46" s="26" t="n">
-        <v>2.769</v>
+        <v>2.912</v>
       </c>
       <c r="G46" s="27" t="n">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="H46" s="25" t="n">
         <v>7</v>
@@ -8118,13 +8118,13 @@
         </is>
       </c>
       <c r="E47" s="26" t="n">
-        <v>20.679</v>
+        <v>22.786</v>
       </c>
       <c r="F47" s="26" t="n">
-        <v>6.717</v>
+        <v>6.551</v>
       </c>
       <c r="G47" s="27" t="n">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="H47" s="25" t="n">
         <v>180</v>
@@ -8158,13 +8158,13 @@
         </is>
       </c>
       <c r="E48" s="26" t="n">
-        <v>15.821</v>
+        <v>17.429</v>
       </c>
       <c r="F48" s="26" t="n">
-        <v>4.785</v>
+        <v>5.196</v>
       </c>
       <c r="G48" s="27" t="n">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="H48" s="25" t="n">
         <v>270</v>
@@ -8198,13 +8198,13 @@
         </is>
       </c>
       <c r="E49" s="26" t="n">
-        <v>9.356999999999999</v>
+        <v>9.179</v>
       </c>
       <c r="F49" s="26" t="n">
-        <v>3.498</v>
+        <v>3.443</v>
       </c>
       <c r="G49" s="27" t="n">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="H49" s="25" t="n">
         <v>240</v>
@@ -8238,13 +8238,13 @@
         </is>
       </c>
       <c r="E50" s="26" t="n">
-        <v>9.143000000000001</v>
+        <v>9.393000000000001</v>
       </c>
       <c r="F50" s="26" t="n">
-        <v>3.229</v>
+        <v>3.224</v>
       </c>
       <c r="G50" s="27" t="n">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="H50" s="25" t="n">
         <v>180</v>
@@ -8278,13 +8278,13 @@
         </is>
       </c>
       <c r="E51" s="26" t="n">
-        <v>10.107</v>
+        <v>9.679</v>
       </c>
       <c r="F51" s="26" t="n">
-        <v>3.833</v>
+        <v>3.682</v>
       </c>
       <c r="G51" s="27" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H51" s="25" t="n">
         <v>300</v>
@@ -8641,7 +8641,7 @@
     <row r="6">
       <c r="C6" s="32" t="inlineStr">
         <is>
-          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 04 Oct 2026.  Shelly v1.6.0.</t>
+          <t>Store: Demo Neighbourhood Store (Eden Terrace format).  Data to 11 Oct 2026.  Shelly v1.19.0.</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
     <row r="24">
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Generated by Shelly on 04 Oct 2026 20:46</t>
+          <t>Generated by Shelly on 11 Oct 2026 21:21</t>
         </is>
       </c>
     </row>
